--- a/research/traditional_assets/database/data/switzerland/switzerland_metals_mining.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_metals_mining.xlsx
@@ -647,10 +647,10 @@
         <v>-0.01141192447540194</v>
       </c>
       <c r="X2">
-        <v>0.1103777281980757</v>
+        <v>0.1103362104604845</v>
       </c>
       <c r="Y2">
-        <v>-0.1217896526734777</v>
+        <v>-0.1217481349358864</v>
       </c>
       <c r="Z2">
         <v>3.325111075563758</v>
@@ -659,10 +659,10 @@
         <v>0.0768185480370874</v>
       </c>
       <c r="AB2">
-        <v>0.08699305095401796</v>
+        <v>0.08696713915889477</v>
       </c>
       <c r="AC2">
-        <v>-0.01017450291693056</v>
+        <v>-0.01014859112180737</v>
       </c>
       <c r="AD2">
         <v>32009</v>
@@ -781,10 +781,10 @@
         <v>-0.01141192447540194</v>
       </c>
       <c r="X3">
-        <v>0.1103777281980757</v>
+        <v>0.1103362104604845</v>
       </c>
       <c r="Y3">
-        <v>-0.1217896526734777</v>
+        <v>-0.1217481349358864</v>
       </c>
       <c r="Z3">
         <v>3.325111075563758</v>
@@ -793,10 +793,10 @@
         <v>0.0768185480370874</v>
       </c>
       <c r="AB3">
-        <v>0.08699305095401796</v>
+        <v>0.08696713915889477</v>
       </c>
       <c r="AC3">
-        <v>-0.01017450291693056</v>
+        <v>-0.01014859112180737</v>
       </c>
       <c r="AD3">
         <v>32009</v>
@@ -1133,49 +1133,49 @@
         <v>1.92735814962053</v>
       </c>
       <c r="F2">
-        <v>7.01296924034749</v>
+        <v>3.00162255195767</v>
       </c>
       <c r="G2">
         <v>2.73231028431037</v>
       </c>
       <c r="H2">
-        <v>1.88993576164</v>
+        <v>4.21601054519691</v>
       </c>
       <c r="I2">
         <v>0.375886148270058</v>
       </c>
       <c r="J2">
-        <v>0.26</v>
+        <v>0.58</v>
       </c>
       <c r="K2">
         <v>53786.8</v>
       </c>
       <c r="L2">
-        <v>64492.7759144133</v>
+        <v>38984.9106281498</v>
       </c>
       <c r="M2">
         <v>83404.0707307838</v>
       </c>
       <c r="N2">
-        <v>84122.85430441709</v>
+        <v>86192.93165200439</v>
       </c>
       <c r="O2">
         <v>32394.2707307838</v>
       </c>
       <c r="P2">
-        <v>22407.0783900038</v>
+        <v>49985.0210238546</v>
       </c>
       <c r="Q2">
-        <v>0.08699305095401801</v>
+        <v>0.0869671391588948</v>
       </c>
       <c r="R2">
-        <v>0.0866410789647362</v>
+        <v>0.0856351340461992</v>
       </c>
       <c r="S2">
         <v>0.0481656</v>
       </c>
       <c r="T2">
-        <v>0.0450912</v>
+        <v>0.0472262</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1184,20 +1184,20 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="W2">
-        <v>0.110377728198076</v>
+        <v>0.110336210460484</v>
       </c>
       <c r="X2">
-        <v>0.101239685087481</v>
+        <v>0.138676042967141</v>
       </c>
       <c r="Y2">
         <v>1.49044365959548</v>
       </c>
       <c r="Z2">
-        <v>1.27953908312106</v>
+        <v>2.14494325559217</v>
       </c>
       <c r="AA2">
         <v>32009</v>
@@ -1230,7 +1230,7 @@
         <v>53786.8</v>
       </c>
       <c r="AK2">
-        <v>0.043327855959079</v>
+        <v>0.04329999999999998</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1418,13 +1418,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.08844413846070454</v>
+        <v>0.0884167220711873</v>
       </c>
       <c r="C2">
-        <v>83343.01116590911</v>
+        <v>83344.12997440589</v>
       </c>
       <c r="D2">
-        <v>80566.01116590911</v>
+        <v>80567.12997440589</v>
       </c>
       <c r="E2">
         <v>-32394.2707307838</v>
@@ -1469,19 +1469,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.08844413846070454</v>
+        <v>0.0884167220711873</v>
       </c>
       <c r="T2">
         <v>0.9842199092652958</v>
       </c>
       <c r="U2">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V2">
         <v>0.146</v>
       </c>
       <c r="W2">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1500,13 +1500,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.08836539601855191</v>
+        <v>0.08832606365696336</v>
       </c>
       <c r="C3">
-        <v>82630.24087798171</v>
+        <v>82654.07483565883</v>
       </c>
       <c r="D3">
-        <v>80715.05158528955</v>
+        <v>80738.88554296667</v>
       </c>
       <c r="E3">
         <v>-31532.46002347596</v>
@@ -1533,37 +1533,37 @@
         <v>8297</v>
       </c>
       <c r="M3">
-        <v>44.55561356781523</v>
+        <v>43.34907857758425</v>
       </c>
       <c r="N3">
-        <v>8252.444386432186</v>
+        <v>8253.650921422415</v>
       </c>
       <c r="O3">
-        <v>1204.856880419099</v>
+        <v>1205.033034527672</v>
       </c>
       <c r="P3">
-        <v>7047.587506013087</v>
+        <v>7048.617886894743</v>
       </c>
       <c r="Q3">
-        <v>13570.58750601309</v>
+        <v>13571.61788689474</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.08881199799853728</v>
+        <v>0.0887843451080438</v>
       </c>
       <c r="T3">
         <v>0.9927100486846145</v>
       </c>
       <c r="U3">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V3">
         <v>0.146</v>
       </c>
       <c r="W3">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>186.2167151479504</v>
+        <v>191.3996853508754</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1582,13 +1582,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.08828665357639928</v>
+        <v>0.08823540524273943</v>
       </c>
       <c r="C4">
-        <v>81918.02303679292</v>
+        <v>81964.75356936523</v>
       </c>
       <c r="D4">
-        <v>80864.64445140859</v>
+        <v>80911.3749839809</v>
       </c>
       <c r="E4">
         <v>-30670.64931616812</v>
@@ -1615,37 +1615,37 @@
         <v>8297</v>
       </c>
       <c r="M4">
-        <v>89.11122713563046</v>
+        <v>86.6981571551685</v>
       </c>
       <c r="N4">
-        <v>8207.888772864369</v>
+        <v>8210.301842844832</v>
       </c>
       <c r="O4">
-        <v>1198.351760838198</v>
+        <v>1198.704069055345</v>
       </c>
       <c r="P4">
-        <v>7009.537012026171</v>
+        <v>7011.597773789486</v>
       </c>
       <c r="Q4">
-        <v>13532.53701202617</v>
+        <v>13534.59777378949</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.08918736487387682</v>
+        <v>0.08915947065585655</v>
       </c>
       <c r="T4">
         <v>1.001373456255348</v>
       </c>
       <c r="U4">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V4">
         <v>0.146</v>
       </c>
       <c r="W4">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>93.10835757397517</v>
+        <v>95.69984267543772</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1664,13 +1664,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.08820791113424667</v>
+        <v>0.08814474682851549</v>
       </c>
       <c r="C5">
-        <v>81206.36071966987</v>
+        <v>81276.17088910009</v>
       </c>
       <c r="D5">
-        <v>81014.79284159339</v>
+        <v>81084.6030110236</v>
       </c>
       <c r="E5">
         <v>-29808.83860886028</v>
@@ -1697,37 +1697,37 @@
         <v>8297</v>
       </c>
       <c r="M5">
-        <v>133.6668407034457</v>
+        <v>130.0472357327527</v>
       </c>
       <c r="N5">
-        <v>8163.333159296554</v>
+        <v>8166.952764267247</v>
       </c>
       <c r="O5">
-        <v>1191.846641257297</v>
+        <v>1192.375103583018</v>
       </c>
       <c r="P5">
-        <v>6971.486518039257</v>
+        <v>6974.577660684229</v>
       </c>
       <c r="Q5">
-        <v>13494.48651803926</v>
+        <v>13497.57766068423</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.08957047127241924</v>
+        <v>0.08954233075104689</v>
       </c>
       <c r="T5">
         <v>1.010215490786303</v>
       </c>
       <c r="U5">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V5">
         <v>0.146</v>
       </c>
       <c r="W5">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>62.07223838265012</v>
+        <v>63.79989511695848</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1746,13 +1746,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.08812916869209401</v>
+        <v>0.08805408841429156</v>
       </c>
       <c r="C6">
-        <v>80495.25702683808</v>
+        <v>80588.33154889125</v>
       </c>
       <c r="D6">
-        <v>81165.49985606944</v>
+        <v>81258.5743781226</v>
       </c>
       <c r="E6">
         <v>-28947.02790155244</v>
@@ -1779,37 +1779,37 @@
         <v>8297</v>
       </c>
       <c r="M6">
-        <v>178.2224542712609</v>
+        <v>173.396314310337</v>
       </c>
       <c r="N6">
-        <v>8118.777545728739</v>
+        <v>8123.603685689663</v>
       </c>
       <c r="O6">
-        <v>1185.341521676396</v>
+        <v>1186.046138110691</v>
       </c>
       <c r="P6">
-        <v>6933.436024052343</v>
+        <v>6937.557547578972</v>
       </c>
       <c r="Q6">
-        <v>13456.43602405234</v>
+        <v>13460.55754757897</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.0899615590542646</v>
+        <v>0.08993316709822037</v>
       </c>
       <c r="T6">
         <v>1.019241734369986</v>
       </c>
       <c r="U6">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V6">
         <v>0.146</v>
       </c>
       <c r="W6">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>46.55417878698758</v>
+        <v>47.84992133771885</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1828,13 +1828,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.0880504262499414</v>
+        <v>0.08796343000006762</v>
       </c>
       <c r="C7">
-        <v>79784.71508163448</v>
+        <v>79901.24034365444</v>
       </c>
       <c r="D7">
-        <v>81316.76861817366</v>
+        <v>81433.29388019363</v>
       </c>
       <c r="E7">
         <v>-28085.2171942446</v>
@@ -1861,37 +1861,37 @@
         <v>8297</v>
       </c>
       <c r="M7">
-        <v>222.7780678390762</v>
+        <v>216.7453928879213</v>
       </c>
       <c r="N7">
-        <v>8074.221932160924</v>
+        <v>8080.254607112079</v>
       </c>
       <c r="O7">
-        <v>1178.836402095495</v>
+        <v>1179.717172638363</v>
       </c>
       <c r="P7">
-        <v>6895.385530065429</v>
+        <v>6900.537434473716</v>
       </c>
       <c r="Q7">
-        <v>13418.38553006543</v>
+        <v>13423.53743447372</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.09036088026309622</v>
+        <v>0.09033223157901855</v>
       </c>
       <c r="T7">
         <v>1.028458004134378</v>
       </c>
       <c r="U7">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V7">
         <v>0.146</v>
       </c>
       <c r="W7">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>37.24334302959006</v>
+        <v>38.27993707017508</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1910,13 +1910,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.08797168380778876</v>
+        <v>0.08787277158584368</v>
       </c>
       <c r="C8">
-        <v>79074.73803072366</v>
+        <v>79214.90210963368</v>
       </c>
       <c r="D8">
-        <v>81468.60227457069</v>
+        <v>81608.76635348071</v>
       </c>
       <c r="E8">
         <v>-27223.40648693677</v>
@@ -1943,37 +1943,37 @@
         <v>8297</v>
       </c>
       <c r="M8">
-        <v>267.3336814068913</v>
+        <v>260.0944714655055</v>
       </c>
       <c r="N8">
-        <v>8029.666318593108</v>
+        <v>8036.905528534495</v>
       </c>
       <c r="O8">
-        <v>1172.331282514594</v>
+        <v>1173.388207166036</v>
       </c>
       <c r="P8">
-        <v>6857.335036078514</v>
+        <v>6863.517321368458</v>
       </c>
       <c r="Q8">
-        <v>13380.33503607852</v>
+        <v>13386.51732136846</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.09076869766786039</v>
+        <v>0.09073978679345074</v>
       </c>
       <c r="T8">
         <v>1.037870364744821</v>
       </c>
       <c r="U8">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V8">
         <v>0.146</v>
       </c>
       <c r="W8">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>31.03611919132506</v>
+        <v>31.89994755847924</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1992,13 +1992,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.08789294136563615</v>
+        <v>0.08778211317161977</v>
       </c>
       <c r="C9">
-        <v>78365.32904431567</v>
+        <v>78529.32172484753</v>
       </c>
       <c r="D9">
-        <v>81621.00399547054</v>
+        <v>81784.9966760024</v>
       </c>
       <c r="E9">
         <v>-26361.59577962893</v>
@@ -2025,37 +2025,37 @@
         <v>8297</v>
       </c>
       <c r="M9">
-        <v>311.8892949747066</v>
+        <v>303.4435500430898</v>
       </c>
       <c r="N9">
-        <v>7985.110705025293</v>
+        <v>7993.55644995691</v>
       </c>
       <c r="O9">
-        <v>1165.826162933693</v>
+        <v>1167.059241693709</v>
       </c>
       <c r="P9">
-        <v>6819.2845420916</v>
+        <v>6826.497208263201</v>
       </c>
       <c r="Q9">
-        <v>13342.2845420916</v>
+        <v>13349.4972082632</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.09118528533939371</v>
+        <v>0.09115610663615029</v>
       </c>
       <c r="T9">
         <v>1.047485141712478</v>
       </c>
       <c r="U9">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V9">
         <v>0.146</v>
       </c>
       <c r="W9">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>26.60238787827862</v>
+        <v>27.3428121929822</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2074,13 +2074,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.08781419892348351</v>
+        <v>0.08769145475739581</v>
       </c>
       <c r="C10">
-        <v>77656.49131638699</v>
+        <v>77844.50410954132</v>
       </c>
       <c r="D10">
-        <v>81773.97697484969</v>
+        <v>81961.98976800402</v>
       </c>
       <c r="E10">
         <v>-25499.78507232109</v>
@@ -2107,37 +2107,37 @@
         <v>8297</v>
       </c>
       <c r="M10">
-        <v>356.4449085425218</v>
+        <v>346.792628620674</v>
       </c>
       <c r="N10">
-        <v>7940.555091457478</v>
+        <v>7950.207371379326</v>
       </c>
       <c r="O10">
-        <v>1159.321043352792</v>
+        <v>1160.730276221381</v>
       </c>
       <c r="P10">
-        <v>6781.234048104686</v>
+        <v>6789.477095157945</v>
       </c>
       <c r="Q10">
-        <v>13304.23404810468</v>
+        <v>13312.47709515794</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.09161092926465599</v>
+        <v>0.09158147691021284</v>
       </c>
       <c r="T10">
         <v>1.057308935570736</v>
       </c>
       <c r="U10">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V10">
         <v>0.146</v>
       </c>
       <c r="W10">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>23.27708939349379</v>
+        <v>23.92496066885943</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2156,13 +2156,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.08773545648133088</v>
+        <v>0.08760079634317189</v>
       </c>
       <c r="C11">
-        <v>76948.22806490331</v>
+        <v>77160.45422664464</v>
       </c>
       <c r="D11">
-        <v>81927.52443067385</v>
+        <v>82139.75059241518</v>
       </c>
       <c r="E11">
         <v>-24637.97436501325</v>
@@ -2189,37 +2189,37 @@
         <v>8297</v>
       </c>
       <c r="M11">
-        <v>401.000522110337</v>
+        <v>390.1417071982582</v>
       </c>
       <c r="N11">
-        <v>7895.999477889663</v>
+        <v>7906.858292801742</v>
       </c>
       <c r="O11">
-        <v>1152.815923771891</v>
+        <v>1154.401310749054</v>
       </c>
       <c r="P11">
-        <v>6743.183554117772</v>
+        <v>6752.456982052688</v>
       </c>
       <c r="Q11">
-        <v>13266.18355411777</v>
+        <v>13275.45698205269</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.0920459280014625</v>
+        <v>0.09201619598150756</v>
       </c>
       <c r="T11">
         <v>1.067348636986318</v>
       </c>
       <c r="U11">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V11">
         <v>0.146</v>
       </c>
       <c r="W11">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>20.69074612755004</v>
+        <v>21.26663170565283</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2238,13 +2238,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.08765671403917827</v>
+        <v>0.08751013792894798</v>
       </c>
       <c r="C12">
-        <v>76240.54253204538</v>
+        <v>76477.1770822356</v>
       </c>
       <c r="D12">
-        <v>82081.64960512376</v>
+        <v>82318.28415531399</v>
       </c>
       <c r="E12">
         <v>-23776.16365770542</v>
@@ -2271,37 +2271,37 @@
         <v>8297</v>
       </c>
       <c r="M12">
-        <v>445.5561356781523</v>
+        <v>433.4907857758425</v>
       </c>
       <c r="N12">
-        <v>7851.443864321847</v>
+        <v>7863.509214224157</v>
       </c>
       <c r="O12">
-        <v>1146.31080419099</v>
+        <v>1148.072345276727</v>
       </c>
       <c r="P12">
-        <v>6705.133060130858</v>
+        <v>6715.43686894743</v>
       </c>
       <c r="Q12">
-        <v>13228.13306013086</v>
+        <v>13238.43686894743</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.09249059337686473</v>
+        <v>0.09246057547660885</v>
       </c>
       <c r="T12">
         <v>1.077611442877803</v>
       </c>
       <c r="U12">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V12">
         <v>0.146</v>
       </c>
       <c r="W12">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>18.62167151479503</v>
+        <v>19.13996853508754</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2320,13 +2320,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.08757797159702563</v>
+        <v>0.08741947951472402</v>
       </c>
       <c r="C13">
-        <v>75533.43798443739</v>
+        <v>75794.67772601079</v>
       </c>
       <c r="D13">
-        <v>82236.35576482362</v>
+        <v>82497.59550639702</v>
       </c>
       <c r="E13">
         <v>-22914.35295039758</v>
@@ -2353,37 +2353,37 @@
         <v>8297</v>
       </c>
       <c r="M13">
-        <v>490.1117492459675</v>
+        <v>476.8398643534268</v>
       </c>
       <c r="N13">
-        <v>7806.888250754033</v>
+        <v>7820.160135646574</v>
       </c>
       <c r="O13">
-        <v>1139.805684610089</v>
+        <v>1141.7433798044</v>
       </c>
       <c r="P13">
-        <v>6667.082566143944</v>
+        <v>6678.416755842174</v>
       </c>
       <c r="Q13">
-        <v>13190.08256614394</v>
+        <v>13201.41675584217</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.09294525123261306</v>
+        <v>0.09291494102777981</v>
       </c>
       <c r="T13">
         <v>1.088104873620781</v>
       </c>
       <c r="U13">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V13">
         <v>0.146</v>
       </c>
       <c r="W13">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>16.92879228617731</v>
+        <v>17.39997139553413</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2402,13 +2402,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.08749922915487299</v>
+        <v>0.0873288211005001</v>
       </c>
       <c r="C14">
-        <v>74826.91771337732</v>
+        <v>75112.96125176095</v>
       </c>
       <c r="D14">
-        <v>82391.64620107137</v>
+        <v>82677.689739455</v>
       </c>
       <c r="E14">
         <v>-22052.54224308974</v>
@@ -2435,37 +2435,37 @@
         <v>8297</v>
       </c>
       <c r="M14">
-        <v>534.6673628137827</v>
+        <v>520.188942931011</v>
       </c>
       <c r="N14">
-        <v>7762.332637186218</v>
+        <v>7776.811057068989</v>
       </c>
       <c r="O14">
-        <v>1133.300565029188</v>
+        <v>1135.414414332072</v>
       </c>
       <c r="P14">
-        <v>6629.03207215703</v>
+        <v>6641.396642736916</v>
       </c>
       <c r="Q14">
-        <v>13152.03207215703</v>
+        <v>13164.39664273692</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.09341024222144659</v>
+        <v>0.09337963306875011</v>
       </c>
       <c r="T14">
         <v>1.0988367914261</v>
       </c>
       <c r="U14">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V14">
         <v>0.146</v>
       </c>
       <c r="W14">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>15.51805959566253</v>
+        <v>15.94997377923962</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2484,13 +2484,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.08742048671272037</v>
+        <v>0.08723816268627616</v>
       </c>
       <c r="C15">
-        <v>74120.9850350706</v>
+        <v>74432.0327978538</v>
       </c>
       <c r="D15">
-        <v>82547.52423007249</v>
+        <v>82858.57199285569</v>
       </c>
       <c r="E15">
         <v>-21190.7315357819</v>
@@ -2517,37 +2517,37 @@
         <v>8297</v>
       </c>
       <c r="M15">
-        <v>579.222976381598</v>
+        <v>563.5380215085953</v>
       </c>
       <c r="N15">
-        <v>7717.777023618402</v>
+        <v>7733.461978491405</v>
       </c>
       <c r="O15">
-        <v>1126.795445448287</v>
+        <v>1129.085448859745</v>
       </c>
       <c r="P15">
-        <v>6590.981578170115</v>
+        <v>6604.37652963166</v>
       </c>
       <c r="Q15">
-        <v>13113.98157817011</v>
+        <v>13127.37652963166</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.09388592265829929</v>
+        <v>0.0938550076853749</v>
       </c>
       <c r="T15">
         <v>1.109815419985564</v>
       </c>
       <c r="U15">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V15">
         <v>0.146</v>
       </c>
       <c r="W15">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>14.32436270368849</v>
+        <v>14.72305271929811</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2566,13 +2566,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.08734174427056775</v>
+        <v>0.08714750427205223</v>
       </c>
       <c r="C16">
-        <v>73415.64329086633</v>
+        <v>73751.89754772243</v>
       </c>
       <c r="D16">
-        <v>82703.99319317607</v>
+        <v>83040.24745003217</v>
       </c>
       <c r="E16">
         <v>-20328.92082847406</v>
@@ -2599,37 +2599,37 @@
         <v>8297</v>
       </c>
       <c r="M16">
-        <v>623.7785899494132</v>
+        <v>606.8871000861795</v>
       </c>
       <c r="N16">
-        <v>7673.221410050587</v>
+        <v>7690.11289991382</v>
       </c>
       <c r="O16">
-        <v>1120.290325867386</v>
+        <v>1122.756483387418</v>
       </c>
       <c r="P16">
-        <v>6552.931084183201</v>
+        <v>6567.356416526402</v>
       </c>
       <c r="Q16">
-        <v>13075.9310841832</v>
+        <v>13090.3564165264</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.09437266543089273</v>
+        <v>0.09434143752564213</v>
       </c>
       <c r="T16">
         <v>1.121049365488271</v>
       </c>
       <c r="U16">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V16">
         <v>0.146</v>
       </c>
       <c r="W16">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>13.30119393913931</v>
+        <v>13.6714060964911</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2648,13 +2648,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.08726300182841511</v>
+        <v>0.08705684585782829</v>
       </c>
       <c r="C17">
-        <v>72710.89584749572</v>
+        <v>73072.56073036067</v>
       </c>
       <c r="D17">
-        <v>82861.05645711329</v>
+        <v>83222.72133997823</v>
       </c>
       <c r="E17">
         <v>-19467.11012116622</v>
@@ -2681,37 +2681,37 @@
         <v>8297</v>
       </c>
       <c r="M17">
-        <v>668.3342035172284</v>
+        <v>650.2361786637637</v>
       </c>
       <c r="N17">
-        <v>7628.665796482772</v>
+        <v>7646.763821336236</v>
       </c>
       <c r="O17">
-        <v>1113.785206286485</v>
+        <v>1116.42751791509</v>
       </c>
       <c r="P17">
-        <v>6514.880590196287</v>
+        <v>6530.336303421145</v>
       </c>
       <c r="Q17">
-        <v>13037.88059019629</v>
+        <v>13053.33630342115</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.09487086097460601</v>
+        <v>0.09483931277391563</v>
       </c>
       <c r="T17">
         <v>1.132547639120454</v>
       </c>
       <c r="U17">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V17">
         <v>0.146</v>
       </c>
       <c r="W17">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>12.41444767653002</v>
+        <v>12.7599790233917</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2730,13 +2730,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.08718425938626248</v>
+        <v>0.08696618744360435</v>
       </c>
       <c r="C18">
-        <v>72006.74609731366</v>
+        <v>72394.02762082452</v>
       </c>
       <c r="D18">
-        <v>83018.71741423907</v>
+        <v>83405.99893774993</v>
       </c>
       <c r="E18">
         <v>-18605.29941385839</v>
@@ -2763,37 +2763,37 @@
         <v>8297</v>
       </c>
       <c r="M18">
-        <v>712.8898170850437</v>
+        <v>693.585257241348</v>
       </c>
       <c r="N18">
-        <v>7584.110182914957</v>
+        <v>7603.414742758652</v>
       </c>
       <c r="O18">
-        <v>1107.280086705584</v>
+        <v>1110.098552442763</v>
       </c>
       <c r="P18">
-        <v>6476.830096209373</v>
+        <v>6493.316190315889</v>
       </c>
       <c r="Q18">
-        <v>12999.83009620937</v>
+        <v>13016.31619031589</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.09538091831697915</v>
+        <v>0.09534904219476709</v>
       </c>
       <c r="T18">
         <v>1.144319681172451</v>
       </c>
       <c r="U18">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V18">
         <v>0.146</v>
       </c>
       <c r="W18">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.6385446967469</v>
+        <v>11.96248033442971</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2812,13 +2812,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.08710551694410985</v>
+        <v>0.08687552902938042</v>
       </c>
       <c r="C19">
-        <v>71303.19745854309</v>
+        <v>71716.30354074064</v>
       </c>
       <c r="D19">
-        <v>83176.97948277634</v>
+        <v>83590.0855649739</v>
       </c>
       <c r="E19">
         <v>-17743.48870655055</v>
@@ -2845,37 +2845,37 @@
         <v>8297</v>
       </c>
       <c r="M19">
-        <v>757.4454306528589</v>
+        <v>736.9343358189323</v>
       </c>
       <c r="N19">
-        <v>7539.554569347141</v>
+        <v>7560.065664181067</v>
       </c>
       <c r="O19">
-        <v>1100.774967124682</v>
+        <v>1103.769586970436</v>
       </c>
       <c r="P19">
-        <v>6438.779602222459</v>
+        <v>6456.296077210632</v>
       </c>
       <c r="Q19">
-        <v>12961.77960222246</v>
+        <v>12979.29607721063</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.09590326619772271</v>
+        <v>0.09587105425226557</v>
       </c>
       <c r="T19">
         <v>1.156375386888351</v>
       </c>
       <c r="U19">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V19">
         <v>0.146</v>
       </c>
       <c r="W19">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>10.95392442046767</v>
+        <v>11.25880502063973</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2894,13 +2894,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.08702677450195723</v>
+        <v>0.08678487061515648</v>
       </c>
       <c r="C20">
-        <v>70600.2533755219</v>
+        <v>71039.39385882148</v>
       </c>
       <c r="D20">
-        <v>83335.84610706299</v>
+        <v>83774.98659036256</v>
       </c>
       <c r="E20">
         <v>-16881.67799924271</v>
@@ -2927,37 +2927,37 @@
         <v>8297</v>
       </c>
       <c r="M20">
-        <v>802.0010442206741</v>
+        <v>780.2834143965165</v>
       </c>
       <c r="N20">
-        <v>7494.998955779326</v>
+        <v>7516.716585603484</v>
       </c>
       <c r="O20">
-        <v>1094.269847543781</v>
+        <v>1097.440621498109</v>
       </c>
       <c r="P20">
-        <v>6400.729108235544</v>
+        <v>6419.275964105374</v>
       </c>
       <c r="Q20">
-        <v>12923.72910823554</v>
+        <v>12942.27596410537</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.09643835427067954</v>
+        <v>0.09640579831116644</v>
       </c>
       <c r="T20">
         <v>1.168725134207078</v>
       </c>
       <c r="U20">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V20">
         <v>0.146</v>
       </c>
       <c r="W20">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>10.34537306377502</v>
+        <v>10.63331585282641</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2976,13 +2976,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.08694803205980461</v>
+        <v>0.08669421220093257</v>
       </c>
       <c r="C21">
-        <v>69897.91731895281</v>
+        <v>70363.30399138689</v>
       </c>
       <c r="D21">
-        <v>83495.32075780173</v>
+        <v>83960.70743023581</v>
       </c>
       <c r="E21">
         <v>-16019.86729193487</v>
@@ -3009,37 +3009,37 @@
         <v>8297</v>
       </c>
       <c r="M21">
-        <v>846.5566577884892</v>
+        <v>823.6324929741007</v>
       </c>
       <c r="N21">
-        <v>7450.443342211511</v>
+        <v>7473.3675070259</v>
       </c>
       <c r="O21">
-        <v>1087.76472796288</v>
+        <v>1091.111656025781</v>
       </c>
       <c r="P21">
-        <v>6362.678614248631</v>
+        <v>6382.255851000118</v>
       </c>
       <c r="Q21">
-        <v>12885.67861424863</v>
+        <v>12905.25585100012</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.09698665439482049</v>
+        <v>0.09695374592707723</v>
       </c>
       <c r="T21">
         <v>1.181379813558366</v>
       </c>
       <c r="U21">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V21">
         <v>0.146</v>
       </c>
       <c r="W21">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>9.800879744628967</v>
+        <v>10.07366765004608</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3058,13 +3058,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.08686928961765197</v>
+        <v>0.08660355378670864</v>
       </c>
       <c r="C22">
-        <v>69196.19278615629</v>
+        <v>69688.03940289341</v>
       </c>
       <c r="D22">
-        <v>83655.40693231305</v>
+        <v>84147.25354905018</v>
       </c>
       <c r="E22">
         <v>-15158.05658462703</v>
@@ -3091,37 +3091,37 @@
         <v>8297</v>
       </c>
       <c r="M22">
-        <v>891.1122713563046</v>
+        <v>866.9815715516851</v>
       </c>
       <c r="N22">
-        <v>7405.887728643695</v>
+        <v>7430.018428448315</v>
       </c>
       <c r="O22">
-        <v>1081.259608381979</v>
+        <v>1084.782690553454</v>
       </c>
       <c r="P22">
-        <v>6324.628120261716</v>
+        <v>6345.235737894861</v>
       </c>
       <c r="Q22">
-        <v>12847.62812026172</v>
+        <v>12868.23573789486</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.09754866202206497</v>
+        <v>0.09751539223338579</v>
       </c>
       <c r="T22">
         <v>1.194350859893436</v>
       </c>
       <c r="U22">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V22">
         <v>0.146</v>
       </c>
       <c r="W22">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>9.310835757397516</v>
+        <v>9.56998426754377</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3140,13 +3140,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.08679054717549932</v>
+        <v>0.08651289537248469</v>
       </c>
       <c r="C23">
-        <v>68495.08330132595</v>
+        <v>69013.60560647004</v>
       </c>
       <c r="D23">
-        <v>83816.10815479055</v>
+        <v>84334.63045993463</v>
       </c>
       <c r="E23">
         <v>-14296.2458773192</v>
@@ -3173,37 +3173,37 @@
         <v>8297</v>
       </c>
       <c r="M23">
-        <v>935.6678849241198</v>
+        <v>910.3306501292692</v>
       </c>
       <c r="N23">
-        <v>7361.33211507588</v>
+        <v>7386.669349870731</v>
       </c>
       <c r="O23">
-        <v>1074.754488801078</v>
+        <v>1078.453725081127</v>
       </c>
       <c r="P23">
-        <v>6286.577626274802</v>
+        <v>6308.215624789605</v>
       </c>
       <c r="Q23">
-        <v>12809.5776262748</v>
+        <v>12831.21562478961</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.09812489769050547</v>
+        <v>0.09809125743352493</v>
       </c>
       <c r="T23">
         <v>1.207650287148382</v>
       </c>
       <c r="U23">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V23">
         <v>0.146</v>
       </c>
       <c r="W23">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.867462626092873</v>
+        <v>9.114270730994068</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3222,13 +3222,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.08691847273334671</v>
+        <v>0.08670405695826076</v>
       </c>
       <c r="C24">
-        <v>67372.50847318531</v>
+        <v>67757.66427023678</v>
       </c>
       <c r="D24">
-        <v>83555.34403395775</v>
+        <v>83940.49983100922</v>
       </c>
       <c r="E24">
         <v>-13434.43517001136</v>
@@ -3255,37 +3255,37 @@
         <v>8297</v>
       </c>
       <c r="M24">
-        <v>1001.079317608785</v>
+        <v>982.1194820480122</v>
       </c>
       <c r="N24">
-        <v>7295.920682391215</v>
+        <v>7314.880517951988</v>
       </c>
       <c r="O24">
-        <v>1065.204419629117</v>
+        <v>1067.97255562099</v>
       </c>
       <c r="P24">
-        <v>6230.716262762098</v>
+        <v>6246.907962330997</v>
       </c>
       <c r="Q24">
-        <v>12753.7162627621</v>
+        <v>12769.907962331</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.0987159086324958</v>
+        <v>0.09868188840802661</v>
       </c>
       <c r="T24">
         <v>1.221290725358583</v>
       </c>
       <c r="U24">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V24">
         <v>0.146</v>
       </c>
       <c r="W24">
-        <v>0.0450912</v>
+        <v>0.0442372</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.288054556774306</v>
+        <v>8.448055609993887</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3304,13 +3304,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.08684912429119408</v>
+        <v>0.08662620854403683</v>
       </c>
       <c r="C25">
-        <v>66651.85626906934</v>
+        <v>67055.91336358273</v>
       </c>
       <c r="D25">
-        <v>83696.50253714962</v>
+        <v>84100.55963166301</v>
       </c>
       <c r="E25">
         <v>-12572.62446270352</v>
@@ -3337,37 +3337,37 @@
         <v>8297</v>
       </c>
       <c r="M25">
-        <v>1046.582922954639</v>
+        <v>1026.761276686558</v>
       </c>
       <c r="N25">
-        <v>7250.417077045361</v>
+        <v>7270.238723313441</v>
       </c>
       <c r="O25">
-        <v>1058.560893248623</v>
+        <v>1061.454853603762</v>
       </c>
       <c r="P25">
-        <v>6191.856183796738</v>
+        <v>6208.783869709679</v>
       </c>
       <c r="Q25">
-        <v>12714.85618379674</v>
+        <v>12731.78386970968</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.09932227050804426</v>
+        <v>0.09928786044680106</v>
       </c>
       <c r="T25">
         <v>1.235285460665152</v>
       </c>
       <c r="U25">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V25">
         <v>0.146</v>
       </c>
       <c r="W25">
-        <v>0.0450912</v>
+        <v>0.0442372</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>7.927704358653682</v>
+        <v>8.080748844341979</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3386,13 +3386,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.08677977584904145</v>
+        <v>0.0865483601298129</v>
       </c>
       <c r="C26">
-        <v>65931.68181877659</v>
+        <v>66354.77403499573</v>
       </c>
       <c r="D26">
-        <v>83838.1387941647</v>
+        <v>84261.23101038384</v>
       </c>
       <c r="E26">
         <v>-11710.81375539568</v>
@@ -3419,37 +3419,37 @@
         <v>8297</v>
       </c>
       <c r="M26">
-        <v>1092.086528300492</v>
+        <v>1071.403071325104</v>
       </c>
       <c r="N26">
-        <v>7204.913471699508</v>
+        <v>7225.596928674896</v>
       </c>
       <c r="O26">
-        <v>1051.917366868128</v>
+        <v>1054.937151586535</v>
       </c>
       <c r="P26">
-        <v>6152.99610483138</v>
+        <v>6170.659777088361</v>
       </c>
       <c r="Q26">
-        <v>12675.99610483138</v>
+        <v>12693.65977708836</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.09994458927505454</v>
+        <v>0.09990977911817486</v>
       </c>
       <c r="T26">
         <v>1.249648478479789</v>
       </c>
       <c r="U26">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V26">
         <v>0.146</v>
       </c>
       <c r="W26">
-        <v>0.0450912</v>
+        <v>0.0442372</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.59738334370978</v>
+        <v>7.744050975827731</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3468,13 +3468,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.08671042740688883</v>
+        <v>0.08647051171558895</v>
       </c>
       <c r="C27">
-        <v>65211.98755186974</v>
+        <v>65654.24979638511</v>
       </c>
       <c r="D27">
-        <v>83980.25523456569</v>
+        <v>84422.51747908106</v>
       </c>
       <c r="E27">
         <v>-10849.00304808784</v>
@@ -3501,37 +3501,37 @@
         <v>8297</v>
       </c>
       <c r="M27">
-        <v>1137.590133646346</v>
+        <v>1116.04486596365</v>
       </c>
       <c r="N27">
-        <v>7159.409866353653</v>
+        <v>7180.95513403635</v>
       </c>
       <c r="O27">
-        <v>1045.273840487633</v>
+        <v>1048.419449569307</v>
       </c>
       <c r="P27">
-        <v>6114.13602586602</v>
+        <v>6132.535684467042</v>
       </c>
       <c r="Q27">
-        <v>12637.13602586602</v>
+        <v>12655.53568446704</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.1005835032091851</v>
+        <v>0.1005482822874519</v>
       </c>
       <c r="T27">
         <v>1.264394510102817</v>
       </c>
       <c r="U27">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V27">
         <v>0.146</v>
       </c>
       <c r="W27">
-        <v>0.0450912</v>
+        <v>0.0442372</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.293488009961388</v>
+        <v>7.434288936794621</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3550,13 +3550,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.08664107896473619</v>
+        <v>0.08639266330136502</v>
       </c>
       <c r="C28">
-        <v>64492.77591441329</v>
+        <v>64954.34418660056</v>
       </c>
       <c r="D28">
-        <v>84122.85430441708</v>
+        <v>84584.42257660435</v>
       </c>
       <c r="E28">
         <v>-9987.192340780006</v>
@@ -3583,37 +3583,37 @@
         <v>8297</v>
       </c>
       <c r="M28">
-        <v>1183.0937389922</v>
+        <v>1160.686660602196</v>
       </c>
       <c r="N28">
-        <v>7113.9062610078</v>
+        <v>7136.313339397804</v>
       </c>
       <c r="O28">
-        <v>1038.630314107139</v>
+        <v>1041.901747552079</v>
       </c>
       <c r="P28">
-        <v>6075.275946900661</v>
+        <v>6094.411591845725</v>
       </c>
       <c r="Q28">
-        <v>12598.27594690066</v>
+        <v>12617.41159184572</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.1012396850874814</v>
+        <v>0.1012040422991419</v>
       </c>
       <c r="T28">
         <v>1.279539083121061</v>
       </c>
       <c r="U28">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V28">
         <v>0.146</v>
       </c>
       <c r="W28">
-        <v>0.0450912</v>
+        <v>0.0442372</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.012969240347489</v>
+        <v>7.148354746917905</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3632,13 +3632,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.08707900652258356</v>
+        <v>0.0863148148871411</v>
       </c>
       <c r="C29">
-        <v>62738.50874441106</v>
+        <v>64255.06077169126</v>
       </c>
       <c r="D29">
-        <v>83230.39784172269</v>
+        <v>84746.94986900288</v>
       </c>
       <c r="E29">
         <v>-9125.381633472167</v>
@@ -3665,45 +3665,45 @@
         <v>8297</v>
       </c>
       <c r="M29">
-        <v>1279.78890035214</v>
+        <v>1205.328455240742</v>
       </c>
       <c r="N29">
-        <v>7017.21109964786</v>
+        <v>7091.671544759258</v>
       </c>
       <c r="O29">
-        <v>1024.512820548588</v>
+        <v>1035.384045534852</v>
       </c>
       <c r="P29">
-        <v>5992.698279099273</v>
+        <v>6056.287499224406</v>
       </c>
       <c r="Q29">
-        <v>12515.69827909927</v>
+        <v>12579.28749922441</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.1019138445514843</v>
+        <v>0.1018777683385494</v>
       </c>
       <c r="T29">
         <v>1.295098575948024</v>
       </c>
       <c r="U29">
-        <v>0.055</v>
+        <v>0.0518</v>
       </c>
       <c r="V29">
         <v>0.146</v>
       </c>
       <c r="W29">
-        <v>0.04697</v>
+        <v>0.0442372</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y29">
-        <v>6.483100453299012</v>
+        <v>6.883600867402426</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3714,13 +3714,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.08702844608043094</v>
+        <v>0.08664347047291716</v>
       </c>
       <c r="C30">
-        <v>61978.76750892389</v>
+        <v>62711.3158866695</v>
       </c>
       <c r="D30">
-        <v>83332.46731354335</v>
+        <v>84065.01569128897</v>
       </c>
       <c r="E30">
         <v>-8263.570926164328</v>
@@ -3747,37 +3747,37 @@
         <v>8297</v>
       </c>
       <c r="M30">
-        <v>1327.188489254071</v>
+        <v>1290.992439547141</v>
       </c>
       <c r="N30">
-        <v>6969.811510745929</v>
+        <v>7006.007560452858</v>
       </c>
       <c r="O30">
-        <v>1017.592480568906</v>
+        <v>1022.877103826117</v>
       </c>
       <c r="P30">
-        <v>5952.219030177023</v>
+        <v>5983.130456626741</v>
       </c>
       <c r="Q30">
-        <v>12475.21903017702</v>
+        <v>12506.13045662674</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.1026067306672652</v>
+        <v>0.1025702089901627</v>
       </c>
       <c r="T30">
         <v>1.31109027690907</v>
       </c>
       <c r="U30">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V30">
         <v>0.146</v>
       </c>
       <c r="W30">
-        <v>0.04697</v>
+        <v>0.045689</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.251561151395475</v>
+        <v>6.426838566855162</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3796,13 +3796,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.08697788563827831</v>
+        <v>0.08658014005869322</v>
       </c>
       <c r="C31">
-        <v>61219.27692630758</v>
+        <v>61980.05579193458</v>
       </c>
       <c r="D31">
-        <v>83434.78743823488</v>
+        <v>84195.56630386188</v>
       </c>
       <c r="E31">
         <v>-7401.760218856496</v>
@@ -3829,37 +3829,37 @@
         <v>8297</v>
       </c>
       <c r="M31">
-        <v>1374.588078156002</v>
+        <v>1337.099312388111</v>
       </c>
       <c r="N31">
-        <v>6922.411921843998</v>
+        <v>6959.900687611889</v>
       </c>
       <c r="O31">
-        <v>1010.672140589224</v>
+        <v>1016.145500391336</v>
       </c>
       <c r="P31">
-        <v>5911.739781254774</v>
+        <v>5943.755187220553</v>
       </c>
       <c r="Q31">
-        <v>12434.73978125478</v>
+        <v>12466.75518722055</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.1033191347018004</v>
+        <v>0.103282155012244</v>
       </c>
       <c r="T31">
         <v>1.327532448319723</v>
       </c>
       <c r="U31">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V31">
         <v>0.146</v>
       </c>
       <c r="W31">
-        <v>0.04697</v>
+        <v>0.045689</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.035990077209425</v>
+        <v>6.205223443860158</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3878,13 +3878,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.08692732519612567</v>
+        <v>0.08651680964446928</v>
       </c>
       <c r="C32">
-        <v>60460.03792099279</v>
+        <v>61249.2018107652</v>
       </c>
       <c r="D32">
-        <v>83537.35914022793</v>
+        <v>84326.52303000033</v>
       </c>
       <c r="E32">
         <v>-6539.949511548657</v>
@@ -3911,37 +3911,37 @@
         <v>8297</v>
       </c>
       <c r="M32">
-        <v>1421.987667057933</v>
+        <v>1383.20618522908</v>
       </c>
       <c r="N32">
-        <v>6875.012332942068</v>
+        <v>6913.79381477092</v>
       </c>
       <c r="O32">
-        <v>1003.751800609542</v>
+        <v>1009.413896956554</v>
       </c>
       <c r="P32">
-        <v>5871.260532332526</v>
+        <v>5904.379917814365</v>
       </c>
       <c r="Q32">
-        <v>12394.26053233253</v>
+        <v>12427.37991781437</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1040518931373224</v>
+        <v>0.1040144423492418</v>
       </c>
       <c r="T32">
         <v>1.344444396056394</v>
       </c>
       <c r="U32">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V32">
         <v>0.146</v>
       </c>
       <c r="W32">
-        <v>0.04697</v>
+        <v>0.045689</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.834790407969112</v>
+        <v>5.998382662398153</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3960,13 +3960,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.08727387475397305</v>
+        <v>0.08645347923024535</v>
       </c>
       <c r="C33">
-        <v>58900.20140718589</v>
+        <v>60518.75584110523</v>
       </c>
       <c r="D33">
-        <v>82839.33333372886</v>
+        <v>84457.88776764821</v>
       </c>
       <c r="E33">
         <v>-5678.138804240818</v>
@@ -3993,45 +3993,45 @@
         <v>8297</v>
       </c>
       <c r="M33">
-        <v>1509.461453849678</v>
+        <v>1429.313058070049</v>
       </c>
       <c r="N33">
-        <v>6787.538546150322</v>
+        <v>6867.686941929951</v>
       </c>
       <c r="O33">
-        <v>990.980627737947</v>
+        <v>1002.682293521773</v>
       </c>
       <c r="P33">
-        <v>5796.557918412375</v>
+        <v>5865.004648408179</v>
       </c>
       <c r="Q33">
-        <v>12319.55791841237</v>
+        <v>12388.00464840818</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.104805890947787</v>
+        <v>0.1047679554061527</v>
       </c>
       <c r="T33">
         <v>1.361846545176737</v>
       </c>
       <c r="U33">
-        <v>0.0565</v>
+        <v>0.0535</v>
       </c>
       <c r="V33">
         <v>0.146</v>
       </c>
       <c r="W33">
-        <v>0.048251</v>
+        <v>0.045689</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>5.496662388323742</v>
+        <v>5.804886447482083</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4042,13 +4042,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.08723612431182043</v>
+        <v>0.08639014881602142</v>
       </c>
       <c r="C34">
-        <v>58113.86159665987</v>
+        <v>59788.71979274352</v>
       </c>
       <c r="D34">
-        <v>82914.80423051069</v>
+        <v>84589.66242659434</v>
       </c>
       <c r="E34">
         <v>-4816.328096932979</v>
@@ -4075,45 +4075,45 @@
         <v>8297</v>
       </c>
       <c r="M34">
-        <v>1558.153758812571</v>
+        <v>1475.419930911019</v>
       </c>
       <c r="N34">
-        <v>6738.846241187429</v>
+        <v>6821.580069088981</v>
       </c>
       <c r="O34">
-        <v>983.8715512133646</v>
+        <v>995.9506900869911</v>
       </c>
       <c r="P34">
-        <v>5754.974689974064</v>
+        <v>5825.62937900199</v>
       </c>
       <c r="Q34">
-        <v>12277.97468997406</v>
+        <v>12348.62937900199</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1055820651644418</v>
+        <v>0.1055436306117962</v>
       </c>
       <c r="T34">
         <v>1.379760522212384</v>
       </c>
       <c r="U34">
-        <v>0.0565</v>
+        <v>0.0535</v>
       </c>
       <c r="V34">
         <v>0.146</v>
       </c>
       <c r="W34">
-        <v>0.048251</v>
+        <v>0.045689</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y34">
-        <v>5.324891688688624</v>
+        <v>5.623483745998267</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4124,13 +4124,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.08719837386966779</v>
+        <v>0.0865522744017975</v>
       </c>
       <c r="C35">
-        <v>57327.65942727566</v>
+        <v>58590.38434484578</v>
       </c>
       <c r="D35">
-        <v>82990.41276843431</v>
+        <v>84253.13768600444</v>
       </c>
       <c r="E35">
         <v>-3954.51738962514</v>
@@ -4157,37 +4157,37 @@
         <v>8297</v>
       </c>
       <c r="M35">
-        <v>1606.846063775464</v>
+        <v>1544.278606424915</v>
       </c>
       <c r="N35">
-        <v>6690.153936224536</v>
+        <v>6752.721393575085</v>
       </c>
       <c r="O35">
-        <v>976.7624746887822</v>
+        <v>985.8973234619624</v>
       </c>
       <c r="P35">
-        <v>5713.391461535753</v>
+        <v>5766.824070113123</v>
       </c>
       <c r="Q35">
-        <v>12236.39146153575</v>
+        <v>12289.82407011312</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1063814087606982</v>
+        <v>0.1063424603011903</v>
       </c>
       <c r="T35">
         <v>1.398209244831185</v>
       </c>
       <c r="U35">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V35">
         <v>0.146</v>
       </c>
       <c r="W35">
-        <v>0.048251</v>
+        <v>0.0463722</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.163531334485939</v>
+        <v>5.372735182291999</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4206,13 +4206,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.08716062342751517</v>
+        <v>0.08649577598757355</v>
       </c>
       <c r="C36">
-        <v>56541.5952759144</v>
+        <v>57845.54323836595</v>
       </c>
       <c r="D36">
-        <v>83066.15932438089</v>
+        <v>84370.10728683244</v>
       </c>
       <c r="E36">
         <v>-3092.706682317301</v>
@@ -4239,37 +4239,37 @@
         <v>8297</v>
       </c>
       <c r="M36">
-        <v>1655.538368738357</v>
+        <v>1591.074927831731</v>
       </c>
       <c r="N36">
-        <v>6641.461631261644</v>
+        <v>6705.925072168269</v>
       </c>
       <c r="O36">
-        <v>969.6533981641999</v>
+        <v>979.0650605365672</v>
       </c>
       <c r="P36">
-        <v>5671.808233097444</v>
+        <v>5726.860011631702</v>
       </c>
       <c r="Q36">
-        <v>12194.80823309744</v>
+        <v>12249.8600116317</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1072049748901745</v>
+        <v>0.107165496950869</v>
       </c>
       <c r="T36">
         <v>1.417217019650555</v>
       </c>
       <c r="U36">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V36">
         <v>0.146</v>
       </c>
       <c r="W36">
-        <v>0.048251</v>
+        <v>0.0463722</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.011662765824588</v>
+        <v>5.21471355928341</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4288,13 +4288,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.08712287298536253</v>
+        <v>0.08643927757334963</v>
       </c>
       <c r="C37">
-        <v>55755.66952083452</v>
+        <v>57101.02736389573</v>
       </c>
       <c r="D37">
-        <v>83142.04427660885</v>
+        <v>84487.40211967006</v>
       </c>
       <c r="E37">
         <v>-2230.895975009462</v>
@@ -4321,37 +4321,37 @@
         <v>8297</v>
       </c>
       <c r="M37">
-        <v>1704.23067370125</v>
+        <v>1637.871249238546</v>
       </c>
       <c r="N37">
-        <v>6592.76932629875</v>
+        <v>6659.128750761453</v>
       </c>
       <c r="O37">
-        <v>962.5443216396175</v>
+        <v>972.2327976111721</v>
       </c>
       <c r="P37">
-        <v>5630.225004659133</v>
+        <v>5686.895953150281</v>
       </c>
       <c r="Q37">
-        <v>12153.22500465913</v>
+        <v>12209.89595315028</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1080538815159424</v>
+        <v>0.1080138578051533</v>
       </c>
       <c r="T37">
         <v>1.436809649079753</v>
       </c>
       <c r="U37">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V37">
         <v>0.146</v>
       </c>
       <c r="W37">
-        <v>0.048251</v>
+        <v>0.0463722</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.868472401086742</v>
+        <v>5.065721743303884</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4370,13 +4370,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.08708512254320992</v>
+        <v>0.08638277915912569</v>
       </c>
       <c r="C38">
-        <v>54969.88254167788</v>
+        <v>56356.8380797769</v>
       </c>
       <c r="D38">
-        <v>83218.06800476005</v>
+        <v>84605.02354285907</v>
       </c>
       <c r="E38">
         <v>-1369.085267701626</v>
@@ -4403,37 +4403,37 @@
         <v>8297</v>
       </c>
       <c r="M38">
-        <v>1752.922978664143</v>
+        <v>1684.667570645362</v>
       </c>
       <c r="N38">
-        <v>6544.077021335857</v>
+        <v>6612.332429354638</v>
       </c>
       <c r="O38">
-        <v>955.4352451150351</v>
+        <v>965.4005346857772</v>
       </c>
       <c r="P38">
-        <v>5588.641776220822</v>
+        <v>5646.931894668861</v>
       </c>
       <c r="Q38">
-        <v>12111.64177622082</v>
+        <v>12169.93189466886</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1089293164737655</v>
+        <v>0.1088887299361339</v>
       </c>
       <c r="T38">
         <v>1.457014548178612</v>
       </c>
       <c r="U38">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V38">
         <v>0.146</v>
       </c>
       <c r="W38">
-        <v>0.048251</v>
+        <v>0.0463722</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.73323705661211</v>
+        <v>4.925007250434333</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4452,13 +4452,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.08704737210105729</v>
+        <v>0.08632628074490176</v>
       </c>
       <c r="C39">
-        <v>54184.2347194763</v>
+        <v>55612.97675192577</v>
       </c>
       <c r="D39">
-        <v>83294.2308898663</v>
+        <v>84722.97292231578</v>
       </c>
       <c r="E39">
         <v>-507.2745603937874</v>
@@ -4485,37 +4485,37 @@
         <v>8297</v>
       </c>
       <c r="M39">
-        <v>1801.615283627036</v>
+        <v>1731.463892052177</v>
       </c>
       <c r="N39">
-        <v>6495.384716372964</v>
+        <v>6565.536107947823</v>
       </c>
       <c r="O39">
-        <v>948.3261685904528</v>
+        <v>958.568271760382</v>
       </c>
       <c r="P39">
-        <v>5547.058547782512</v>
+        <v>5606.96783618744</v>
       </c>
       <c r="Q39">
-        <v>12070.05854778251</v>
+        <v>12129.96783618744</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1098325430175512</v>
+        <v>0.1097913757855583</v>
       </c>
       <c r="T39">
         <v>1.47786087264569</v>
       </c>
       <c r="U39">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V39">
         <v>0.146</v>
       </c>
       <c r="W39">
-        <v>0.048251</v>
+        <v>0.0463722</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.605311730757728</v>
+        <v>4.79189894636854</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4534,13 +4534,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.08700962165890466</v>
+        <v>0.08626978233067782</v>
       </c>
       <c r="C40">
-        <v>53398.72643665761</v>
+        <v>54869.4447538864</v>
       </c>
       <c r="D40">
-        <v>83370.53331435546</v>
+        <v>84841.25163158425</v>
       </c>
       <c r="E40">
         <v>354.536146914048</v>
@@ -4567,37 +4567,37 @@
         <v>8297</v>
       </c>
       <c r="M40">
-        <v>1850.307588589928</v>
+        <v>1778.260213458993</v>
       </c>
       <c r="N40">
-        <v>6446.692411410072</v>
+        <v>6518.739786541008</v>
       </c>
       <c r="O40">
-        <v>941.2170920658705</v>
+        <v>951.736008834987</v>
       </c>
       <c r="P40">
-        <v>5505.475319344201</v>
+        <v>5567.003777706021</v>
       </c>
       <c r="Q40">
-        <v>12028.4753193442</v>
+        <v>12090.00377770602</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1107649059014591</v>
+        <v>0.1107231392430287</v>
       </c>
       <c r="T40">
         <v>1.49937965919235</v>
       </c>
       <c r="U40">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V40">
         <v>0.146</v>
       </c>
       <c r="W40">
-        <v>0.048251</v>
+        <v>0.0463722</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.484119316790421</v>
+        <v>4.665796342516737</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4616,13 +4616,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.08697187121675203</v>
+        <v>0.0862132839164539</v>
       </c>
       <c r="C41">
-        <v>52613.35807705238</v>
+        <v>54126.2434668837</v>
       </c>
       <c r="D41">
-        <v>83446.97566205806</v>
+        <v>84959.86105188938</v>
       </c>
       <c r="E41">
         <v>1216.346854221887</v>
@@ -4649,37 +4649,37 @@
         <v>8297</v>
       </c>
       <c r="M41">
-        <v>1898.999893552821</v>
+        <v>1825.056534865809</v>
       </c>
       <c r="N41">
-        <v>6398.000106447179</v>
+        <v>6471.943465134192</v>
       </c>
       <c r="O41">
-        <v>934.1080155412881</v>
+        <v>944.903745909592</v>
       </c>
       <c r="P41">
-        <v>5463.892090905891</v>
+        <v>5527.0397192246</v>
       </c>
       <c r="Q41">
-        <v>11986.89209090589</v>
+        <v>12050.0397192246</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1117278380602492</v>
+        <v>0.1116854523220556</v>
       </c>
       <c r="T41">
         <v>1.521603979724147</v>
       </c>
       <c r="U41">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V41">
         <v>0.146</v>
       </c>
       <c r="W41">
-        <v>0.048251</v>
+        <v>0.0463722</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.369141898411179</v>
+        <v>4.546160538862461</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4698,13 +4698,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.08693412077459939</v>
+        <v>0.08615678550222997</v>
       </c>
       <c r="C42">
-        <v>51828.13002590012</v>
+        <v>53383.37427987738</v>
       </c>
       <c r="D42">
-        <v>83523.55831821365</v>
+        <v>85078.80257219091</v>
       </c>
       <c r="E42">
         <v>2078.15756152973</v>
@@ -4731,37 +4731,37 @@
         <v>8297</v>
       </c>
       <c r="M42">
-        <v>1947.692198515714</v>
+        <v>1871.852856272624</v>
       </c>
       <c r="N42">
-        <v>6349.307801484286</v>
+        <v>6425.147143727376</v>
       </c>
       <c r="O42">
-        <v>926.9989390167057</v>
+        <v>938.0714829841968</v>
       </c>
       <c r="P42">
-        <v>5422.30886246758</v>
+        <v>5487.075660743179</v>
       </c>
       <c r="Q42">
-        <v>11945.30886246758</v>
+        <v>12010.07566074318</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1127228679576656</v>
+        <v>0.1126798425037166</v>
       </c>
       <c r="T42">
         <v>1.544569110940337</v>
       </c>
       <c r="U42">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V42">
         <v>0.146</v>
       </c>
       <c r="W42">
-        <v>0.048251</v>
+        <v>0.0463722</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.2599133509509</v>
+        <v>4.432506525390899</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4780,13 +4780,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.08738656633244676</v>
+        <v>0.08610028708800602</v>
       </c>
       <c r="C43">
-        <v>50057.61570900388</v>
+        <v>52640.83858961605</v>
       </c>
       <c r="D43">
-        <v>82614.85470862524</v>
+        <v>85198.07758923741</v>
       </c>
       <c r="E43">
         <v>2939.968268837565</v>
@@ -4813,45 +4813,45 @@
         <v>8297</v>
       </c>
       <c r="M43">
-        <v>2045.852438078077</v>
+        <v>1918.64917767944</v>
       </c>
       <c r="N43">
-        <v>6251.147561921924</v>
+        <v>6378.35082232056</v>
       </c>
       <c r="O43">
-        <v>912.6675440406008</v>
+        <v>931.2392200588017</v>
       </c>
       <c r="P43">
-        <v>5338.480017881323</v>
+        <v>5447.111602261758</v>
       </c>
       <c r="Q43">
-        <v>11861.48001788132</v>
+        <v>11970.11160226176</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1137516276821132</v>
+        <v>0.1137079408271288</v>
       </c>
       <c r="T43">
         <v>1.568312721180805</v>
       </c>
       <c r="U43">
-        <v>0.0579</v>
+        <v>0.0543</v>
       </c>
       <c r="V43">
         <v>0.146</v>
       </c>
       <c r="W43">
-        <v>0.0494466</v>
+        <v>0.0463722</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y43">
-        <v>4.055522209507155</v>
+        <v>4.324396610137462</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4862,13 +4862,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.08736077189029413</v>
+        <v>0.0864024686737821</v>
       </c>
       <c r="C44">
-        <v>49247.07941248791</v>
+        <v>51144.94598945983</v>
       </c>
       <c r="D44">
-        <v>82666.12911941711</v>
+        <v>84563.99569638903</v>
       </c>
       <c r="E44">
         <v>3801.778976145401</v>
@@ -4895,37 +4895,37 @@
         <v>8297</v>
       </c>
       <c r="M44">
-        <v>2095.7512780312</v>
+        <v>2001.641548793185</v>
       </c>
       <c r="N44">
-        <v>6201.248721968799</v>
+        <v>6295.358451206816</v>
       </c>
       <c r="O44">
-        <v>905.3823134074446</v>
+        <v>919.1223338761951</v>
       </c>
       <c r="P44">
-        <v>5295.866408561355</v>
+        <v>5376.236117330621</v>
       </c>
       <c r="Q44">
-        <v>11818.86640856135</v>
+        <v>11899.23611733062</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1148158618798175</v>
+        <v>0.1147714908168657</v>
       </c>
       <c r="T44">
         <v>1.592875076601979</v>
       </c>
       <c r="U44">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V44">
         <v>0.146</v>
       </c>
       <c r="W44">
-        <v>0.0494466</v>
+        <v>0.0472262</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.958962156899841</v>
+        <v>4.145097809846307</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4944,13 +4944,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.08733497744814152</v>
+        <v>0.08635451025955816</v>
       </c>
       <c r="C45">
-        <v>48436.6068018051</v>
+        <v>50383.13784926677</v>
       </c>
       <c r="D45">
-        <v>82717.46721604213</v>
+        <v>84663.9982635038</v>
       </c>
       <c r="E45">
         <v>4663.589683453236</v>
@@ -4977,37 +4977,37 @@
         <v>8297</v>
       </c>
       <c r="M45">
-        <v>2145.650117984324</v>
+        <v>2049.299680907308</v>
       </c>
       <c r="N45">
-        <v>6151.349882015676</v>
+        <v>6247.700319092692</v>
       </c>
       <c r="O45">
-        <v>898.0970827742888</v>
+        <v>912.1642465875329</v>
       </c>
       <c r="P45">
-        <v>5253.252799241388</v>
+        <v>5335.536072505159</v>
       </c>
       <c r="Q45">
-        <v>11776.25279924139</v>
+        <v>11858.53607250516</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1159174376283184</v>
+        <v>0.115872358350102</v>
       </c>
       <c r="T45">
         <v>1.618299269055474</v>
       </c>
       <c r="U45">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V45">
         <v>0.146</v>
       </c>
       <c r="W45">
-        <v>0.0494466</v>
+        <v>0.0472262</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.866893269530078</v>
+        <v>4.04870018636151</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5026,13 +5026,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.08730918300598889</v>
+        <v>0.08630655184533423</v>
       </c>
       <c r="C46">
-        <v>47626.19799568159</v>
+        <v>49621.56650852063</v>
       </c>
       <c r="D46">
-        <v>82768.86911722647</v>
+        <v>84764.2376300655</v>
       </c>
       <c r="E46">
         <v>5525.400390761079</v>
@@ -5059,37 +5059,37 @@
         <v>8297</v>
       </c>
       <c r="M46">
-        <v>2195.548957937448</v>
+        <v>2096.957813021432</v>
       </c>
       <c r="N46">
-        <v>6101.451042062552</v>
+        <v>6200.042186978568</v>
       </c>
       <c r="O46">
-        <v>890.8118521411326</v>
+        <v>905.2061592988708</v>
       </c>
       <c r="P46">
-        <v>5210.63918992142</v>
+        <v>5294.836027679697</v>
       </c>
       <c r="Q46">
-        <v>11733.63918992142</v>
+        <v>11817.8360276797</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1170583553678373</v>
+        <v>0.1170125425809539</v>
       </c>
       <c r="T46">
         <v>1.644631468382309</v>
       </c>
       <c r="U46">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V46">
         <v>0.146</v>
       </c>
       <c r="W46">
-        <v>0.0494466</v>
+        <v>0.0472262</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.779009331586212</v>
+        <v>3.956684273035111</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5108,13 +5108,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.08728338856383624</v>
+        <v>0.08625859343111029</v>
       </c>
       <c r="C47">
-        <v>46815.85311313874</v>
+        <v>48860.23280930652</v>
       </c>
       <c r="D47">
-        <v>82820.33494199144</v>
+        <v>84864.71463815923</v>
       </c>
       <c r="E47">
         <v>6387.211098068914</v>
@@ -5141,37 +5141,37 @@
         <v>8297</v>
       </c>
       <c r="M47">
-        <v>2245.447797890572</v>
+        <v>2144.615945135555</v>
       </c>
       <c r="N47">
-        <v>6051.552202109428</v>
+        <v>6152.384054864446</v>
       </c>
       <c r="O47">
-        <v>883.5266215079764</v>
+        <v>898.2480720102091</v>
       </c>
       <c r="P47">
-        <v>5168.025580601451</v>
+        <v>5254.135982854236</v>
       </c>
       <c r="Q47">
-        <v>11691.02558060145</v>
+        <v>11777.13598285424</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1182407610251568</v>
+        <v>0.1181941880565641</v>
       </c>
       <c r="T47">
         <v>1.67192120223012</v>
       </c>
       <c r="U47">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V47">
         <v>0.146</v>
       </c>
       <c r="W47">
-        <v>0.0494466</v>
+        <v>0.0472262</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.695031346439851</v>
+        <v>3.868757955856554</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5190,13 +5190,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.08725759412168363</v>
+        <v>0.08621063501688636</v>
       </c>
       <c r="C48">
-        <v>46005.57227349401</v>
+        <v>48099.13759770699</v>
       </c>
       <c r="D48">
-        <v>82871.86480965457</v>
+        <v>84965.43013386754</v>
       </c>
       <c r="E48">
         <v>7249.021805376757</v>
@@ -5223,37 +5223,37 @@
         <v>8297</v>
       </c>
       <c r="M48">
-        <v>2295.346637843696</v>
+        <v>2192.274077249679</v>
       </c>
       <c r="N48">
-        <v>6001.653362156304</v>
+        <v>6104.725922750322</v>
       </c>
       <c r="O48">
-        <v>876.2413908748204</v>
+        <v>891.2899847215469</v>
       </c>
       <c r="P48">
-        <v>5125.411971281484</v>
+        <v>5213.435938028775</v>
       </c>
       <c r="Q48">
-        <v>11648.41197128148</v>
+        <v>11736.43593802878</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1194669594845993</v>
+        <v>0.1194195981794192</v>
       </c>
       <c r="T48">
         <v>1.700221666961182</v>
       </c>
       <c r="U48">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V48">
         <v>0.146</v>
       </c>
       <c r="W48">
-        <v>0.0494466</v>
+        <v>0.0472262</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.614704578038985</v>
+        <v>3.784654522033585</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5272,13 +5272,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.08723179967953101</v>
+        <v>0.08616267660266241</v>
       </c>
       <c r="C49">
-        <v>45195.35559636218</v>
+        <v>47338.2817238258</v>
       </c>
       <c r="D49">
-        <v>82923.45883983056</v>
+        <v>85066.38496729419</v>
       </c>
       <c r="E49">
         <v>8110.832512684592</v>
@@ -5305,37 +5305,37 @@
         <v>8297</v>
       </c>
       <c r="M49">
-        <v>2345.24547779682</v>
+        <v>2239.932209363802</v>
       </c>
       <c r="N49">
-        <v>5951.75452220318</v>
+        <v>6057.067790636198</v>
       </c>
       <c r="O49">
-        <v>868.9561602416643</v>
+        <v>884.3318974328848</v>
       </c>
       <c r="P49">
-        <v>5082.798361961516</v>
+        <v>5172.735893203313</v>
       </c>
       <c r="Q49">
-        <v>11605.79836196152</v>
+        <v>11695.73589320331</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1207394295840208</v>
+        <v>0.1206912501937027</v>
       </c>
       <c r="T49">
         <v>1.729590073757568</v>
       </c>
       <c r="U49">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V49">
         <v>0.146</v>
       </c>
       <c r="W49">
-        <v>0.0494466</v>
+        <v>0.0472262</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.537795969995603</v>
+        <v>3.704129957734998</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5354,13 +5354,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.08720600523737837</v>
+        <v>0.08611471818843848</v>
       </c>
       <c r="C50">
-        <v>44385.20320165608</v>
+        <v>46577.66604181183</v>
       </c>
       <c r="D50">
-        <v>82975.1171524323</v>
+        <v>85167.57999258806</v>
       </c>
       <c r="E50">
         <v>8972.643219992427</v>
@@ -5387,37 +5387,37 @@
         <v>8297</v>
       </c>
       <c r="M50">
-        <v>2395.144317749943</v>
+        <v>2287.590341477925</v>
       </c>
       <c r="N50">
-        <v>5901.855682250057</v>
+        <v>6009.409658522075</v>
       </c>
       <c r="O50">
-        <v>861.6709296085082</v>
+        <v>877.3738101442229</v>
       </c>
       <c r="P50">
-        <v>5040.184752641549</v>
+        <v>5132.035848377852</v>
       </c>
       <c r="Q50">
-        <v>11563.18475264155</v>
+        <v>11655.03584837785</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1220608408411122</v>
+        <v>0.1220118119008432</v>
       </c>
       <c r="T50">
         <v>1.760088034661507</v>
       </c>
       <c r="U50">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V50">
         <v>0.146</v>
       </c>
       <c r="W50">
-        <v>0.0494466</v>
+        <v>0.0472262</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.464091887287361</v>
+        <v>3.626960583615519</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5436,13 +5436,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.08718021079522574</v>
+        <v>0.08606675977421455</v>
       </c>
       <c r="C51">
-        <v>43575.11520958735</v>
+        <v>45817.29140988323</v>
       </c>
       <c r="D51">
-        <v>83026.83986767141</v>
+        <v>85269.0160679673</v>
       </c>
       <c r="E51">
         <v>9834.45392730027</v>
@@ -5469,37 +5469,37 @@
         <v>8297</v>
       </c>
       <c r="M51">
-        <v>2445.043157703067</v>
+        <v>2335.248473592049</v>
       </c>
       <c r="N51">
-        <v>5851.956842296933</v>
+        <v>5961.751526407951</v>
       </c>
       <c r="O51">
-        <v>854.3856989753522</v>
+        <v>870.4157228555608</v>
       </c>
       <c r="P51">
-        <v>4997.571143321581</v>
+        <v>5091.335803552391</v>
       </c>
       <c r="Q51">
-        <v>11520.57114332158</v>
+        <v>11614.33580355239</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1234340721475014</v>
+        <v>0.1233841603415972</v>
       </c>
       <c r="T51">
         <v>1.791781994032268</v>
       </c>
       <c r="U51">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V51">
         <v>0.146</v>
       </c>
       <c r="W51">
-        <v>0.0494466</v>
+        <v>0.0472262</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.393396134485578</v>
+        <v>3.552940979868263</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5518,13 +5518,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.08715441635307311</v>
+        <v>0.08601880135999061</v>
       </c>
       <c r="C52">
-        <v>42765.09174066773</v>
+        <v>45057.1586903516</v>
       </c>
       <c r="D52">
-        <v>83078.62710605963</v>
+        <v>85370.6940557435</v>
       </c>
       <c r="E52">
         <v>10696.26463460811</v>
@@ -5551,37 +5551,37 @@
         <v>8297</v>
       </c>
       <c r="M52">
-        <v>2494.941997656191</v>
+        <v>2382.906605706172</v>
       </c>
       <c r="N52">
-        <v>5802.058002343809</v>
+        <v>5914.093394293828</v>
       </c>
       <c r="O52">
-        <v>847.100468342196</v>
+        <v>863.4576355668988</v>
       </c>
       <c r="P52">
-        <v>4954.957534001613</v>
+        <v>5050.635758726929</v>
       </c>
       <c r="Q52">
-        <v>11477.95753400161</v>
+        <v>11573.63575872693</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1248622327061462</v>
+        <v>0.1248114027199812</v>
       </c>
       <c r="T52">
         <v>1.824743711777858</v>
       </c>
       <c r="U52">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V52">
         <v>0.146</v>
       </c>
       <c r="W52">
-        <v>0.0494466</v>
+        <v>0.0472262</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.325528211795866</v>
+        <v>3.481882160270898</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5600,13 +5600,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.08712862191092047</v>
+        <v>0.08597084294576669</v>
       </c>
       <c r="C53">
-        <v>41955.13291570979</v>
+        <v>44297.26874964646</v>
       </c>
       <c r="D53">
-        <v>83130.47898840952</v>
+        <v>85472.61482234619</v>
       </c>
       <c r="E53">
         <v>11558.07534191594</v>
@@ -5633,37 +5633,37 @@
         <v>8297</v>
       </c>
       <c r="M53">
-        <v>2544.840837609315</v>
+        <v>2430.564737820296</v>
       </c>
       <c r="N53">
-        <v>5752.159162390685</v>
+        <v>5866.435262179704</v>
       </c>
       <c r="O53">
-        <v>839.8152377090399</v>
+        <v>856.4995482782368</v>
       </c>
       <c r="P53">
-        <v>4912.343924681645</v>
+        <v>5009.935713901467</v>
       </c>
       <c r="Q53">
-        <v>11435.34392468165</v>
+        <v>11532.93571390147</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1263486855324908</v>
+        <v>0.1262968998893198</v>
       </c>
       <c r="T53">
         <v>1.859050805757963</v>
       </c>
       <c r="U53">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V53">
         <v>0.146</v>
       </c>
       <c r="W53">
-        <v>0.0494466</v>
+        <v>0.0472262</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.260321776270457</v>
+        <v>3.4136099610499</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5682,13 +5682,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.08710282746876785</v>
+        <v>0.08592288453154276</v>
       </c>
       <c r="C54">
-        <v>41145.23885582778</v>
+        <v>43537.62245833992</v>
       </c>
       <c r="D54">
-        <v>83182.39563583536</v>
+        <v>85574.7792383475</v>
       </c>
       <c r="E54">
         <v>12419.88604922378</v>
@@ -5715,37 +5715,37 @@
         <v>8297</v>
       </c>
       <c r="M54">
-        <v>2594.739677562439</v>
+        <v>2478.222869934419</v>
       </c>
       <c r="N54">
-        <v>5702.260322437562</v>
+        <v>5818.77713006558</v>
       </c>
       <c r="O54">
-        <v>832.530007075884</v>
+        <v>849.5414609895747</v>
       </c>
       <c r="P54">
-        <v>4869.730315361678</v>
+        <v>4969.235669076006</v>
       </c>
       <c r="Q54">
-        <v>11392.73031536168</v>
+        <v>11492.23566907601</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1278970738932663</v>
+        <v>0.1278442927740474</v>
       </c>
       <c r="T54">
         <v>1.894787361987239</v>
       </c>
       <c r="U54">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V54">
         <v>0.146</v>
       </c>
       <c r="W54">
-        <v>0.0494466</v>
+        <v>0.0472262</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.197623280572949</v>
+        <v>3.347963615645094</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5764,13 +5764,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.08707703302661522</v>
+        <v>0.08587492611731883</v>
       </c>
       <c r="C55">
-        <v>40335.40968243887</v>
+        <v>42778.22069117134</v>
       </c>
       <c r="D55">
-        <v>83234.37716975428</v>
+        <v>85677.18817848676</v>
       </c>
       <c r="E55">
         <v>13281.69675653162</v>
@@ -5797,37 +5797,37 @@
         <v>8297</v>
       </c>
       <c r="M55">
-        <v>2644.638517515562</v>
+        <v>2525.881002048543</v>
       </c>
       <c r="N55">
-        <v>5652.361482484437</v>
+        <v>5771.118997951457</v>
       </c>
       <c r="O55">
-        <v>825.2447764427278</v>
+        <v>842.5833737009127</v>
       </c>
       <c r="P55">
-        <v>4827.116706041709</v>
+        <v>4928.535624250545</v>
       </c>
       <c r="Q55">
-        <v>11350.11670604171</v>
+        <v>11451.53562425054</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1295113511204579</v>
+        <v>0.1294575321645081</v>
       </c>
       <c r="T55">
         <v>1.932044622736909</v>
       </c>
       <c r="U55">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V55">
         <v>0.146</v>
       </c>
       <c r="W55">
-        <v>0.0494466</v>
+        <v>0.0472262</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.137290765845157</v>
+        <v>3.284794490821602</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5846,13 +5846,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.08705123858446259</v>
+        <v>0.08582696770309488</v>
       </c>
       <c r="C56">
-        <v>39525.64551726379</v>
+        <v>42019.06432707247</v>
       </c>
       <c r="D56">
-        <v>83286.42371188705</v>
+        <v>85779.84252169573</v>
       </c>
       <c r="E56">
         <v>14143.50746383946</v>
@@ -5879,37 +5879,37 @@
         <v>8297</v>
       </c>
       <c r="M56">
-        <v>2694.537357468686</v>
+        <v>2573.539134162666</v>
       </c>
       <c r="N56">
-        <v>5602.462642531314</v>
+        <v>5723.460865837334</v>
       </c>
       <c r="O56">
-        <v>817.9595458095718</v>
+        <v>835.6252864122506</v>
       </c>
       <c r="P56">
-        <v>4784.503096721742</v>
+        <v>4887.835579425083</v>
       </c>
       <c r="Q56">
-        <v>11307.50309672174</v>
+        <v>11410.83557942508</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1311958143140491</v>
+        <v>0.1311409123980324</v>
       </c>
       <c r="T56">
         <v>1.970921764388739</v>
       </c>
       <c r="U56">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V56">
         <v>0.146</v>
       </c>
       <c r="W56">
-        <v>0.0494466</v>
+        <v>0.0472262</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.079192788699876</v>
+        <v>3.223964963213794</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5928,13 +5928,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.08702544414230996</v>
+        <v>0.08577900928887097</v>
       </c>
       <c r="C57">
-        <v>38715.94648232801</v>
+        <v>41260.15424919222</v>
       </c>
       <c r="D57">
-        <v>83338.5353842591</v>
+        <v>85882.74315112332</v>
       </c>
       <c r="E57">
         <v>15005.3181711473</v>
@@ -5961,37 +5961,37 @@
         <v>8297</v>
       </c>
       <c r="M57">
-        <v>2744.43619742181</v>
+        <v>2621.197266276789</v>
       </c>
       <c r="N57">
-        <v>5552.56380257819</v>
+        <v>5675.802733723211</v>
       </c>
       <c r="O57">
-        <v>810.6743151764157</v>
+        <v>828.6671991235887</v>
       </c>
       <c r="P57">
-        <v>4741.889487401774</v>
+        <v>4847.135534599622</v>
       </c>
       <c r="Q57">
-        <v>11264.88948740178</v>
+        <v>11370.13553459962</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1329551425384666</v>
+        <v>0.1328991095308244</v>
       </c>
       <c r="T57">
         <v>2.011526779002873</v>
       </c>
       <c r="U57">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V57">
         <v>0.146</v>
       </c>
       <c r="W57">
-        <v>0.0494466</v>
+        <v>0.0472262</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.023207465268969</v>
+        <v>3.165347418428089</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6010,13 +6010,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08824307370015734</v>
+        <v>0.08573105087464702</v>
       </c>
       <c r="C58">
-        <v>35463.27537908217</v>
+        <v>40501.49134492268</v>
       </c>
       <c r="D58">
-        <v>80947.6749883211</v>
+        <v>85985.89095416162</v>
       </c>
       <c r="E58">
         <v>15867.12887845514</v>
@@ -6043,45 +6043,45 @@
         <v>8297</v>
       </c>
       <c r="M58">
-        <v>2919.814676358956</v>
+        <v>2668.855398390913</v>
       </c>
       <c r="N58">
-        <v>5377.185323641044</v>
+        <v>5628.144601609087</v>
       </c>
       <c r="O58">
-        <v>785.0690572515924</v>
+        <v>821.7091118349266</v>
       </c>
       <c r="P58">
-        <v>4592.116266389452</v>
+        <v>4806.43548977416</v>
       </c>
       <c r="Q58">
-        <v>11115.11626638945</v>
+        <v>11329.43548977416</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1347944402276303</v>
+        <v>0.1347372247151069</v>
       </c>
       <c r="T58">
         <v>2.053977476099467</v>
       </c>
       <c r="U58">
-        <v>0.0605</v>
+        <v>0.0553</v>
       </c>
       <c r="V58">
         <v>0.146</v>
       </c>
       <c r="W58">
-        <v>0.051667</v>
+        <v>0.0472262</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y58">
-        <v>2.841618705179761</v>
+        <v>3.10882335738473</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6092,13 +6092,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08823948325800471</v>
+        <v>0.08568309246042308</v>
       </c>
       <c r="C59">
-        <v>34608.31296308525</v>
+        <v>39743.07650592388</v>
       </c>
       <c r="D59">
-        <v>80954.52327963202</v>
+        <v>86089.28682247065</v>
       </c>
       <c r="E59">
         <v>16728.93958576298</v>
@@ -6125,45 +6125,45 @@
         <v>8297</v>
       </c>
       <c r="M59">
-        <v>2971.954224151079</v>
+        <v>2716.513530505037</v>
       </c>
       <c r="N59">
-        <v>5325.045775848921</v>
+        <v>5580.486469494963</v>
       </c>
       <c r="O59">
-        <v>777.4566832739424</v>
+        <v>814.7510245462645</v>
       </c>
       <c r="P59">
-        <v>4547.589092574979</v>
+        <v>4765.735444948698</v>
       </c>
       <c r="Q59">
-        <v>11070.58909257498</v>
+        <v>11288.7354449487</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1367192866465226</v>
+        <v>0.1366608336288909</v>
       </c>
       <c r="T59">
         <v>2.098402624223809</v>
       </c>
       <c r="U59">
-        <v>0.0605</v>
+        <v>0.0553</v>
       </c>
       <c r="V59">
         <v>0.146</v>
       </c>
       <c r="W59">
-        <v>0.051667</v>
+        <v>0.0472262</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y59">
-        <v>2.791765745439766</v>
+        <v>3.054282596728858</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6174,13 +6174,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.08823589281585209</v>
+        <v>0.08563513404619916</v>
       </c>
       <c r="C60">
-        <v>33753.35170593721</v>
+        <v>38984.91062814984</v>
       </c>
       <c r="D60">
-        <v>80961.37272979181</v>
+        <v>86192.93165200444</v>
       </c>
       <c r="E60">
         <v>17590.7502930708</v>
@@ -6207,45 +6207,45 @@
         <v>8297</v>
       </c>
       <c r="M60">
-        <v>3024.093771943203</v>
+        <v>2764.17166261916</v>
       </c>
       <c r="N60">
-        <v>5272.906228056797</v>
+        <v>5532.828337380841</v>
       </c>
       <c r="O60">
-        <v>769.8443092962923</v>
+        <v>807.7929372576027</v>
       </c>
       <c r="P60">
-        <v>4503.061918760504</v>
+        <v>4725.035400123238</v>
       </c>
       <c r="Q60">
-        <v>11026.0619187605</v>
+        <v>11248.03540012324</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1387357924186954</v>
+        <v>0.1386760429671408</v>
       </c>
       <c r="T60">
         <v>2.144943255592168</v>
       </c>
       <c r="U60">
-        <v>0.0605</v>
+        <v>0.0553</v>
       </c>
       <c r="V60">
         <v>0.146</v>
       </c>
       <c r="W60">
-        <v>0.051667</v>
+        <v>0.0472262</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y60">
-        <v>2.743631853277012</v>
+        <v>3.001622551957671</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6256,13 +6256,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.08823230237369946</v>
+        <v>0.08684682563197521</v>
       </c>
       <c r="C61">
-        <v>32898.39160793225</v>
+        <v>35578.70706151339</v>
       </c>
       <c r="D61">
-        <v>80968.22333909469</v>
+        <v>83648.53879267583</v>
       </c>
       <c r="E61">
         <v>18452.56100037865</v>
@@ -6289,37 +6289,37 @@
         <v>8297</v>
       </c>
       <c r="M61">
-        <v>3076.233319735328</v>
+        <v>2938.946874061189</v>
       </c>
       <c r="N61">
-        <v>5220.766680264673</v>
+        <v>5358.053125938811</v>
       </c>
       <c r="O61">
-        <v>762.2319353186422</v>
+        <v>782.2757563870663</v>
       </c>
       <c r="P61">
-        <v>4458.534744946031</v>
+        <v>4575.777369551744</v>
       </c>
       <c r="Q61">
-        <v>10981.53474494603</v>
+        <v>11098.77736955174</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1408506643260962</v>
+        <v>0.1407895551999395</v>
       </c>
       <c r="T61">
         <v>2.193754161661422</v>
       </c>
       <c r="U61">
-        <v>0.0605</v>
+        <v>0.0578</v>
       </c>
       <c r="V61">
         <v>0.146</v>
       </c>
       <c r="W61">
-        <v>0.051667</v>
+        <v>0.0493612</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.697129618475707</v>
+        <v>2.823120102383741</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6338,13 +6338,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.08822871193154683</v>
+        <v>0.08682021721775128</v>
       </c>
       <c r="C62">
-        <v>32043.43266936464</v>
+        <v>34771.15630503924</v>
       </c>
       <c r="D62">
-        <v>80975.07510783491</v>
+        <v>83702.79874350951</v>
       </c>
       <c r="E62">
         <v>19314.37170768648</v>
@@ -6371,37 +6371,37 @@
         <v>8297</v>
       </c>
       <c r="M62">
-        <v>3128.372867527451</v>
+        <v>2988.759532943582</v>
       </c>
       <c r="N62">
-        <v>5168.627132472549</v>
+        <v>5308.240467056417</v>
       </c>
       <c r="O62">
-        <v>754.619561340992</v>
+        <v>775.0031081902368</v>
       </c>
       <c r="P62">
-        <v>4414.007571131557</v>
+        <v>4533.23735886618</v>
       </c>
       <c r="Q62">
-        <v>10937.00757113156</v>
+        <v>11056.23735886618</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1430712798288671</v>
+        <v>0.1430087430443782</v>
       </c>
       <c r="T62">
         <v>2.245005613034139</v>
       </c>
       <c r="U62">
-        <v>0.0605</v>
+        <v>0.0578</v>
       </c>
       <c r="V62">
         <v>0.146</v>
       </c>
       <c r="W62">
-        <v>0.051667</v>
+        <v>0.0493612</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.652177458167778</v>
+        <v>2.776068100677345</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6420,13 +6420,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.0882251214893942</v>
+        <v>0.08679360880352735</v>
       </c>
       <c r="C63">
-        <v>31188.47489052872</v>
+        <v>33963.67598741101</v>
       </c>
       <c r="D63">
-        <v>80981.92803630684</v>
+        <v>83757.12913318913</v>
       </c>
       <c r="E63">
         <v>20176.18241499432</v>
@@ -6453,37 +6453,37 @@
         <v>8297</v>
       </c>
       <c r="M63">
-        <v>3180.512415319576</v>
+        <v>3038.572191825976</v>
       </c>
       <c r="N63">
-        <v>5116.487584680424</v>
+        <v>5258.427808174025</v>
       </c>
       <c r="O63">
-        <v>747.0071873633419</v>
+        <v>767.7304599934076</v>
       </c>
       <c r="P63">
-        <v>4369.480397317082</v>
+        <v>4490.697348180617</v>
       </c>
       <c r="Q63">
-        <v>10892.48039731708</v>
+        <v>11013.69734818062</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1454057730497287</v>
+        <v>0.1453417353936599</v>
       </c>
       <c r="T63">
         <v>2.298885343964432</v>
       </c>
       <c r="U63">
-        <v>0.0605</v>
+        <v>0.0578</v>
       </c>
       <c r="V63">
         <v>0.146</v>
       </c>
       <c r="W63">
-        <v>0.051667</v>
+        <v>0.0493612</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.608699139181421</v>
+        <v>2.730558787551487</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6502,13 +6502,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.08822153104724156</v>
+        <v>0.08676700038930342</v>
       </c>
       <c r="C64">
-        <v>30333.51827171899</v>
+        <v>33156.26624588062</v>
       </c>
       <c r="D64">
-        <v>80988.78212480494</v>
+        <v>83811.53009896657</v>
       </c>
       <c r="E64">
         <v>21037.99312230216</v>
@@ -6535,37 +6535,37 @@
         <v>8297</v>
       </c>
       <c r="M64">
-        <v>3232.6519631117</v>
+        <v>3088.384850708369</v>
       </c>
       <c r="N64">
-        <v>5064.348036888299</v>
+        <v>5208.615149291631</v>
       </c>
       <c r="O64">
-        <v>739.3948133856917</v>
+        <v>760.4578117965782</v>
       </c>
       <c r="P64">
-        <v>4324.953223502607</v>
+        <v>4448.157337495053</v>
       </c>
       <c r="Q64">
-        <v>10847.95322350261</v>
+        <v>10971.15733749505</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1478631343348462</v>
+        <v>0.1477975168139564</v>
       </c>
       <c r="T64">
         <v>2.355600850206845</v>
       </c>
       <c r="U64">
-        <v>0.0605</v>
+        <v>0.0578</v>
       </c>
       <c r="V64">
         <v>0.146</v>
       </c>
       <c r="W64">
-        <v>0.051667</v>
+        <v>0.0493612</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.566623346613978</v>
+        <v>2.686517516784527</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6584,13 +6584,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.08821794060508892</v>
+        <v>0.08674039197507949</v>
       </c>
       <c r="C65">
-        <v>29478.56281323003</v>
+        <v>32348.92721805675</v>
       </c>
       <c r="D65">
-        <v>80995.63737362383</v>
+        <v>83866.00177845055</v>
       </c>
       <c r="E65">
         <v>21899.80382961</v>
@@ -6617,37 +6617,37 @@
         <v>8297</v>
       </c>
       <c r="M65">
-        <v>3284.791510903824</v>
+        <v>3138.197509590762</v>
       </c>
       <c r="N65">
-        <v>5012.208489096176</v>
+        <v>5158.802490409238</v>
       </c>
       <c r="O65">
-        <v>731.7824394080417</v>
+        <v>753.1851635997488</v>
       </c>
       <c r="P65">
-        <v>4280.426049688134</v>
+        <v>4405.617326809489</v>
       </c>
       <c r="Q65">
-        <v>10803.42604968813</v>
+        <v>10928.61732680949</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1504533259596998</v>
+        <v>0.1503860431758905</v>
       </c>
       <c r="T65">
         <v>2.415382059489389</v>
       </c>
       <c r="U65">
-        <v>0.0605</v>
+        <v>0.0578</v>
       </c>
       <c r="V65">
         <v>0.146</v>
       </c>
       <c r="W65">
-        <v>0.051667</v>
+        <v>0.0493612</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.525883293493122</v>
+        <v>2.643874381597471</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6666,13 +6666,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.08969006216293632</v>
+        <v>0.08671378356085555</v>
       </c>
       <c r="C66">
-        <v>25900.06823733582</v>
+        <v>31541.65904190612</v>
       </c>
       <c r="D66">
-        <v>78278.95350503745</v>
+        <v>83920.54430960775</v>
       </c>
       <c r="E66">
         <v>22761.61453691784</v>
@@ -6699,45 +6699,45 @@
         <v>8297</v>
       </c>
       <c r="M66">
-        <v>3485.851948918743</v>
+        <v>3188.010168473154</v>
       </c>
       <c r="N66">
-        <v>4811.148051081256</v>
+        <v>5108.989831526846</v>
       </c>
       <c r="O66">
-        <v>702.4276154578633</v>
+        <v>745.9125154029194</v>
       </c>
       <c r="P66">
-        <v>4108.720435623392</v>
+        <v>4363.077316123926</v>
       </c>
       <c r="Q66">
-        <v>10631.72043562339</v>
+        <v>10886.07731612393</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1531874171192675</v>
+        <v>0.1531183765579321</v>
       </c>
       <c r="T66">
         <v>2.478484447065407</v>
       </c>
       <c r="U66">
-        <v>0.06320000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V66">
         <v>0.146</v>
       </c>
       <c r="W66">
-        <v>0.0539728</v>
+        <v>0.0493612</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y66">
-        <v>2.380192882997684</v>
+        <v>2.602563844385011</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6748,13 +6748,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.08970952972078369</v>
+        <v>0.08668717514663163</v>
       </c>
       <c r="C67">
-        <v>25003.5520784943</v>
+        <v>30734.46185575444</v>
       </c>
       <c r="D67">
-        <v>78244.24805350378</v>
+        <v>83975.15783076391</v>
       </c>
       <c r="E67">
         <v>23623.42524422568</v>
@@ -6781,45 +6781,45 @@
         <v>8297</v>
       </c>
       <c r="M67">
-        <v>3540.318385620599</v>
+        <v>3237.822827355548</v>
       </c>
       <c r="N67">
-        <v>4756.6816143794</v>
+        <v>5059.177172644452</v>
       </c>
       <c r="O67">
-        <v>694.4755156993924</v>
+        <v>738.63986720609</v>
       </c>
       <c r="P67">
-        <v>4062.206098680008</v>
+        <v>4320.537305438362</v>
       </c>
       <c r="Q67">
-        <v>10585.20609868001</v>
+        <v>10843.53730543836</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.156077742059382</v>
+        <v>0.1560068432760904</v>
       </c>
       <c r="T67">
         <v>2.545192685360055</v>
       </c>
       <c r="U67">
-        <v>0.06320000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V67">
         <v>0.146</v>
       </c>
       <c r="W67">
-        <v>0.0539728</v>
+        <v>0.0493612</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y67">
-        <v>2.343574530951566</v>
+        <v>2.562524400625241</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6830,13 +6830,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.08972899727863104</v>
+        <v>0.08666056673240768</v>
       </c>
       <c r="C68">
-        <v>24107.06667976243</v>
+        <v>29927.335798288</v>
       </c>
       <c r="D68">
-        <v>78209.57336207974</v>
+        <v>84029.84248060531</v>
       </c>
       <c r="E68">
         <v>24485.23595153352</v>
@@ -6863,45 +6863,45 @@
         <v>8297</v>
       </c>
       <c r="M68">
-        <v>3594.784822322455</v>
+        <v>3287.635486237941</v>
       </c>
       <c r="N68">
-        <v>4702.215177677545</v>
+        <v>5009.364513762059</v>
       </c>
       <c r="O68">
-        <v>686.5234159409216</v>
+        <v>731.3672190092606</v>
       </c>
       <c r="P68">
-        <v>4015.691761736624</v>
+        <v>4277.997294752799</v>
       </c>
       <c r="Q68">
-        <v>10538.69176173662</v>
+        <v>10800.9972947528</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1591380861136207</v>
+        <v>0.1590652198011991</v>
       </c>
       <c r="T68">
         <v>2.615824937672035</v>
       </c>
       <c r="U68">
-        <v>0.06320000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V68">
         <v>0.146</v>
       </c>
       <c r="W68">
-        <v>0.0539728</v>
+        <v>0.0493612</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y68">
-        <v>2.308065825937148</v>
+        <v>2.523698273343041</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6912,13 +6912,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.08974846483647843</v>
+        <v>0.08863658831818376</v>
       </c>
       <c r="C69">
-        <v>23210.61200026327</v>
+        <v>25189.28776419577</v>
       </c>
       <c r="D69">
-        <v>78174.92938988842</v>
+        <v>80153.60515382093</v>
       </c>
       <c r="E69">
         <v>25347.04665884136</v>
@@ -6945,37 +6945,37 @@
         <v>8297</v>
       </c>
       <c r="M69">
-        <v>3649.25125902431</v>
+        <v>3539.542755984022</v>
       </c>
       <c r="N69">
-        <v>4647.74874097569</v>
+        <v>4757.457244015978</v>
       </c>
       <c r="O69">
-        <v>678.5713161824508</v>
+        <v>694.5887576263327</v>
       </c>
       <c r="P69">
-        <v>3969.17742479324</v>
+        <v>4062.868486389646</v>
       </c>
       <c r="Q69">
-        <v>10492.17742479324</v>
+        <v>10585.86848638965</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1623839055650862</v>
+        <v>0.1623089524793447</v>
       </c>
       <c r="T69">
         <v>2.690737932548378</v>
       </c>
       <c r="U69">
-        <v>0.06320000000000001</v>
+        <v>0.0613</v>
       </c>
       <c r="V69">
         <v>0.146</v>
       </c>
       <c r="W69">
-        <v>0.0539728</v>
+        <v>0.0523502</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.273617082266444</v>
+        <v>2.344088084816302</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6994,13 +6994,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.09249731639432579</v>
+        <v>0.08863986990395981</v>
       </c>
       <c r="C70">
-        <v>17747.01058996519</v>
+        <v>24321.33719392474</v>
       </c>
       <c r="D70">
-        <v>73573.13868689818</v>
+        <v>80147.46529085773</v>
       </c>
       <c r="E70">
         <v>26208.85736614919</v>
@@ -7027,45 +7027,45 @@
         <v>8297</v>
       </c>
       <c r="M70">
-        <v>3979.15239778175</v>
+        <v>3592.371752341992</v>
       </c>
       <c r="N70">
-        <v>4317.847602218249</v>
+        <v>4704.628247658007</v>
       </c>
       <c r="O70">
-        <v>630.4057499238644</v>
+        <v>686.875724158069</v>
       </c>
       <c r="P70">
-        <v>3687.441852294385</v>
+        <v>4017.752523499938</v>
       </c>
       <c r="Q70">
-        <v>10210.44185229439</v>
+        <v>10540.75252349994</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1658325887322681</v>
+        <v>0.1657554184498744</v>
       </c>
       <c r="T70">
         <v>2.770332989604491</v>
       </c>
       <c r="U70">
-        <v>0.0679</v>
+        <v>0.0613</v>
       </c>
       <c r="V70">
         <v>0.146</v>
       </c>
       <c r="W70">
-        <v>0.0579866</v>
+        <v>0.0523502</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y70">
-        <v>2.085117424661923</v>
+        <v>2.309616201216062</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7076,13 +7076,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09255692195217317</v>
+        <v>0.08864315148973589</v>
       </c>
       <c r="C71">
-        <v>16791.40910706906</v>
+        <v>23453.38756422341</v>
       </c>
       <c r="D71">
-        <v>73479.34791130989</v>
+        <v>80141.32636846424</v>
       </c>
       <c r="E71">
         <v>27070.66807345704</v>
@@ -7109,45 +7109,45 @@
         <v>8297</v>
       </c>
       <c r="M71">
-        <v>4037.669344807953</v>
+        <v>3645.200748699963</v>
       </c>
       <c r="N71">
-        <v>4259.330655192047</v>
+        <v>4651.799251300037</v>
       </c>
       <c r="O71">
-        <v>621.8622756580388</v>
+        <v>679.1626906898053</v>
       </c>
       <c r="P71">
-        <v>3637.468379534008</v>
+        <v>3972.636560610232</v>
       </c>
       <c r="Q71">
-        <v>10160.46837953401</v>
+        <v>10495.63656061023</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1695037675876554</v>
+        <v>0.1694242370636642</v>
       </c>
       <c r="T71">
         <v>2.855063211631968</v>
       </c>
       <c r="U71">
-        <v>0.0679</v>
+        <v>0.0613</v>
       </c>
       <c r="V71">
         <v>0.146</v>
       </c>
       <c r="W71">
-        <v>0.0579866</v>
+        <v>0.0523502</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y71">
-        <v>2.054898331550881</v>
+        <v>2.276143502647713</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7158,13 +7158,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09261652751002053</v>
+        <v>0.09032027307551195</v>
       </c>
       <c r="C72">
-        <v>15836.04644801564</v>
+        <v>19572.57586971801</v>
       </c>
       <c r="D72">
-        <v>73385.7959595643</v>
+        <v>77122.32538126668</v>
       </c>
       <c r="E72">
         <v>27932.47878076487</v>
@@ -7191,37 +7191,37 @@
         <v>8297</v>
       </c>
       <c r="M72">
-        <v>4096.186291834155</v>
+        <v>3866.94464369027</v>
       </c>
       <c r="N72">
-        <v>4200.813708165845</v>
+        <v>4430.05535630973</v>
       </c>
       <c r="O72">
-        <v>613.3188013922133</v>
+        <v>646.7880820212206</v>
       </c>
       <c r="P72">
-        <v>3587.494906773632</v>
+        <v>3783.26727428851</v>
       </c>
       <c r="Q72">
-        <v>10110.49490677363</v>
+        <v>10306.26727428851</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1734196917000685</v>
+        <v>0.1733376435850399</v>
       </c>
       <c r="T72">
         <v>2.945442115127942</v>
       </c>
       <c r="U72">
-        <v>0.0679</v>
+        <v>0.0641</v>
       </c>
       <c r="V72">
         <v>0.146</v>
       </c>
       <c r="W72">
-        <v>0.0579866</v>
+        <v>0.0547414</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.025542641100154</v>
+        <v>2.145621612023408</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7240,13 +7240,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.09831509506786791</v>
+        <v>0.09034746666128803</v>
       </c>
       <c r="C73">
-        <v>7010.926990689783</v>
+        <v>18663.68655777366</v>
       </c>
       <c r="D73">
-        <v>65422.48720954628</v>
+        <v>77075.24677663016</v>
       </c>
       <c r="E73">
         <v>28794.2894880727</v>
@@ -7273,45 +7273,45 @@
         <v>8297</v>
       </c>
       <c r="M73">
-        <v>4723.756848895721</v>
+        <v>3922.186710028702</v>
       </c>
       <c r="N73">
-        <v>3573.243151104279</v>
+        <v>4374.813289971298</v>
       </c>
       <c r="O73">
-        <v>521.6935000612247</v>
+        <v>638.7227403358095</v>
       </c>
       <c r="P73">
-        <v>3051.549651043054</v>
+        <v>3736.090549635489</v>
       </c>
       <c r="Q73">
-        <v>9574.549651043053</v>
+        <v>10259.09054963549</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1776056795443721</v>
+        <v>0.177520940211338</v>
       </c>
       <c r="T73">
         <v>3.042054046451225</v>
       </c>
       <c r="U73">
-        <v>0.07719999999999999</v>
+        <v>0.0641</v>
       </c>
       <c r="V73">
         <v>0.146</v>
       </c>
       <c r="W73">
-        <v>0.0659288</v>
+        <v>0.0547414</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y73">
-        <v>1.756440956934437</v>
+        <v>2.115401589318854</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7322,13 +7322,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.1013440586257153</v>
+        <v>0.09037466024706409</v>
       </c>
       <c r="C74">
-        <v>2581.456041684956</v>
+        <v>17754.8546881549</v>
       </c>
       <c r="D74">
-        <v>61854.82696784929</v>
+        <v>77028.22561431924</v>
       </c>
       <c r="E74">
         <v>29656.10019538054</v>
@@ -7355,45 +7355,45 @@
         <v>8297</v>
       </c>
       <c r="M74">
-        <v>5081.925378852859</v>
+        <v>3977.428776367134</v>
       </c>
       <c r="N74">
-        <v>3215.074621147141</v>
+        <v>4319.571223632865</v>
       </c>
       <c r="O74">
-        <v>469.4008946874825</v>
+        <v>630.6573986503984</v>
       </c>
       <c r="P74">
-        <v>2745.673726459658</v>
+        <v>3688.913824982467</v>
       </c>
       <c r="Q74">
-        <v>9268.673726459658</v>
+        <v>10211.91382498247</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1820906665204117</v>
+        <v>0.1820030437395146</v>
       </c>
       <c r="T74">
         <v>3.145566830011885</v>
       </c>
       <c r="U74">
-        <v>0.0819</v>
+        <v>0.0641</v>
       </c>
       <c r="V74">
         <v>0.146</v>
       </c>
       <c r="W74">
-        <v>0.06994259999999999</v>
+        <v>0.0547414</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y74">
-        <v>1.632648923678781</v>
+        <v>2.086021011689425</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7404,13 +7404,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.1015232241835627</v>
+        <v>0.09040185383284015</v>
       </c>
       <c r="C75">
-        <v>1520.764979881817</v>
+        <v>16846.0801557946</v>
       </c>
       <c r="D75">
-        <v>61655.94661335399</v>
+        <v>76981.26178926678</v>
       </c>
       <c r="E75">
         <v>30517.91090268838</v>
@@ -7437,45 +7437,45 @@
         <v>8297</v>
       </c>
       <c r="M75">
-        <v>5152.507675781371</v>
+        <v>4032.670842705566</v>
       </c>
       <c r="N75">
-        <v>3144.492324218629</v>
+        <v>4264.329157294434</v>
       </c>
       <c r="O75">
-        <v>459.0958793359198</v>
+        <v>622.5920569649873</v>
       </c>
       <c r="P75">
-        <v>2685.396444882709</v>
+        <v>3641.737100329447</v>
       </c>
       <c r="Q75">
-        <v>9208.39644488271</v>
+        <v>10164.73710032945</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1869078747539357</v>
+        <v>0.186817154936445</v>
       </c>
       <c r="T75">
         <v>3.256747227169631</v>
       </c>
       <c r="U75">
-        <v>0.0819</v>
+        <v>0.0641</v>
       </c>
       <c r="V75">
         <v>0.146</v>
       </c>
       <c r="W75">
-        <v>0.06994259999999999</v>
+        <v>0.0547414</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y75">
-        <v>1.610283869929756</v>
+        <v>2.057445381392309</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7486,13 +7486,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.10170238974141</v>
+        <v>0.09042904741861622</v>
       </c>
       <c r="C76">
-        <v>461.348729757512</v>
+        <v>15937.36285588169</v>
       </c>
       <c r="D76">
-        <v>61458.34107053753</v>
+        <v>76934.35519666171</v>
       </c>
       <c r="E76">
         <v>31379.72160999622</v>
@@ -7519,45 +7519,45 @@
         <v>8297</v>
       </c>
       <c r="M76">
-        <v>5223.089972709883</v>
+        <v>4087.912909043999</v>
       </c>
       <c r="N76">
-        <v>3073.910027290117</v>
+        <v>4209.087090956001</v>
       </c>
       <c r="O76">
-        <v>448.790863984357</v>
+        <v>614.526715279576</v>
       </c>
       <c r="P76">
-        <v>2625.11916330576</v>
+        <v>3594.560375676425</v>
       </c>
       <c r="Q76">
-        <v>9148.119163305761</v>
+        <v>10117.56037567642</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1920956374669616</v>
+        <v>0.1920015823792932</v>
       </c>
       <c r="T76">
         <v>3.376479962570281</v>
       </c>
       <c r="U76">
-        <v>0.0819</v>
+        <v>0.0641</v>
       </c>
       <c r="V76">
         <v>0.146</v>
       </c>
       <c r="W76">
-        <v>0.06994259999999999</v>
+        <v>0.0547414</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y76">
-        <v>1.588523277092868</v>
+        <v>2.029642065427548</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7568,13 +7568,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.1018815552992574</v>
+        <v>0.09045624100439228</v>
       </c>
       <c r="C77">
-        <v>-596.8049267342285</v>
+        <v>15028.70268386051</v>
       </c>
       <c r="D77">
-        <v>61261.99812135362</v>
+        <v>76887.50573194836</v>
       </c>
       <c r="E77">
         <v>32241.53231730406</v>
@@ -7601,45 +7601,45 @@
         <v>8297</v>
       </c>
       <c r="M77">
-        <v>5293.672269638395</v>
+        <v>4143.154975382432</v>
       </c>
       <c r="N77">
-        <v>3003.327730361605</v>
+        <v>4153.845024617568</v>
       </c>
       <c r="O77">
-        <v>438.4858486327943</v>
+        <v>606.4613735941649</v>
       </c>
       <c r="P77">
-        <v>2564.841881728811</v>
+        <v>3547.383651023403</v>
       </c>
       <c r="Q77">
-        <v>9087.841881728811</v>
+        <v>10070.3836510234</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1976984211970296</v>
+        <v>0.1976007640175691</v>
       </c>
       <c r="T77">
         <v>3.505791316802983</v>
       </c>
       <c r="U77">
-        <v>0.0819</v>
+        <v>0.0641</v>
       </c>
       <c r="V77">
         <v>0.146</v>
       </c>
       <c r="W77">
-        <v>0.06994259999999999</v>
+        <v>0.0547414</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y77">
-        <v>1.567342966731629</v>
+        <v>2.002580171221847</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7650,13 +7650,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.1020607208571048</v>
+        <v>0.09554594659016835</v>
       </c>
       <c r="C78">
-        <v>-1653.708052003356</v>
+        <v>6300.225560004277</v>
       </c>
       <c r="D78">
-        <v>61066.90570339233</v>
+        <v>69020.83931539996</v>
       </c>
       <c r="E78">
         <v>33103.3430246119</v>
@@ -7683,45 +7683,45 @@
         <v>8297</v>
       </c>
       <c r="M78">
-        <v>5364.254566566907</v>
+        <v>4709.27842901295</v>
       </c>
       <c r="N78">
-        <v>2932.745433433093</v>
+        <v>3587.72157098705</v>
       </c>
       <c r="O78">
-        <v>428.1808332812316</v>
+        <v>523.8073493641092</v>
       </c>
       <c r="P78">
-        <v>2504.564600151862</v>
+        <v>3063.914221622941</v>
       </c>
       <c r="Q78">
-        <v>9027.564600151862</v>
+        <v>9586.914221622941</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.2037681035712699</v>
+        <v>0.2036665441257015</v>
       </c>
       <c r="T78">
         <v>3.645878617221744</v>
       </c>
       <c r="U78">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V78">
         <v>0.146</v>
       </c>
       <c r="W78">
-        <v>0.06994259999999999</v>
+        <v>0.0614026</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y78">
-        <v>1.546720032958845</v>
+        <v>1.761841038933649</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7732,13 +7732,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.1022398864149521</v>
+        <v>0.09820431417594441</v>
       </c>
       <c r="C79">
-        <v>-2709.372555293696</v>
+        <v>1937.123692524328</v>
       </c>
       <c r="D79">
-        <v>60873.05190740983</v>
+        <v>65519.54815522784</v>
       </c>
       <c r="E79">
         <v>33965.15373191972</v>
@@ -7765,37 +7765,37 @@
         <v>8297</v>
       </c>
       <c r="M79">
-        <v>5434.836863495419</v>
+        <v>5030.044374272928</v>
       </c>
       <c r="N79">
-        <v>2862.163136504581</v>
+        <v>3266.955625727072</v>
       </c>
       <c r="O79">
-        <v>417.8758179296689</v>
+        <v>476.9755213561526</v>
       </c>
       <c r="P79">
-        <v>2444.287318574913</v>
+        <v>2789.98010437092</v>
       </c>
       <c r="Q79">
-        <v>8967.287318574912</v>
+        <v>9312.980104370919</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.2103655844128354</v>
+        <v>0.2102597833736714</v>
       </c>
       <c r="T79">
         <v>3.798147422024745</v>
       </c>
       <c r="U79">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V79">
         <v>0.146</v>
       </c>
       <c r="W79">
-        <v>0.06994259999999999</v>
+        <v>0.0647332</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.526632759803535</v>
+        <v>1.649488430447355</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7814,13 +7814,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.1024190519727995</v>
+        <v>0.09833142576172049</v>
       </c>
       <c r="C80">
-        <v>-3763.810195106562</v>
+        <v>916.7737195373047</v>
       </c>
       <c r="D80">
-        <v>60680.4249749048</v>
+        <v>65361.00888954867</v>
       </c>
       <c r="E80">
         <v>34826.96443922757</v>
@@ -7847,37 +7847,37 @@
         <v>8297</v>
       </c>
       <c r="M80">
-        <v>5505.41916042393</v>
+        <v>5095.369625886862</v>
       </c>
       <c r="N80">
-        <v>2791.58083957607</v>
+        <v>3201.630374113138</v>
       </c>
       <c r="O80">
-        <v>407.5708025781061</v>
+        <v>467.4380346205181</v>
       </c>
       <c r="P80">
-        <v>2384.010036997964</v>
+        <v>2734.19233949262</v>
       </c>
       <c r="Q80">
-        <v>8907.010036997963</v>
+        <v>9257.19233949262</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.2175628362399978</v>
+        <v>0.2174524080078204</v>
       </c>
       <c r="T80">
         <v>3.964258845446199</v>
       </c>
       <c r="U80">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V80">
         <v>0.146</v>
       </c>
       <c r="W80">
-        <v>0.06994259999999999</v>
+        <v>0.0647332</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.507060544934259</v>
+        <v>1.628341142877517</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7896,13 +7896,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.1370380111746119</v>
+        <v>0.09845853734749656</v>
       </c>
       <c r="C81">
-        <v>-27649.94080494437</v>
+        <v>-102.8108627463807</v>
       </c>
       <c r="D81">
-        <v>37656.10507237484</v>
+        <v>65203.23501457283</v>
       </c>
       <c r="E81">
         <v>35688.77514653541</v>
@@ -7929,45 +7929,45 @@
         <v>8297</v>
       </c>
       <c r="M81">
-        <v>8912.070705341084</v>
+        <v>5160.694877500797</v>
       </c>
       <c r="N81">
-        <v>-615.0707053410842</v>
+        <v>3136.305122499203</v>
       </c>
       <c r="O81">
-        <v>-89.8003229797983</v>
+        <v>457.9005478848836</v>
       </c>
       <c r="P81">
-        <v>-525.270382361286</v>
+        <v>2678.40457461432</v>
       </c>
       <c r="Q81">
-        <v>5997.729617638714</v>
+        <v>9201.40457461432</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.2270620060352834</v>
+        <v>0.2253300445118884</v>
       </c>
       <c r="T81">
-        <v>4.183498168164062</v>
+        <v>4.146190404431604</v>
       </c>
       <c r="U81">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V81">
-        <v>0.1359237420854415</v>
+        <v>0.146</v>
       </c>
       <c r="W81">
-        <v>0.1131075821610157</v>
+        <v>0.0647332</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y81">
-        <v>0.9309845348317909</v>
+        <v>1.607729229676536</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7978,13 +7978,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.1378890111746119</v>
+        <v>0.09858564893327262</v>
       </c>
       <c r="C82">
-        <v>-28859.73380685878</v>
+        <v>-1121.635583671989</v>
       </c>
       <c r="D82">
-        <v>37308.12277776827</v>
+        <v>65046.22100095507</v>
       </c>
       <c r="E82">
         <v>36550.58585384325</v>
@@ -8011,45 +8011,45 @@
         <v>8297</v>
       </c>
       <c r="M82">
-        <v>9024.881726927681</v>
+        <v>5226.02012911473</v>
       </c>
       <c r="N82">
-        <v>-727.8817269276806</v>
+        <v>3070.97987088527</v>
       </c>
       <c r="O82">
-        <v>-106.2707321314414</v>
+        <v>448.3630611492493</v>
       </c>
       <c r="P82">
-        <v>-621.6109947962392</v>
+        <v>2622.61680973602</v>
       </c>
       <c r="Q82">
-        <v>5901.38900520376</v>
+        <v>9145.616809736021</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.2361251063370475</v>
+        <v>0.2339954446663631</v>
       </c>
       <c r="T82">
-        <v>4.392673076572265</v>
+        <v>4.346315119315546</v>
       </c>
       <c r="U82">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V82">
-        <v>0.1342246953093734</v>
+        <v>0.146</v>
       </c>
       <c r="W82">
-        <v>0.113329987384003</v>
+        <v>0.0647332</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y82">
-        <v>0.9193472281463935</v>
+        <v>1.587632614305579</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8060,13 +8060,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1387400111746119</v>
+        <v>0.09871276051904869</v>
       </c>
       <c r="C83">
-        <v>-30063.15424804358</v>
+        <v>-2139.705919452521</v>
       </c>
       <c r="D83">
-        <v>36966.5130438913</v>
+        <v>64889.96137248236</v>
       </c>
       <c r="E83">
         <v>37412.39656115108</v>
@@ -8093,45 +8093,45 @@
         <v>8297</v>
       </c>
       <c r="M83">
-        <v>9137.692748514275</v>
+        <v>5291.345380728664</v>
       </c>
       <c r="N83">
-        <v>-840.6927485142751</v>
+        <v>3005.654619271336</v>
       </c>
       <c r="O83">
-        <v>-122.7411412830842</v>
+        <v>438.825574413615</v>
       </c>
       <c r="P83">
-        <v>-717.9516072311909</v>
+        <v>2566.829044857721</v>
       </c>
       <c r="Q83">
-        <v>5805.048392768809</v>
+        <v>9089.829044857721</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.2461422171968922</v>
+        <v>0.2435729922055194</v>
       </c>
       <c r="T83">
-        <v>4.623866396391859</v>
+        <v>4.567505593660958</v>
       </c>
       <c r="U83">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V83">
-        <v>0.132567600305554</v>
+        <v>0.146</v>
       </c>
       <c r="W83">
-        <v>0.113546901120003</v>
+        <v>0.0647332</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y83">
-        <v>0.9079972623668086</v>
+        <v>1.568032211659832</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8142,13 +8142,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1395910111746119</v>
+        <v>0.09883987210482476</v>
       </c>
       <c r="C84">
-        <v>-31260.3755901913</v>
+        <v>-3157.027293805382</v>
       </c>
       <c r="D84">
-        <v>36631.10240905143</v>
+        <v>64734.45070543734</v>
       </c>
       <c r="E84">
         <v>38274.20726845892</v>
@@ -8175,45 +8175,45 @@
         <v>8297</v>
       </c>
       <c r="M84">
-        <v>9250.503770100871</v>
+        <v>5356.670632342599</v>
       </c>
       <c r="N84">
-        <v>-953.5037701008714</v>
+        <v>2940.329367657401</v>
       </c>
       <c r="O84">
-        <v>-139.2115504347272</v>
+        <v>429.2880876779806</v>
       </c>
       <c r="P84">
-        <v>-814.2922196661442</v>
+        <v>2511.041279979421</v>
       </c>
       <c r="Q84">
-        <v>5708.707780333856</v>
+        <v>9034.041279979421</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.2572723403744973</v>
+        <v>0.2542147116934709</v>
       </c>
       <c r="T84">
-        <v>4.880747862858073</v>
+        <v>4.813272787378082</v>
       </c>
       <c r="U84">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V84">
-        <v>0.1309509222530473</v>
+        <v>0.146</v>
       </c>
       <c r="W84">
-        <v>0.1137585242770761</v>
+        <v>0.0647332</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y84">
-        <v>0.8969241250208718</v>
+        <v>1.548909867615199</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8224,13 +8224,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1404420111746119</v>
+        <v>0.09896698369060082</v>
       </c>
       <c r="C85">
-        <v>-32451.56505607803</v>
+        <v>-4173.605078579872</v>
       </c>
       <c r="D85">
-        <v>36301.72365047253</v>
+        <v>64579.6836279707</v>
       </c>
       <c r="E85">
         <v>39136.01797576676</v>
@@ -8257,45 +8257,45 @@
         <v>8297</v>
       </c>
       <c r="M85">
-        <v>9363.314791687468</v>
+        <v>5421.995883956533</v>
       </c>
       <c r="N85">
-        <v>-1066.314791687468</v>
+        <v>2875.004116043467</v>
       </c>
       <c r="O85">
-        <v>-155.6819595863703</v>
+        <v>419.7506009423461</v>
       </c>
       <c r="P85">
-        <v>-910.6328321010974</v>
+        <v>2455.253515101121</v>
       </c>
       <c r="Q85">
-        <v>5612.367167898903</v>
+        <v>8978.253515101122</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.2697118898082912</v>
+        <v>0.2661083981800049</v>
       </c>
       <c r="T85">
-        <v>5.167850678320313</v>
+        <v>5.087953768591339</v>
       </c>
       <c r="U85">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V85">
-        <v>0.1293732002981913</v>
+        <v>0.146</v>
       </c>
       <c r="W85">
-        <v>0.1139650480809667</v>
+        <v>0.0647332</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y85">
-        <v>0.8861178102615842</v>
+        <v>1.530248302945136</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8306,13 +8306,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.1412930111746119</v>
+        <v>0.09909409527637689</v>
       </c>
       <c r="C86">
-        <v>-33636.88390755846</v>
+        <v>-5189.444594375716</v>
       </c>
       <c r="D86">
-        <v>35978.21550629993</v>
+        <v>64425.65481948267</v>
       </c>
       <c r="E86">
         <v>39997.82868307459</v>
@@ -8339,45 +8339,45 @@
         <v>8297</v>
       </c>
       <c r="M86">
-        <v>9476.125813274062</v>
+        <v>5487.321135570466</v>
       </c>
       <c r="N86">
-        <v>-1179.125813274062</v>
+        <v>2809.678864429534</v>
       </c>
       <c r="O86">
-        <v>-172.1523687380131</v>
+        <v>410.2131142067119</v>
       </c>
       <c r="P86">
-        <v>-1006.973444536049</v>
+        <v>2399.465750222822</v>
       </c>
       <c r="Q86">
-        <v>5516.026555463951</v>
+        <v>8922.465750222822</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.2837063829213093</v>
+        <v>0.2794887954773555</v>
       </c>
       <c r="T86">
-        <v>5.49084134571533</v>
+        <v>5.396969872456249</v>
       </c>
       <c r="U86">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V86">
-        <v>0.1278330431517843</v>
+        <v>0.146</v>
       </c>
       <c r="W86">
-        <v>0.1141666546514314</v>
+        <v>0.0647332</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y86">
-        <v>0.8755687887108512</v>
+        <v>1.512031061243409</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8388,13 +8388,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.1421440111746119</v>
+        <v>0.109528986862153</v>
       </c>
       <c r="C87">
-        <v>-34816.487708828</v>
+        <v>-16600.21828516982</v>
       </c>
       <c r="D87">
-        <v>35660.42241233823</v>
+        <v>53876.69183599641</v>
       </c>
       <c r="E87">
         <v>40859.63939038244</v>
@@ -8421,45 +8421,45 @@
         <v>8297</v>
       </c>
       <c r="M87">
-        <v>9588.936834860659</v>
+        <v>6592.851910904961</v>
       </c>
       <c r="N87">
-        <v>-1291.936834860659</v>
+        <v>1704.148089095039</v>
       </c>
       <c r="O87">
-        <v>-188.6227778896561</v>
+        <v>248.8056210078757</v>
       </c>
       <c r="P87">
-        <v>-1103.314056971002</v>
+        <v>1455.342468087163</v>
       </c>
       <c r="Q87">
-        <v>5419.685943028998</v>
+        <v>7978.342468087163</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.2995668084493966</v>
+        <v>0.2946532457476863</v>
       </c>
       <c r="T87">
-        <v>5.856897435429686</v>
+        <v>5.747188123503149</v>
       </c>
       <c r="U87">
-        <v>0.1309</v>
+        <v>0.09</v>
       </c>
       <c r="V87">
-        <v>0.1263291249970574</v>
+        <v>0.146</v>
       </c>
       <c r="W87">
-        <v>0.1143635175378852</v>
+        <v>0.07686</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y87">
-        <v>0.8652679794318999</v>
+        <v>1.258484205640396</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8470,13 +8470,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.1429950111746119</v>
+        <v>0.1319179440563445</v>
       </c>
       <c r="C88">
-        <v>-35990.52657585465</v>
+        <v>-31468.90015618732</v>
       </c>
       <c r="D88">
-        <v>35348.19425261941</v>
+        <v>39869.82067228674</v>
       </c>
       <c r="E88">
         <v>41721.45009769026</v>
@@ -8503,37 +8503,37 @@
         <v>8297</v>
       </c>
       <c r="M88">
-        <v>9701.747856447253</v>
+        <v>8790.124490257025</v>
       </c>
       <c r="N88">
-        <v>-1404.747856447253</v>
+        <v>-493.1244902570252</v>
       </c>
       <c r="O88">
-        <v>-205.0931870412989</v>
+        <v>-71.99617557752568</v>
       </c>
       <c r="P88">
-        <v>-1199.654669405954</v>
+        <v>-421.1283146794995</v>
       </c>
       <c r="Q88">
-        <v>5323.345330594046</v>
+        <v>6101.871685320501</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.317693009052925</v>
+        <v>0.3141282439224437</v>
       </c>
       <c r="T88">
-        <v>6.275247252246092</v>
+        <v>6.196957134467523</v>
       </c>
       <c r="U88">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V88">
-        <v>0.1248601816831381</v>
+        <v>0.1378094248087924</v>
       </c>
       <c r="W88">
-        <v>0.1145558022176772</v>
+        <v>0.1022558022176772</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8552067238571105</v>
+        <v>0.9439001699232356</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8552,13 +8552,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.1438460111746119</v>
+        <v>0.1326459440563445</v>
       </c>
       <c r="C89">
-        <v>-37159.14541282121</v>
+        <v>-32664.92600462591</v>
       </c>
       <c r="D89">
-        <v>35041.3861229607</v>
+        <v>39535.605531156</v>
       </c>
       <c r="E89">
         <v>42583.26080499811</v>
@@ -8585,37 +8585,37 @@
         <v>8297</v>
       </c>
       <c r="M89">
-        <v>9814.558878033851</v>
+        <v>8892.335240143735</v>
       </c>
       <c r="N89">
-        <v>-1517.558878033851</v>
+        <v>-595.3352401437351</v>
       </c>
       <c r="O89">
-        <v>-221.5635961929423</v>
+        <v>-86.91894506098531</v>
       </c>
       <c r="P89">
-        <v>-1295.995281840909</v>
+        <v>-508.4162950827497</v>
       </c>
       <c r="Q89">
-        <v>5227.004718159091</v>
+        <v>6014.583704917251</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.33860785590315</v>
+        <v>0.3347688780703239</v>
       </c>
       <c r="T89">
-        <v>6.757958579341945</v>
+        <v>6.673646144811178</v>
       </c>
       <c r="U89">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V89">
-        <v>0.1234250071810331</v>
+        <v>0.1362254084316798</v>
       </c>
       <c r="W89">
-        <v>0.1147436665600028</v>
+        <v>0.1024436665600028</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8453767615139252</v>
+        <v>0.9330507426827386</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8634,13 +8634,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.1446970111746119</v>
+        <v>0.1333739440563445</v>
       </c>
       <c r="C90">
-        <v>-38322.4841363599</v>
+        <v>-33855.39520889678</v>
       </c>
       <c r="D90">
-        <v>34739.85810672985</v>
+        <v>39206.94703419297</v>
       </c>
       <c r="E90">
         <v>43445.07151230595</v>
@@ -8667,37 +8667,37 @@
         <v>8297</v>
       </c>
       <c r="M90">
-        <v>9927.369899620448</v>
+        <v>8994.545990030445</v>
       </c>
       <c r="N90">
-        <v>-1630.369899620448</v>
+        <v>-697.545990030445</v>
       </c>
       <c r="O90">
-        <v>-238.0340053445853</v>
+        <v>-101.841714544445</v>
       </c>
       <c r="P90">
-        <v>-1392.335894275862</v>
+        <v>-595.704275486</v>
       </c>
       <c r="Q90">
-        <v>5130.664105724138</v>
+        <v>5927.295724514</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.3630085105617459</v>
+        <v>0.3588496179095176</v>
       </c>
       <c r="T90">
-        <v>7.321121794287109</v>
+        <v>7.229783323545444</v>
       </c>
       <c r="U90">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V90">
-        <v>0.1220224502812486</v>
+        <v>0.1346773924267743</v>
       </c>
       <c r="W90">
-        <v>0.1149272612581845</v>
+        <v>0.1026272612581846</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8357702074058123</v>
+        <v>0.922447893334071</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8716,13 +8716,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.1455480111746119</v>
+        <v>0.1341019440563445</v>
       </c>
       <c r="C91">
-        <v>-39480.67788830884</v>
+        <v>-35040.44520324319</v>
       </c>
       <c r="D91">
-        <v>34443.47506208875</v>
+        <v>38883.7077471544</v>
       </c>
       <c r="E91">
         <v>44306.88221961379</v>
@@ -8749,37 +8749,37 @@
         <v>8297</v>
       </c>
       <c r="M91">
-        <v>10040.18092120704</v>
+        <v>9096.756739917155</v>
       </c>
       <c r="N91">
-        <v>-1743.180921207044</v>
+        <v>-799.7567399171548</v>
       </c>
       <c r="O91">
-        <v>-254.5044144962284</v>
+        <v>-116.7644840279046</v>
       </c>
       <c r="P91">
-        <v>-1488.676506710815</v>
+        <v>-682.9922558892503</v>
       </c>
       <c r="Q91">
-        <v>5034.323493289185</v>
+        <v>5840.00774411075</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.3918456478855409</v>
+        <v>0.3873086740831101</v>
       </c>
       <c r="T91">
-        <v>7.986678321040483</v>
+        <v>7.887036352958667</v>
       </c>
       <c r="U91">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V91">
-        <v>0.1206514115140435</v>
+        <v>0.1331641632983836</v>
       </c>
       <c r="W91">
-        <v>0.1151067302328117</v>
+        <v>0.1028067302328117</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8263795309181066</v>
+        <v>0.9120833102629017</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8798,13 +8798,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.1463990111746119</v>
+        <v>0.1348299440563445</v>
       </c>
       <c r="C92">
-        <v>-40633.85723766984</v>
+        <v>-36220.20892669594</v>
       </c>
       <c r="D92">
-        <v>34152.10642003558</v>
+        <v>38565.75473100948</v>
       </c>
       <c r="E92">
         <v>45168.69292692162</v>
@@ -8831,37 +8831,37 @@
         <v>8297</v>
       </c>
       <c r="M92">
-        <v>10152.99194279364</v>
+        <v>9198.967489803863</v>
       </c>
       <c r="N92">
-        <v>-1855.991942793638</v>
+        <v>-901.9674898038629</v>
       </c>
       <c r="O92">
-        <v>-270.9748236478712</v>
+        <v>-131.687253511364</v>
       </c>
       <c r="P92">
-        <v>-1585.017119145767</v>
+        <v>-770.2802362924989</v>
       </c>
       <c r="Q92">
-        <v>4937.982880854233</v>
+        <v>5752.719763707501</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.4264502126740951</v>
+        <v>0.4214595414914211</v>
       </c>
       <c r="T92">
-        <v>8.78534615314453</v>
+        <v>8.675739988254533</v>
       </c>
       <c r="U92">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V92">
-        <v>0.1193108402749986</v>
+        <v>0.1316845614839572</v>
       </c>
       <c r="W92">
-        <v>0.1152822110080027</v>
+        <v>0.1029822110080027</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8171975361301277</v>
+        <v>0.9019490512599807</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8880,13 +8880,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.1472500111746119</v>
+        <v>0.1355579440563445</v>
       </c>
       <c r="C93">
-        <v>-41782.14837240146</v>
+        <v>-37394.81500537002</v>
       </c>
       <c r="D93">
-        <v>33865.6259926118</v>
+        <v>38252.95935964325</v>
       </c>
       <c r="E93">
         <v>46030.50363422946</v>
@@ -8913,37 +8913,37 @@
         <v>8297</v>
       </c>
       <c r="M93">
-        <v>10265.80296438023</v>
+        <v>9301.178239690573</v>
       </c>
       <c r="N93">
-        <v>-1968.802964380235</v>
+        <v>-1004.178239690573</v>
       </c>
       <c r="O93">
-        <v>-287.4452327995143</v>
+        <v>-146.6100229948236</v>
       </c>
       <c r="P93">
-        <v>-1681.35773158072</v>
+        <v>-857.5682166957492</v>
       </c>
       <c r="Q93">
-        <v>4841.642268419279</v>
+        <v>5665.431783304251</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.4687446807489946</v>
+        <v>0.4631994905460236</v>
       </c>
       <c r="T93">
-        <v>9.761495725716147</v>
+        <v>9.639711098060594</v>
       </c>
       <c r="U93">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V93">
-        <v>0.1179997321401085</v>
+        <v>0.1302374783907269</v>
       </c>
       <c r="W93">
-        <v>0.1154538350628598</v>
+        <v>0.1031538350628598</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.808217343425401</v>
+        <v>0.8920375232241566</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8962,13 +8962,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2280105266969046</v>
+        <v>0.1362859440563445</v>
       </c>
       <c r="C94">
-        <v>-57654.09852241004</v>
+        <v>-38564.38792596129</v>
       </c>
       <c r="D94">
-        <v>18855.48654991107</v>
+        <v>37945.19714635982</v>
       </c>
       <c r="E94">
         <v>46892.31434153731</v>
@@ -8995,45 +8995,45 @@
         <v>8297</v>
       </c>
       <c r="M94">
-        <v>17110.04505860689</v>
+        <v>9403.388989577285</v>
       </c>
       <c r="N94">
-        <v>-8813.045058606895</v>
+        <v>-1106.388989577285</v>
       </c>
       <c r="O94">
-        <v>-1286.704578556607</v>
+        <v>-161.5327924782835</v>
       </c>
       <c r="P94">
-        <v>-7526.340480050289</v>
+        <v>-944.856197099001</v>
       </c>
       <c r="Q94">
-        <v>-1003.340480050289</v>
+        <v>5578.143802900999</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.5441317098712769</v>
+        <v>0.5153744268642766</v>
       </c>
       <c r="T94">
-        <v>11.50141632537567</v>
+        <v>10.84467498531817</v>
       </c>
       <c r="U94">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V94">
-        <v>0.07079829397589146</v>
+        <v>0.1288218536256102</v>
       </c>
       <c r="W94">
-        <v>0.2005217281600027</v>
+        <v>0.1033217281600026</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y94">
-        <v>0.4849198217526812</v>
+        <v>0.8823414631891113</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9044,13 +9044,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2297105266969046</v>
+        <v>0.1370139440563445</v>
       </c>
       <c r="C95">
-        <v>-58690.20228248955</v>
+        <v>-39729.04820093486</v>
       </c>
       <c r="D95">
-        <v>18681.1934971394</v>
+        <v>37642.34757869409</v>
       </c>
       <c r="E95">
         <v>47754.12504884515</v>
@@ -9077,45 +9077,45 @@
         <v>8297</v>
       </c>
       <c r="M95">
-        <v>17296.02380924393</v>
+        <v>9505.599739463994</v>
       </c>
       <c r="N95">
-        <v>-8999.023809243929</v>
+        <v>-1208.599739463994</v>
       </c>
       <c r="O95">
-        <v>-1313.857476149613</v>
+        <v>-176.4555619617432</v>
       </c>
       <c r="P95">
-        <v>-7685.166333094316</v>
+        <v>-1032.144177502251</v>
       </c>
       <c r="Q95">
-        <v>-1162.166333094316</v>
+        <v>5490.855822497749</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.6153219541386021</v>
+        <v>0.5824564878448877</v>
       </c>
       <c r="T95">
-        <v>13.14447580042934</v>
+        <v>12.39391426893506</v>
       </c>
       <c r="U95">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V95">
-        <v>0.07003702199765606</v>
+        <v>0.1274366724038295</v>
       </c>
       <c r="W95">
-        <v>0.2006860106529058</v>
+        <v>0.1034860106529058</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y95">
-        <v>0.4797056301209319</v>
+        <v>0.8728539205741745</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9126,13 +9126,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2314105266969046</v>
+        <v>0.1377419440563445</v>
       </c>
       <c r="C96">
-        <v>-59723.11335522545</v>
+        <v>-40888.91252586574</v>
       </c>
       <c r="D96">
-        <v>18510.09313171133</v>
+        <v>37344.29396107104</v>
       </c>
       <c r="E96">
         <v>48615.93575615298</v>
@@ -9159,45 +9159,45 @@
         <v>8297</v>
       </c>
       <c r="M96">
-        <v>17482.00255988096</v>
+        <v>9607.810489350702</v>
       </c>
       <c r="N96">
-        <v>-9185.002559880959</v>
+        <v>-1310.810489350702</v>
       </c>
       <c r="O96">
-        <v>-1341.01037374262</v>
+        <v>-191.3783314452025</v>
       </c>
       <c r="P96">
-        <v>-7843.992186138339</v>
+        <v>-1119.4321579055</v>
       </c>
       <c r="Q96">
-        <v>-1320.992186138339</v>
+        <v>5403.567842094501</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.7102422798283693</v>
+        <v>0.6718992358190358</v>
       </c>
       <c r="T96">
-        <v>15.33522176716757</v>
+        <v>14.4595666470909</v>
       </c>
       <c r="U96">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V96">
-        <v>0.06929194729555334</v>
+        <v>0.1260809631229377</v>
       </c>
       <c r="W96">
-        <v>0.2008467977736196</v>
+        <v>0.1036467977736196</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y96">
-        <v>0.4746023787366668</v>
+        <v>0.8635682405680665</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9208,13 +9208,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2331105266969046</v>
+        <v>0.1384699440563446</v>
       </c>
       <c r="C97">
-        <v>-60752.91866955732</v>
+        <v>-42044.09392936317</v>
       </c>
       <c r="D97">
-        <v>18342.09852468731</v>
+        <v>37050.92326488145</v>
       </c>
       <c r="E97">
         <v>49477.74646346082</v>
@@ -9241,45 +9241,45 @@
         <v>8297</v>
       </c>
       <c r="M97">
-        <v>17667.98131051799</v>
+        <v>9710.021239237412</v>
       </c>
       <c r="N97">
-        <v>-9370.981310517989</v>
+        <v>-1413.021239237412</v>
       </c>
       <c r="O97">
-        <v>-1368.163271335626</v>
+        <v>-206.3011009286622</v>
       </c>
       <c r="P97">
-        <v>-8002.818039182363</v>
+        <v>-1206.72013830875</v>
       </c>
       <c r="Q97">
-        <v>-1479.818039182363</v>
+        <v>5316.27986169125</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.8431307357940435</v>
+        <v>0.7971190829828433</v>
       </c>
       <c r="T97">
-        <v>18.40226612060109</v>
+        <v>17.35147997650909</v>
       </c>
       <c r="U97">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V97">
-        <v>0.06856255837665277</v>
+        <v>0.1247537950900647</v>
       </c>
       <c r="W97">
-        <v>0.2010041999023184</v>
+        <v>0.1038041999023183</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y97">
-        <v>0.4696065642236492</v>
+        <v>0.8544780485620869</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9290,13 +9290,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2348105266969046</v>
+        <v>0.1391979440563445</v>
       </c>
       <c r="C98">
-        <v>-61779.70202699679</v>
+        <v>-43194.70191598328</v>
       </c>
       <c r="D98">
-        <v>18177.12587455565</v>
+        <v>36762.12598556917</v>
       </c>
       <c r="E98">
         <v>50339.55717076865</v>
@@ -9323,45 +9323,45 @@
         <v>8297</v>
       </c>
       <c r="M98">
-        <v>17853.96006115502</v>
+        <v>9812.23198912412</v>
       </c>
       <c r="N98">
-        <v>-9556.96006115502</v>
+        <v>-1515.23198912412</v>
       </c>
       <c r="O98">
-        <v>-1395.316168928633</v>
+        <v>-221.2238704121216</v>
       </c>
       <c r="P98">
-        <v>-8161.643892226387</v>
+        <v>-1294.008118711999</v>
       </c>
       <c r="Q98">
-        <v>-1638.643892226387</v>
+        <v>5228.991881288001</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>1.042463419742552</v>
+        <v>0.9849488537285519</v>
       </c>
       <c r="T98">
-        <v>23.00283265075131</v>
+        <v>21.68934997063631</v>
       </c>
       <c r="U98">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V98">
-        <v>0.06784836506022932</v>
+        <v>0.1234542763912098</v>
       </c>
       <c r="W98">
-        <v>0.2011583228200025</v>
+        <v>0.1039583228200025</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y98">
-        <v>0.4647148291796529</v>
+        <v>0.8455772355562319</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9372,13 +9372,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2365105266969045</v>
+        <v>0.1399259440563445</v>
       </c>
       <c r="C99">
-        <v>-62803.54424101772</v>
+        <v>-44340.84260250996</v>
       </c>
       <c r="D99">
-        <v>18015.09436784257</v>
+        <v>36477.79600635033</v>
       </c>
       <c r="E99">
         <v>51201.36787807649</v>
@@ -9405,45 +9405,45 @@
         <v>8297</v>
       </c>
       <c r="M99">
-        <v>18039.93881179205</v>
+        <v>9914.44273901083</v>
       </c>
       <c r="N99">
-        <v>-9742.938811792053</v>
+        <v>-1617.44273901083</v>
       </c>
       <c r="O99">
-        <v>-1422.46906652164</v>
+        <v>-236.1466398955812</v>
       </c>
       <c r="P99">
-        <v>-8320.469745270413</v>
+        <v>-1381.296099115249</v>
       </c>
       <c r="Q99">
-        <v>-1797.469745270413</v>
+        <v>5141.703900884751</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.374684559656737</v>
+        <v>1.297998471638069</v>
       </c>
       <c r="T99">
-        <v>30.67044353433509</v>
+        <v>28.91913329418175</v>
       </c>
       <c r="U99">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V99">
-        <v>0.06714889737919602</v>
+        <v>0.1221815518923314</v>
       </c>
       <c r="W99">
-        <v>0.2013092679455695</v>
+        <v>0.1041092679455695</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y99">
-        <v>0.4599239546520275</v>
+        <v>0.8368599444680233</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9454,13 +9454,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2382105266969046</v>
+        <v>0.1406539440563445</v>
       </c>
       <c r="C100">
-        <v>-63824.52326905666</v>
+        <v>-45482.61884795978</v>
       </c>
       <c r="D100">
-        <v>17855.92604711147</v>
+        <v>36197.83046820835</v>
       </c>
       <c r="E100">
         <v>52063.17858538433</v>
@@ -9487,45 +9487,45 @@
         <v>8297</v>
       </c>
       <c r="M100">
-        <v>18225.91756242908</v>
+        <v>10016.65348889754</v>
       </c>
       <c r="N100">
-        <v>-9928.917562429084</v>
+        <v>-1719.653488897542</v>
       </c>
       <c r="O100">
-        <v>-1449.621964114646</v>
+        <v>-251.0694093790411</v>
       </c>
       <c r="P100">
-        <v>-8479.295598314438</v>
+        <v>-1468.584079518501</v>
       </c>
       <c r="Q100">
-        <v>-1956.295598314438</v>
+        <v>5054.415920481499</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>2.039126839485105</v>
+        <v>1.924097707457104</v>
       </c>
       <c r="T100">
-        <v>46.00566530150263</v>
+        <v>43.37869994127263</v>
       </c>
       <c r="U100">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V100">
-        <v>0.06646370454879606</v>
+        <v>0.1209348013628178</v>
       </c>
       <c r="W100">
-        <v>0.2014571325583698</v>
+        <v>0.1042571325583698</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y100">
-        <v>0.4552308530739456</v>
+        <v>0.8283205572795739</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9536,13 +9536,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2399105266969045</v>
+        <v>0.1413819440563445</v>
       </c>
       <c r="C101">
-        <v>-64842.7143375774</v>
+        <v>-46620.13037764595</v>
       </c>
       <c r="D101">
-        <v>17699.54568589856</v>
+        <v>35922.12964583001</v>
       </c>
       <c r="E101">
         <v>52924.98929269216</v>
@@ -9569,45 +9569,45 @@
         <v>8297</v>
       </c>
       <c r="M101">
-        <v>18411.89631306611</v>
+        <v>10118.86423878425</v>
       </c>
       <c r="N101">
-        <v>-10114.89631306611</v>
+        <v>-1821.86423878425</v>
       </c>
       <c r="O101">
-        <v>-1476.774861707652</v>
+        <v>-265.9921788625005</v>
       </c>
       <c r="P101">
-        <v>-8638.121451358462</v>
+        <v>-1555.872059921749</v>
       </c>
       <c r="Q101">
-        <v>-2115.121451358462</v>
+        <v>4967.127940078251</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>4.032453678970209</v>
+        <v>3.802395414914208</v>
       </c>
       <c r="T101">
-        <v>92.01133060300525</v>
+        <v>86.75739988254524</v>
       </c>
       <c r="U101">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V101">
-        <v>0.06579235399779812</v>
+        <v>0.1197132377126883</v>
       </c>
       <c r="W101">
-        <v>0.2016020100072752</v>
+        <v>0.1044020100072752</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y101">
-        <v>0.4506325616287543</v>
+        <v>0.8199536829636187</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/switzerland/switzerland_metals_mining.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_metals_mining.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.0884167220711873</v>
+        <v>0.08832606365696336</v>
       </c>
       <c r="C2">
-        <v>83344.12997440589</v>
+        <v>82654.07483565883</v>
       </c>
       <c r="D2">
-        <v>80567.12997440589</v>
+        <v>80738.88554296667</v>
       </c>
       <c r="E2">
-        <v>-32394.2707307838</v>
+        <v>-31532.46002347596</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>861.810707307838</v>
       </c>
       <c r="G2">
         <v>2777</v>
@@ -1451,28 +1451,28 @@
         <v>8297</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>43.34907857758425</v>
       </c>
       <c r="N2">
-        <v>8297</v>
+        <v>8253.650921422415</v>
       </c>
       <c r="O2">
-        <v>1211.362</v>
+        <v>1205.033034527672</v>
       </c>
       <c r="P2">
-        <v>7085.638</v>
+        <v>7048.617886894743</v>
       </c>
       <c r="Q2">
-        <v>13608.638</v>
+        <v>13571.61788689474</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.0884167220711873</v>
+        <v>0.0887843451080438</v>
       </c>
       <c r="T2">
-        <v>0.9842199092652958</v>
+        <v>0.9927100486846145</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>191.3996853508754</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08832606365696336</v>
+        <v>0.08823540524273943</v>
       </c>
       <c r="C3">
-        <v>82654.07483565883</v>
+        <v>81964.75356936523</v>
       </c>
       <c r="D3">
-        <v>80738.88554296667</v>
+        <v>80911.3749839809</v>
       </c>
       <c r="E3">
-        <v>-31532.46002347596</v>
+        <v>-30670.64931616812</v>
       </c>
       <c r="F3">
-        <v>861.810707307838</v>
+        <v>1723.621414615676</v>
       </c>
       <c r="G3">
         <v>2777</v>
@@ -1533,28 +1533,28 @@
         <v>8297</v>
       </c>
       <c r="M3">
-        <v>43.34907857758425</v>
+        <v>86.6981571551685</v>
       </c>
       <c r="N3">
-        <v>8253.650921422415</v>
+        <v>8210.301842844832</v>
       </c>
       <c r="O3">
-        <v>1205.033034527672</v>
+        <v>1198.704069055345</v>
       </c>
       <c r="P3">
-        <v>7048.617886894743</v>
+        <v>7011.597773789486</v>
       </c>
       <c r="Q3">
-        <v>13571.61788689474</v>
+        <v>13534.59777378949</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.0887843451080438</v>
+        <v>0.08915947065585655</v>
       </c>
       <c r="T3">
-        <v>0.9927100486846145</v>
+        <v>1.001373456255348</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>191.3996853508754</v>
+        <v>95.69984267543772</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08823540524273943</v>
+        <v>0.08814474682851549</v>
       </c>
       <c r="C4">
-        <v>81964.75356936523</v>
+        <v>81276.17088910009</v>
       </c>
       <c r="D4">
-        <v>80911.3749839809</v>
+        <v>81084.6030110236</v>
       </c>
       <c r="E4">
-        <v>-30670.64931616812</v>
+        <v>-29808.83860886028</v>
       </c>
       <c r="F4">
-        <v>1723.621414615676</v>
+        <v>2585.432121923514</v>
       </c>
       <c r="G4">
         <v>2777</v>
@@ -1615,28 +1615,28 @@
         <v>8297</v>
       </c>
       <c r="M4">
-        <v>86.6981571551685</v>
+        <v>130.0472357327527</v>
       </c>
       <c r="N4">
-        <v>8210.301842844832</v>
+        <v>8166.952764267247</v>
       </c>
       <c r="O4">
-        <v>1198.704069055345</v>
+        <v>1192.375103583018</v>
       </c>
       <c r="P4">
-        <v>7011.597773789486</v>
+        <v>6974.577660684229</v>
       </c>
       <c r="Q4">
-        <v>13534.59777378949</v>
+        <v>13497.57766068423</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08915947065585655</v>
+        <v>0.08954233075104689</v>
       </c>
       <c r="T4">
-        <v>1.001373456255348</v>
+        <v>1.010215490786303</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>95.69984267543772</v>
+        <v>63.79989511695848</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08814474682851549</v>
+        <v>0.08805408841429156</v>
       </c>
       <c r="C5">
-        <v>81276.17088910009</v>
+        <v>80588.33154889125</v>
       </c>
       <c r="D5">
-        <v>81084.6030110236</v>
+        <v>81258.5743781226</v>
       </c>
       <c r="E5">
-        <v>-29808.83860886028</v>
+        <v>-28947.02790155244</v>
       </c>
       <c r="F5">
-        <v>2585.432121923514</v>
+        <v>3447.242829231352</v>
       </c>
       <c r="G5">
         <v>2777</v>
@@ -1697,28 +1697,28 @@
         <v>8297</v>
       </c>
       <c r="M5">
-        <v>130.0472357327527</v>
+        <v>173.396314310337</v>
       </c>
       <c r="N5">
-        <v>8166.952764267247</v>
+        <v>8123.603685689663</v>
       </c>
       <c r="O5">
-        <v>1192.375103583018</v>
+        <v>1186.046138110691</v>
       </c>
       <c r="P5">
-        <v>6974.577660684229</v>
+        <v>6937.557547578972</v>
       </c>
       <c r="Q5">
-        <v>13497.57766068423</v>
+        <v>13460.55754757897</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08954233075104689</v>
+        <v>0.08993316709822037</v>
       </c>
       <c r="T5">
-        <v>1.010215490786303</v>
+        <v>1.019241734369986</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>63.79989511695848</v>
+        <v>47.84992133771885</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08805408841429156</v>
+        <v>0.08796343000006762</v>
       </c>
       <c r="C6">
-        <v>80588.33154889125</v>
+        <v>79901.24034365444</v>
       </c>
       <c r="D6">
-        <v>81258.5743781226</v>
+        <v>81433.29388019363</v>
       </c>
       <c r="E6">
-        <v>-28947.02790155244</v>
+        <v>-28085.2171942446</v>
       </c>
       <c r="F6">
-        <v>3447.242829231352</v>
+        <v>4309.053536539191</v>
       </c>
       <c r="G6">
         <v>2777</v>
@@ -1779,28 +1779,28 @@
         <v>8297</v>
       </c>
       <c r="M6">
-        <v>173.396314310337</v>
+        <v>216.7453928879213</v>
       </c>
       <c r="N6">
-        <v>8123.603685689663</v>
+        <v>8080.254607112079</v>
       </c>
       <c r="O6">
-        <v>1186.046138110691</v>
+        <v>1179.717172638363</v>
       </c>
       <c r="P6">
-        <v>6937.557547578972</v>
+        <v>6900.537434473716</v>
       </c>
       <c r="Q6">
-        <v>13460.55754757897</v>
+        <v>13423.53743447372</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08993316709822037</v>
+        <v>0.09033223157901855</v>
       </c>
       <c r="T6">
-        <v>1.019241734369986</v>
+        <v>1.028458004134378</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>47.84992133771885</v>
+        <v>38.27993707017508</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08796343000006762</v>
+        <v>0.08787277158584368</v>
       </c>
       <c r="C7">
-        <v>79901.24034365444</v>
+        <v>79214.90210963368</v>
       </c>
       <c r="D7">
-        <v>81433.29388019363</v>
+        <v>81608.76635348071</v>
       </c>
       <c r="E7">
-        <v>-28085.2171942446</v>
+        <v>-27223.40648693676</v>
       </c>
       <c r="F7">
-        <v>4309.053536539191</v>
+        <v>5170.864243847029</v>
       </c>
       <c r="G7">
         <v>2777</v>
@@ -1861,28 +1861,28 @@
         <v>8297</v>
       </c>
       <c r="M7">
-        <v>216.7453928879213</v>
+        <v>260.0944714655055</v>
       </c>
       <c r="N7">
-        <v>8080.254607112079</v>
+        <v>8036.905528534495</v>
       </c>
       <c r="O7">
-        <v>1179.717172638363</v>
+        <v>1173.388207166036</v>
       </c>
       <c r="P7">
-        <v>6900.537434473716</v>
+        <v>6863.517321368458</v>
       </c>
       <c r="Q7">
-        <v>13423.53743447372</v>
+        <v>13386.51732136846</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09033223157901855</v>
+        <v>0.09073978679345074</v>
       </c>
       <c r="T7">
-        <v>1.028458004134378</v>
+        <v>1.037870364744821</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>38.27993707017508</v>
+        <v>31.89994755847923</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08787277158584368</v>
+        <v>0.08778211317161977</v>
       </c>
       <c r="C8">
-        <v>79214.90210963368</v>
+        <v>78529.32172484753</v>
       </c>
       <c r="D8">
-        <v>81608.76635348071</v>
+        <v>81784.9966760024</v>
       </c>
       <c r="E8">
-        <v>-27223.40648693677</v>
+        <v>-26361.59577962893</v>
       </c>
       <c r="F8">
-        <v>5170.864243847028</v>
+        <v>6032.674951154865</v>
       </c>
       <c r="G8">
         <v>2777</v>
@@ -1943,28 +1943,28 @@
         <v>8297</v>
       </c>
       <c r="M8">
-        <v>260.0944714655055</v>
+        <v>303.4435500430897</v>
       </c>
       <c r="N8">
-        <v>8036.905528534495</v>
+        <v>7993.55644995691</v>
       </c>
       <c r="O8">
-        <v>1173.388207166036</v>
+        <v>1167.059241693709</v>
       </c>
       <c r="P8">
-        <v>6863.517321368458</v>
+        <v>6826.497208263201</v>
       </c>
       <c r="Q8">
-        <v>13386.51732136846</v>
+        <v>13349.4972082632</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09073978679345074</v>
+        <v>0.09115610663615029</v>
       </c>
       <c r="T8">
-        <v>1.037870364744821</v>
+        <v>1.047485141712478</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>31.89994755847924</v>
+        <v>27.3428121929822</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08778211317161977</v>
+        <v>0.08769145475739581</v>
       </c>
       <c r="C9">
-        <v>78529.32172484753</v>
+        <v>77844.50410954132</v>
       </c>
       <c r="D9">
-        <v>81784.9966760024</v>
+        <v>81961.98976800402</v>
       </c>
       <c r="E9">
-        <v>-26361.59577962893</v>
+        <v>-25499.78507232109</v>
       </c>
       <c r="F9">
-        <v>6032.674951154867</v>
+        <v>6894.485658462704</v>
       </c>
       <c r="G9">
         <v>2777</v>
@@ -2025,28 +2025,28 @@
         <v>8297</v>
       </c>
       <c r="M9">
-        <v>303.4435500430898</v>
+        <v>346.792628620674</v>
       </c>
       <c r="N9">
-        <v>7993.55644995691</v>
+        <v>7950.207371379326</v>
       </c>
       <c r="O9">
-        <v>1167.059241693709</v>
+        <v>1160.730276221381</v>
       </c>
       <c r="P9">
-        <v>6826.497208263201</v>
+        <v>6789.477095157945</v>
       </c>
       <c r="Q9">
-        <v>13349.4972082632</v>
+        <v>13312.47709515794</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09115610663615029</v>
+        <v>0.09158147691021284</v>
       </c>
       <c r="T9">
-        <v>1.047485141712478</v>
+        <v>1.057308935570736</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>27.3428121929822</v>
+        <v>23.92496066885943</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08769145475739581</v>
+        <v>0.08760079634317189</v>
       </c>
       <c r="C10">
-        <v>77844.50410954132</v>
+        <v>77160.45422664464</v>
       </c>
       <c r="D10">
-        <v>81961.98976800402</v>
+        <v>82139.75059241518</v>
       </c>
       <c r="E10">
-        <v>-25499.78507232109</v>
+        <v>-24637.97436501325</v>
       </c>
       <c r="F10">
-        <v>6894.485658462704</v>
+        <v>7756.296365770542</v>
       </c>
       <c r="G10">
         <v>2777</v>
@@ -2107,28 +2107,28 @@
         <v>8297</v>
       </c>
       <c r="M10">
-        <v>346.792628620674</v>
+        <v>390.1417071982582</v>
       </c>
       <c r="N10">
-        <v>7950.207371379326</v>
+        <v>7906.858292801742</v>
       </c>
       <c r="O10">
-        <v>1160.730276221381</v>
+        <v>1154.401310749054</v>
       </c>
       <c r="P10">
-        <v>6789.477095157945</v>
+        <v>6752.456982052688</v>
       </c>
       <c r="Q10">
-        <v>13312.47709515794</v>
+        <v>13275.45698205269</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09158147691021284</v>
+        <v>0.09201619598150756</v>
       </c>
       <c r="T10">
-        <v>1.057308935570736</v>
+        <v>1.067348636986318</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>23.92496066885943</v>
+        <v>21.26663170565283</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08760079634317189</v>
+        <v>0.08751013792894798</v>
       </c>
       <c r="C11">
-        <v>77160.45422664464</v>
+        <v>76477.1770822356</v>
       </c>
       <c r="D11">
-        <v>82139.75059241518</v>
+        <v>82318.28415531399</v>
       </c>
       <c r="E11">
-        <v>-24637.97436501325</v>
+        <v>-23776.16365770542</v>
       </c>
       <c r="F11">
-        <v>7756.296365770542</v>
+        <v>8618.107073078379</v>
       </c>
       <c r="G11">
         <v>2777</v>
@@ -2189,28 +2189,28 @@
         <v>8297</v>
       </c>
       <c r="M11">
-        <v>390.1417071982582</v>
+        <v>433.4907857758425</v>
       </c>
       <c r="N11">
-        <v>7906.858292801742</v>
+        <v>7863.509214224157</v>
       </c>
       <c r="O11">
-        <v>1154.401310749054</v>
+        <v>1148.072345276727</v>
       </c>
       <c r="P11">
-        <v>6752.456982052688</v>
+        <v>6715.43686894743</v>
       </c>
       <c r="Q11">
-        <v>13275.45698205269</v>
+        <v>13238.43686894743</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09201619598150756</v>
+        <v>0.09246057547660885</v>
       </c>
       <c r="T11">
-        <v>1.067348636986318</v>
+        <v>1.077611442877803</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>21.26663170565283</v>
+        <v>19.13996853508754</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08751013792894798</v>
+        <v>0.08741947951472402</v>
       </c>
       <c r="C12">
-        <v>76477.1770822356</v>
+        <v>75794.67772601079</v>
       </c>
       <c r="D12">
-        <v>82318.28415531399</v>
+        <v>82497.59550639702</v>
       </c>
       <c r="E12">
-        <v>-23776.16365770542</v>
+        <v>-22914.35295039758</v>
       </c>
       <c r="F12">
-        <v>8618.107073078381</v>
+        <v>9479.917780386219</v>
       </c>
       <c r="G12">
         <v>2777</v>
@@ -2271,28 +2271,28 @@
         <v>8297</v>
       </c>
       <c r="M12">
-        <v>433.4907857758425</v>
+        <v>476.8398643534268</v>
       </c>
       <c r="N12">
-        <v>7863.509214224157</v>
+        <v>7820.160135646574</v>
       </c>
       <c r="O12">
-        <v>1148.072345276727</v>
+        <v>1141.7433798044</v>
       </c>
       <c r="P12">
-        <v>6715.43686894743</v>
+        <v>6678.416755842174</v>
       </c>
       <c r="Q12">
-        <v>13238.43686894743</v>
+        <v>13201.41675584217</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09246057547660885</v>
+        <v>0.09291494102777981</v>
       </c>
       <c r="T12">
-        <v>1.077611442877803</v>
+        <v>1.088104873620781</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>19.13996853508754</v>
+        <v>17.39997139553413</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08741947951472402</v>
+        <v>0.0873288211005001</v>
       </c>
       <c r="C13">
-        <v>75794.67772601079</v>
+        <v>75112.96125176095</v>
       </c>
       <c r="D13">
-        <v>82497.59550639702</v>
+        <v>82677.689739455</v>
       </c>
       <c r="E13">
-        <v>-22914.35295039758</v>
+        <v>-22052.54224308974</v>
       </c>
       <c r="F13">
-        <v>9479.917780386219</v>
+        <v>10341.72848769406</v>
       </c>
       <c r="G13">
         <v>2777</v>
@@ -2353,28 +2353,28 @@
         <v>8297</v>
       </c>
       <c r="M13">
-        <v>476.8398643534268</v>
+        <v>520.188942931011</v>
       </c>
       <c r="N13">
-        <v>7820.160135646574</v>
+        <v>7776.811057068989</v>
       </c>
       <c r="O13">
-        <v>1141.7433798044</v>
+        <v>1135.414414332072</v>
       </c>
       <c r="P13">
-        <v>6678.416755842174</v>
+        <v>6641.396642736916</v>
       </c>
       <c r="Q13">
-        <v>13201.41675584217</v>
+        <v>13164.39664273692</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09291494102777981</v>
+        <v>0.09337963306875011</v>
       </c>
       <c r="T13">
-        <v>1.088104873620781</v>
+        <v>1.0988367914261</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>17.39997139553413</v>
+        <v>15.94997377923962</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0873288211005001</v>
+        <v>0.08723816268627616</v>
       </c>
       <c r="C14">
-        <v>75112.96125176095</v>
+        <v>74432.0327978538</v>
       </c>
       <c r="D14">
-        <v>82677.689739455</v>
+        <v>82858.57199285569</v>
       </c>
       <c r="E14">
-        <v>-22052.54224308974</v>
+        <v>-21190.7315357819</v>
       </c>
       <c r="F14">
-        <v>10341.72848769406</v>
+        <v>11203.53919500189</v>
       </c>
       <c r="G14">
         <v>2777</v>
@@ -2435,28 +2435,28 @@
         <v>8297</v>
       </c>
       <c r="M14">
-        <v>520.188942931011</v>
+        <v>563.5380215085953</v>
       </c>
       <c r="N14">
-        <v>7776.811057068989</v>
+        <v>7733.461978491405</v>
       </c>
       <c r="O14">
-        <v>1135.414414332072</v>
+        <v>1129.085448859745</v>
       </c>
       <c r="P14">
-        <v>6641.396642736916</v>
+        <v>6604.37652963166</v>
       </c>
       <c r="Q14">
-        <v>13164.39664273692</v>
+        <v>13127.37652963166</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09337963306875011</v>
+        <v>0.0938550076853749</v>
       </c>
       <c r="T14">
-        <v>1.0988367914261</v>
+        <v>1.109815419985564</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>15.94997377923962</v>
+        <v>14.72305271929811</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08723816268627616</v>
+        <v>0.08714750427205223</v>
       </c>
       <c r="C15">
-        <v>74432.0327978538</v>
+        <v>73751.89754772243</v>
       </c>
       <c r="D15">
-        <v>82858.57199285569</v>
+        <v>83040.24745003217</v>
       </c>
       <c r="E15">
-        <v>-21190.7315357819</v>
+        <v>-20328.92082847406</v>
       </c>
       <c r="F15">
-        <v>11203.53919500189</v>
+        <v>12065.34990230973</v>
       </c>
       <c r="G15">
         <v>2777</v>
@@ -2517,28 +2517,28 @@
         <v>8297</v>
       </c>
       <c r="M15">
-        <v>563.5380215085953</v>
+        <v>606.8871000861795</v>
       </c>
       <c r="N15">
-        <v>7733.461978491405</v>
+        <v>7690.11289991382</v>
       </c>
       <c r="O15">
-        <v>1129.085448859745</v>
+        <v>1122.756483387418</v>
       </c>
       <c r="P15">
-        <v>6604.37652963166</v>
+        <v>6567.356416526402</v>
       </c>
       <c r="Q15">
-        <v>13127.37652963166</v>
+        <v>13090.3564165264</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.0938550076853749</v>
+        <v>0.09434143752564213</v>
       </c>
       <c r="T15">
-        <v>1.109815419985564</v>
+        <v>1.121049365488271</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>14.72305271929811</v>
+        <v>13.6714060964911</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08714750427205223</v>
+        <v>0.08705684585782829</v>
       </c>
       <c r="C16">
-        <v>73751.89754772243</v>
+        <v>73072.56073036067</v>
       </c>
       <c r="D16">
-        <v>83040.24745003217</v>
+        <v>83222.72133997823</v>
       </c>
       <c r="E16">
-        <v>-20328.92082847406</v>
+        <v>-19467.11012116622</v>
       </c>
       <c r="F16">
-        <v>12065.34990230973</v>
+        <v>12927.16060961757</v>
       </c>
       <c r="G16">
         <v>2777</v>
@@ -2599,28 +2599,28 @@
         <v>8297</v>
       </c>
       <c r="M16">
-        <v>606.8871000861795</v>
+        <v>650.2361786637639</v>
       </c>
       <c r="N16">
-        <v>7690.11289991382</v>
+        <v>7646.763821336236</v>
       </c>
       <c r="O16">
-        <v>1122.756483387418</v>
+        <v>1116.42751791509</v>
       </c>
       <c r="P16">
-        <v>6567.356416526402</v>
+        <v>6530.336303421145</v>
       </c>
       <c r="Q16">
-        <v>13090.3564165264</v>
+        <v>13053.33630342115</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09434143752564213</v>
+        <v>0.09483931277391563</v>
       </c>
       <c r="T16">
-        <v>1.121049365488271</v>
+        <v>1.132547639120454</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>13.6714060964911</v>
+        <v>12.75997902339169</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08705684585782829</v>
+        <v>0.08696618744360435</v>
       </c>
       <c r="C17">
-        <v>73072.56073036067</v>
+        <v>72394.02762082452</v>
       </c>
       <c r="D17">
-        <v>83222.72133997823</v>
+        <v>83405.99893774993</v>
       </c>
       <c r="E17">
-        <v>-19467.11012116622</v>
+        <v>-18605.29941385839</v>
       </c>
       <c r="F17">
-        <v>12927.16060961757</v>
+        <v>13788.97131692541</v>
       </c>
       <c r="G17">
         <v>2777</v>
@@ -2681,28 +2681,28 @@
         <v>8297</v>
       </c>
       <c r="M17">
-        <v>650.2361786637637</v>
+        <v>693.585257241348</v>
       </c>
       <c r="N17">
-        <v>7646.763821336236</v>
+        <v>7603.414742758652</v>
       </c>
       <c r="O17">
-        <v>1116.42751791509</v>
+        <v>1110.098552442763</v>
       </c>
       <c r="P17">
-        <v>6530.336303421145</v>
+        <v>6493.316190315889</v>
       </c>
       <c r="Q17">
-        <v>13053.33630342115</v>
+        <v>13016.31619031589</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09483931277391563</v>
+        <v>0.09534904219476709</v>
       </c>
       <c r="T17">
-        <v>1.132547639120454</v>
+        <v>1.144319681172451</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>12.7599790233917</v>
+        <v>11.96248033442971</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08696618744360435</v>
+        <v>0.08687552902938042</v>
       </c>
       <c r="C18">
-        <v>72394.02762082452</v>
+        <v>71716.30354074064</v>
       </c>
       <c r="D18">
-        <v>83405.99893774993</v>
+        <v>83590.0855649739</v>
       </c>
       <c r="E18">
-        <v>-18605.29941385839</v>
+        <v>-17743.48870655055</v>
       </c>
       <c r="F18">
-        <v>13788.97131692541</v>
+        <v>14650.78202423325</v>
       </c>
       <c r="G18">
         <v>2777</v>
@@ -2763,28 +2763,28 @@
         <v>8297</v>
       </c>
       <c r="M18">
-        <v>693.585257241348</v>
+        <v>736.9343358189323</v>
       </c>
       <c r="N18">
-        <v>7603.414742758652</v>
+        <v>7560.065664181067</v>
       </c>
       <c r="O18">
-        <v>1110.098552442763</v>
+        <v>1103.769586970436</v>
       </c>
       <c r="P18">
-        <v>6493.316190315889</v>
+        <v>6456.296077210632</v>
       </c>
       <c r="Q18">
-        <v>13016.31619031589</v>
+        <v>12979.29607721063</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09534904219476709</v>
+        <v>0.09587105425226557</v>
       </c>
       <c r="T18">
-        <v>1.144319681172451</v>
+        <v>1.156375386888351</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.96248033442971</v>
+        <v>11.25880502063973</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08687552902938042</v>
+        <v>0.08678487061515647</v>
       </c>
       <c r="C19">
-        <v>71716.30354074064</v>
+        <v>71039.39385882152</v>
       </c>
       <c r="D19">
-        <v>83590.0855649739</v>
+        <v>83774.98659036261</v>
       </c>
       <c r="E19">
-        <v>-17743.48870655055</v>
+        <v>-16881.67799924271</v>
       </c>
       <c r="F19">
-        <v>14650.78202423325</v>
+        <v>15512.59273154109</v>
       </c>
       <c r="G19">
         <v>2777</v>
@@ -2845,28 +2845,28 @@
         <v>8297</v>
       </c>
       <c r="M19">
-        <v>736.9343358189323</v>
+        <v>780.2834143965166</v>
       </c>
       <c r="N19">
-        <v>7560.065664181067</v>
+        <v>7516.716585603484</v>
       </c>
       <c r="O19">
-        <v>1103.769586970436</v>
+        <v>1097.440621498109</v>
       </c>
       <c r="P19">
-        <v>6456.296077210632</v>
+        <v>6419.275964105374</v>
       </c>
       <c r="Q19">
-        <v>12979.29607721063</v>
+        <v>12942.27596410537</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09587105425226557</v>
+        <v>0.09640579831116644</v>
       </c>
       <c r="T19">
-        <v>1.156375386888351</v>
+        <v>1.168725134207078</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.25880502063973</v>
+        <v>10.63331585282641</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08678487061515648</v>
+        <v>0.08669421220093257</v>
       </c>
       <c r="C20">
-        <v>71039.39385882148</v>
+        <v>70363.30399138689</v>
       </c>
       <c r="D20">
-        <v>83774.98659036256</v>
+        <v>83960.70743023581</v>
       </c>
       <c r="E20">
-        <v>-16881.67799924271</v>
+        <v>-16019.86729193487</v>
       </c>
       <c r="F20">
-        <v>15512.59273154108</v>
+        <v>16374.40343884892</v>
       </c>
       <c r="G20">
         <v>2777</v>
@@ -2927,28 +2927,28 @@
         <v>8297</v>
       </c>
       <c r="M20">
-        <v>780.2834143965165</v>
+        <v>823.6324929741007</v>
       </c>
       <c r="N20">
-        <v>7516.716585603484</v>
+        <v>7473.3675070259</v>
       </c>
       <c r="O20">
-        <v>1097.440621498109</v>
+        <v>1091.111656025781</v>
       </c>
       <c r="P20">
-        <v>6419.275964105374</v>
+        <v>6382.255851000118</v>
       </c>
       <c r="Q20">
-        <v>12942.27596410537</v>
+        <v>12905.25585100012</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09640579831116644</v>
+        <v>0.09695374592707723</v>
       </c>
       <c r="T20">
-        <v>1.168725134207078</v>
+        <v>1.181379813558366</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>10.63331585282641</v>
+        <v>10.07366765004608</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08669421220093257</v>
+        <v>0.08660355378670864</v>
       </c>
       <c r="C21">
-        <v>70363.30399138689</v>
+        <v>69688.03940289341</v>
       </c>
       <c r="D21">
-        <v>83960.70743023581</v>
+        <v>84147.25354905018</v>
       </c>
       <c r="E21">
-        <v>-16019.86729193487</v>
+        <v>-15158.05658462703</v>
       </c>
       <c r="F21">
-        <v>16374.40343884892</v>
+        <v>17236.21414615676</v>
       </c>
       <c r="G21">
         <v>2777</v>
@@ -3009,28 +3009,28 @@
         <v>8297</v>
       </c>
       <c r="M21">
-        <v>823.6324929741007</v>
+        <v>866.9815715516851</v>
       </c>
       <c r="N21">
-        <v>7473.3675070259</v>
+        <v>7430.018428448315</v>
       </c>
       <c r="O21">
-        <v>1091.111656025781</v>
+        <v>1084.782690553454</v>
       </c>
       <c r="P21">
-        <v>6382.255851000118</v>
+        <v>6345.235737894861</v>
       </c>
       <c r="Q21">
-        <v>12905.25585100012</v>
+        <v>12868.23573789486</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09695374592707723</v>
+        <v>0.09751539223338579</v>
       </c>
       <c r="T21">
-        <v>1.181379813558366</v>
+        <v>1.194350859893436</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>10.07366765004608</v>
+        <v>9.56998426754377</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08660355378670864</v>
+        <v>0.08651289537248469</v>
       </c>
       <c r="C22">
-        <v>69688.03940289341</v>
+        <v>69013.60560647002</v>
       </c>
       <c r="D22">
-        <v>84147.25354905018</v>
+        <v>84334.63045993463</v>
       </c>
       <c r="E22">
-        <v>-15158.05658462703</v>
+        <v>-14296.24587731919</v>
       </c>
       <c r="F22">
-        <v>17236.21414615676</v>
+        <v>18098.0248534646</v>
       </c>
       <c r="G22">
         <v>2777</v>
@@ -3091,28 +3091,28 @@
         <v>8297</v>
       </c>
       <c r="M22">
-        <v>866.9815715516851</v>
+        <v>910.3306501292694</v>
       </c>
       <c r="N22">
-        <v>7430.018428448315</v>
+        <v>7386.669349870731</v>
       </c>
       <c r="O22">
-        <v>1084.782690553454</v>
+        <v>1078.453725081127</v>
       </c>
       <c r="P22">
-        <v>6345.235737894861</v>
+        <v>6308.215624789605</v>
       </c>
       <c r="Q22">
-        <v>12868.23573789486</v>
+        <v>12831.21562478961</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09751539223338579</v>
+        <v>0.09809125743352493</v>
       </c>
       <c r="T22">
-        <v>1.194350859893436</v>
+        <v>1.207650287148382</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>9.56998426754377</v>
+        <v>9.114270730994066</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08651289537248469</v>
+        <v>0.08670405695826076</v>
       </c>
       <c r="C23">
-        <v>69013.60560647004</v>
+        <v>67757.66427023678</v>
       </c>
       <c r="D23">
-        <v>84334.63045993463</v>
+        <v>83940.49983100922</v>
       </c>
       <c r="E23">
-        <v>-14296.2458773192</v>
+        <v>-13434.43517001136</v>
       </c>
       <c r="F23">
-        <v>18098.0248534646</v>
+        <v>18959.83556077244</v>
       </c>
       <c r="G23">
         <v>2777</v>
@@ -3173,45 +3173,45 @@
         <v>8297</v>
       </c>
       <c r="M23">
-        <v>910.3306501292692</v>
+        <v>982.1194820480122</v>
       </c>
       <c r="N23">
-        <v>7386.669349870731</v>
+        <v>7314.880517951988</v>
       </c>
       <c r="O23">
-        <v>1078.453725081127</v>
+        <v>1067.97255562099</v>
       </c>
       <c r="P23">
-        <v>6308.215624789605</v>
+        <v>6246.907962330997</v>
       </c>
       <c r="Q23">
-        <v>12831.21562478961</v>
+        <v>12769.907962331</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09809125743352493</v>
+        <v>0.09868188840802661</v>
       </c>
       <c r="T23">
-        <v>1.207650287148382</v>
+        <v>1.221290725358583</v>
       </c>
       <c r="U23">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V23">
         <v>0.146</v>
       </c>
       <c r="W23">
-        <v>0.0429562</v>
+        <v>0.0442372</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y23">
-        <v>9.114270730994068</v>
+        <v>8.448055609993887</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08670405695826076</v>
+        <v>0.08662620854403683</v>
       </c>
       <c r="C24">
-        <v>67757.66427023678</v>
+        <v>67055.91336358273</v>
       </c>
       <c r="D24">
-        <v>83940.49983100922</v>
+        <v>84100.55963166301</v>
       </c>
       <c r="E24">
-        <v>-13434.43517001136</v>
+        <v>-12572.62446270352</v>
       </c>
       <c r="F24">
-        <v>18959.83556077244</v>
+        <v>19821.64626808028</v>
       </c>
       <c r="G24">
         <v>2777</v>
@@ -3255,28 +3255,28 @@
         <v>8297</v>
       </c>
       <c r="M24">
-        <v>982.1194820480122</v>
+        <v>1026.761276686558</v>
       </c>
       <c r="N24">
-        <v>7314.880517951988</v>
+        <v>7270.238723313441</v>
       </c>
       <c r="O24">
-        <v>1067.97255562099</v>
+        <v>1061.454853603762</v>
       </c>
       <c r="P24">
-        <v>6246.907962330997</v>
+        <v>6208.783869709679</v>
       </c>
       <c r="Q24">
-        <v>12769.907962331</v>
+        <v>12731.78386970968</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09868188840802661</v>
+        <v>0.09928786044680106</v>
       </c>
       <c r="T24">
-        <v>1.221290725358583</v>
+        <v>1.235285460665152</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.448055609993887</v>
+        <v>8.080748844341979</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08662620854403683</v>
+        <v>0.0865483601298129</v>
       </c>
       <c r="C25">
-        <v>67055.91336358273</v>
+        <v>66354.77403499573</v>
       </c>
       <c r="D25">
-        <v>84100.55963166301</v>
+        <v>84261.23101038384</v>
       </c>
       <c r="E25">
-        <v>-12572.62446270352</v>
+        <v>-11710.81375539568</v>
       </c>
       <c r="F25">
-        <v>19821.64626808028</v>
+        <v>20683.45697538812</v>
       </c>
       <c r="G25">
         <v>2777</v>
@@ -3337,28 +3337,28 @@
         <v>8297</v>
       </c>
       <c r="M25">
-        <v>1026.761276686558</v>
+        <v>1071.403071325104</v>
       </c>
       <c r="N25">
-        <v>7270.238723313441</v>
+        <v>7225.596928674896</v>
       </c>
       <c r="O25">
-        <v>1061.454853603762</v>
+        <v>1054.937151586535</v>
       </c>
       <c r="P25">
-        <v>6208.783869709679</v>
+        <v>6170.659777088361</v>
       </c>
       <c r="Q25">
-        <v>12731.78386970968</v>
+        <v>12693.65977708836</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09928786044680106</v>
+        <v>0.09990977911817486</v>
       </c>
       <c r="T25">
-        <v>1.235285460665152</v>
+        <v>1.249648478479789</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.080748844341979</v>
+        <v>7.744050975827729</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.0865483601298129</v>
+        <v>0.08647051171558895</v>
       </c>
       <c r="C26">
-        <v>66354.77403499573</v>
+        <v>65654.24979638511</v>
       </c>
       <c r="D26">
-        <v>84261.23101038384</v>
+        <v>84422.51747908106</v>
       </c>
       <c r="E26">
-        <v>-11710.81375539568</v>
+        <v>-10849.00304808784</v>
       </c>
       <c r="F26">
-        <v>20683.45697538811</v>
+        <v>21545.26768269595</v>
       </c>
       <c r="G26">
         <v>2777</v>
@@ -3419,28 +3419,28 @@
         <v>8297</v>
       </c>
       <c r="M26">
-        <v>1071.403071325104</v>
+        <v>1116.04486596365</v>
       </c>
       <c r="N26">
-        <v>7225.596928674896</v>
+        <v>7180.95513403635</v>
       </c>
       <c r="O26">
-        <v>1054.937151586535</v>
+        <v>1048.419449569307</v>
       </c>
       <c r="P26">
-        <v>6170.659777088361</v>
+        <v>6132.535684467042</v>
       </c>
       <c r="Q26">
-        <v>12693.65977708836</v>
+        <v>12655.53568446704</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09990977911817486</v>
+        <v>0.1005482822874519</v>
       </c>
       <c r="T26">
-        <v>1.249648478479789</v>
+        <v>1.264394510102817</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.744050975827731</v>
+        <v>7.434288936794621</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08647051171558895</v>
+        <v>0.08639266330136502</v>
       </c>
       <c r="C27">
-        <v>65654.24979638511</v>
+        <v>64954.34418660056</v>
       </c>
       <c r="D27">
-        <v>84422.51747908106</v>
+        <v>84584.42257660435</v>
       </c>
       <c r="E27">
-        <v>-10849.00304808784</v>
+        <v>-9987.192340780006</v>
       </c>
       <c r="F27">
-        <v>21545.26768269595</v>
+        <v>22407.07839000379</v>
       </c>
       <c r="G27">
         <v>2777</v>
@@ -3501,28 +3501,28 @@
         <v>8297</v>
       </c>
       <c r="M27">
-        <v>1116.04486596365</v>
+        <v>1160.686660602196</v>
       </c>
       <c r="N27">
-        <v>7180.95513403635</v>
+        <v>7136.313339397804</v>
       </c>
       <c r="O27">
-        <v>1048.419449569307</v>
+        <v>1041.901747552079</v>
       </c>
       <c r="P27">
-        <v>6132.535684467042</v>
+        <v>6094.411591845725</v>
       </c>
       <c r="Q27">
-        <v>12655.53568446704</v>
+        <v>12617.41159184572</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1005482822874519</v>
+        <v>0.1012040422991419</v>
       </c>
       <c r="T27">
-        <v>1.264394510102817</v>
+        <v>1.279539083121061</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.434288936794621</v>
+        <v>7.148354746917905</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08639266330136502</v>
+        <v>0.0863148148871411</v>
       </c>
       <c r="C28">
-        <v>64954.34418660056</v>
+        <v>64255.06077169126</v>
       </c>
       <c r="D28">
-        <v>84584.42257660435</v>
+        <v>84746.94986900288</v>
       </c>
       <c r="E28">
-        <v>-9987.192340780006</v>
+        <v>-9125.381633472167</v>
       </c>
       <c r="F28">
-        <v>22407.07839000379</v>
+        <v>23268.88909731163</v>
       </c>
       <c r="G28">
         <v>2777</v>
@@ -3583,28 +3583,28 @@
         <v>8297</v>
       </c>
       <c r="M28">
-        <v>1160.686660602196</v>
+        <v>1205.328455240742</v>
       </c>
       <c r="N28">
-        <v>7136.313339397804</v>
+        <v>7091.671544759258</v>
       </c>
       <c r="O28">
-        <v>1041.901747552079</v>
+        <v>1035.384045534852</v>
       </c>
       <c r="P28">
-        <v>6094.411591845725</v>
+        <v>6056.287499224406</v>
       </c>
       <c r="Q28">
-        <v>12617.41159184572</v>
+        <v>12579.28749922441</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1012040422991419</v>
+        <v>0.1018777683385494</v>
       </c>
       <c r="T28">
-        <v>1.279539083121061</v>
+        <v>1.295098575948024</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.148354746917905</v>
+        <v>6.883600867402426</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.0863148148871411</v>
+        <v>0.08664347047291716</v>
       </c>
       <c r="C29">
-        <v>64255.06077169126</v>
+        <v>62711.3158866695</v>
       </c>
       <c r="D29">
-        <v>84746.94986900288</v>
+        <v>84065.01569128897</v>
       </c>
       <c r="E29">
-        <v>-9125.381633472167</v>
+        <v>-8263.570926164328</v>
       </c>
       <c r="F29">
-        <v>23268.88909731163</v>
+        <v>24130.69980461947</v>
       </c>
       <c r="G29">
         <v>2777</v>
@@ -3665,45 +3665,45 @@
         <v>8297</v>
       </c>
       <c r="M29">
-        <v>1205.328455240742</v>
+        <v>1290.992439547141</v>
       </c>
       <c r="N29">
-        <v>7091.671544759258</v>
+        <v>7006.007560452858</v>
       </c>
       <c r="O29">
-        <v>1035.384045534852</v>
+        <v>1022.877103826117</v>
       </c>
       <c r="P29">
-        <v>6056.287499224406</v>
+        <v>5983.130456626741</v>
       </c>
       <c r="Q29">
-        <v>12579.28749922441</v>
+        <v>12506.13045662674</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1018777683385494</v>
+        <v>0.1025702089901627</v>
       </c>
       <c r="T29">
-        <v>1.295098575948024</v>
+        <v>1.31109027690907</v>
       </c>
       <c r="U29">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V29">
         <v>0.146</v>
       </c>
       <c r="W29">
-        <v>0.0442372</v>
+        <v>0.045689</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y29">
-        <v>6.883600867402426</v>
+        <v>6.426838566855162</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08664347047291716</v>
+        <v>0.08658014005869322</v>
       </c>
       <c r="C30">
-        <v>62711.3158866695</v>
+        <v>61980.05579193457</v>
       </c>
       <c r="D30">
-        <v>84065.01569128897</v>
+        <v>84195.56630386188</v>
       </c>
       <c r="E30">
-        <v>-8263.570926164328</v>
+        <v>-7401.760218856489</v>
       </c>
       <c r="F30">
-        <v>24130.69980461947</v>
+        <v>24992.51051192731</v>
       </c>
       <c r="G30">
         <v>2777</v>
@@ -3747,28 +3747,28 @@
         <v>8297</v>
       </c>
       <c r="M30">
-        <v>1290.992439547141</v>
+        <v>1337.099312388111</v>
       </c>
       <c r="N30">
-        <v>7006.007560452858</v>
+        <v>6959.900687611889</v>
       </c>
       <c r="O30">
-        <v>1022.877103826117</v>
+        <v>1016.145500391336</v>
       </c>
       <c r="P30">
-        <v>5983.130456626741</v>
+        <v>5943.755187220553</v>
       </c>
       <c r="Q30">
-        <v>12506.13045662674</v>
+        <v>12466.75518722055</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1025702089901627</v>
+        <v>0.103282155012244</v>
       </c>
       <c r="T30">
-        <v>1.31109027690907</v>
+        <v>1.327532448319723</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.426838566855162</v>
+        <v>6.205223443860157</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08658014005869322</v>
+        <v>0.08651680964446928</v>
       </c>
       <c r="C31">
-        <v>61980.05579193458</v>
+        <v>61249.2018107652</v>
       </c>
       <c r="D31">
-        <v>84195.56630386188</v>
+        <v>84326.52303000033</v>
       </c>
       <c r="E31">
-        <v>-7401.760218856496</v>
+        <v>-6539.949511548657</v>
       </c>
       <c r="F31">
-        <v>24992.5105119273</v>
+        <v>25854.32121923514</v>
       </c>
       <c r="G31">
         <v>2777</v>
@@ -3829,28 +3829,28 @@
         <v>8297</v>
       </c>
       <c r="M31">
-        <v>1337.099312388111</v>
+        <v>1383.20618522908</v>
       </c>
       <c r="N31">
-        <v>6959.900687611889</v>
+        <v>6913.79381477092</v>
       </c>
       <c r="O31">
-        <v>1016.145500391336</v>
+        <v>1009.413896956554</v>
       </c>
       <c r="P31">
-        <v>5943.755187220553</v>
+        <v>5904.379917814365</v>
       </c>
       <c r="Q31">
-        <v>12466.75518722055</v>
+        <v>12427.37991781437</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.103282155012244</v>
+        <v>0.1040144423492418</v>
       </c>
       <c r="T31">
-        <v>1.327532448319723</v>
+        <v>1.344444396056394</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.205223443860158</v>
+        <v>5.998382662398153</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08651680964446928</v>
+        <v>0.08645347923024535</v>
       </c>
       <c r="C32">
-        <v>61249.2018107652</v>
+        <v>60518.75584110523</v>
       </c>
       <c r="D32">
-        <v>84326.52303000033</v>
+        <v>84457.88776764821</v>
       </c>
       <c r="E32">
-        <v>-6539.949511548657</v>
+        <v>-5678.138804240818</v>
       </c>
       <c r="F32">
-        <v>25854.32121923514</v>
+        <v>26716.13192654298</v>
       </c>
       <c r="G32">
         <v>2777</v>
@@ -3911,28 +3911,28 @@
         <v>8297</v>
       </c>
       <c r="M32">
-        <v>1383.20618522908</v>
+        <v>1429.313058070049</v>
       </c>
       <c r="N32">
-        <v>6913.79381477092</v>
+        <v>6867.686941929951</v>
       </c>
       <c r="O32">
-        <v>1009.413896956554</v>
+        <v>1002.682293521773</v>
       </c>
       <c r="P32">
-        <v>5904.379917814365</v>
+        <v>5865.004648408179</v>
       </c>
       <c r="Q32">
-        <v>12427.37991781437</v>
+        <v>12388.00464840818</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1040144423492418</v>
+        <v>0.1047679554061527</v>
       </c>
       <c r="T32">
-        <v>1.344444396056394</v>
+        <v>1.361846545176737</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.998382662398153</v>
+        <v>5.804886447482083</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08645347923024535</v>
+        <v>0.08639014881602142</v>
       </c>
       <c r="C33">
-        <v>60518.75584110523</v>
+        <v>59788.71979274352</v>
       </c>
       <c r="D33">
-        <v>84457.88776764821</v>
+        <v>84589.66242659434</v>
       </c>
       <c r="E33">
-        <v>-5678.138804240818</v>
+        <v>-4816.328096932979</v>
       </c>
       <c r="F33">
-        <v>26716.13192654298</v>
+        <v>27577.94263385082</v>
       </c>
       <c r="G33">
         <v>2777</v>
@@ -3993,28 +3993,28 @@
         <v>8297</v>
       </c>
       <c r="M33">
-        <v>1429.313058070049</v>
+        <v>1475.419930911019</v>
       </c>
       <c r="N33">
-        <v>6867.686941929951</v>
+        <v>6821.580069088981</v>
       </c>
       <c r="O33">
-        <v>1002.682293521773</v>
+        <v>995.9506900869911</v>
       </c>
       <c r="P33">
-        <v>5865.004648408179</v>
+        <v>5825.62937900199</v>
       </c>
       <c r="Q33">
-        <v>12388.00464840818</v>
+        <v>12348.62937900199</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1047679554061527</v>
+        <v>0.1055436306117962</v>
       </c>
       <c r="T33">
-        <v>1.361846545176737</v>
+        <v>1.379760522212384</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.804886447482083</v>
+        <v>5.623483745998267</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08639014881602142</v>
+        <v>0.0865522744017975</v>
       </c>
       <c r="C34">
-        <v>59788.71979274352</v>
+        <v>58590.38434484578</v>
       </c>
       <c r="D34">
-        <v>84589.66242659434</v>
+        <v>84253.13768600444</v>
       </c>
       <c r="E34">
-        <v>-4816.328096932979</v>
+        <v>-3954.51738962514</v>
       </c>
       <c r="F34">
-        <v>27577.94263385082</v>
+        <v>28439.75334115866</v>
       </c>
       <c r="G34">
         <v>2777</v>
@@ -4075,45 +4075,45 @@
         <v>8297</v>
       </c>
       <c r="M34">
-        <v>1475.419930911019</v>
+        <v>1544.278606424915</v>
       </c>
       <c r="N34">
-        <v>6821.580069088981</v>
+        <v>6752.721393575085</v>
       </c>
       <c r="O34">
-        <v>995.9506900869911</v>
+        <v>985.8973234619624</v>
       </c>
       <c r="P34">
-        <v>5825.62937900199</v>
+        <v>5766.824070113123</v>
       </c>
       <c r="Q34">
-        <v>12348.62937900199</v>
+        <v>12289.82407011312</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1055436306117962</v>
+        <v>0.1063424603011903</v>
       </c>
       <c r="T34">
-        <v>1.379760522212384</v>
+        <v>1.398209244831185</v>
       </c>
       <c r="U34">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V34">
         <v>0.146</v>
       </c>
       <c r="W34">
-        <v>0.045689</v>
+        <v>0.0463722</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y34">
-        <v>5.623483745998267</v>
+        <v>5.372735182291999</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.0865522744017975</v>
+        <v>0.08649577598757355</v>
       </c>
       <c r="C35">
-        <v>58590.38434484578</v>
+        <v>57845.54323836595</v>
       </c>
       <c r="D35">
-        <v>84253.13768600444</v>
+        <v>84370.10728683244</v>
       </c>
       <c r="E35">
-        <v>-3954.51738962514</v>
+        <v>-3092.706682317301</v>
       </c>
       <c r="F35">
-        <v>28439.75334115866</v>
+        <v>29301.56404846649</v>
       </c>
       <c r="G35">
         <v>2777</v>
@@ -4157,28 +4157,28 @@
         <v>8297</v>
       </c>
       <c r="M35">
-        <v>1544.278606424915</v>
+        <v>1591.074927831731</v>
       </c>
       <c r="N35">
-        <v>6752.721393575085</v>
+        <v>6705.925072168269</v>
       </c>
       <c r="O35">
-        <v>985.8973234619624</v>
+        <v>979.0650605365672</v>
       </c>
       <c r="P35">
-        <v>5766.824070113123</v>
+        <v>5726.860011631702</v>
       </c>
       <c r="Q35">
-        <v>12289.82407011312</v>
+        <v>12249.8600116317</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1063424603011903</v>
+        <v>0.107165496950869</v>
       </c>
       <c r="T35">
-        <v>1.398209244831185</v>
+        <v>1.417217019650555</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.372735182291999</v>
+        <v>5.21471355928341</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08649577598757355</v>
+        <v>0.08643927757334963</v>
       </c>
       <c r="C36">
-        <v>57845.54323836595</v>
+        <v>57101.02736389573</v>
       </c>
       <c r="D36">
-        <v>84370.10728683244</v>
+        <v>84487.40211967006</v>
       </c>
       <c r="E36">
-        <v>-3092.706682317301</v>
+        <v>-2230.895975009462</v>
       </c>
       <c r="F36">
-        <v>29301.56404846649</v>
+        <v>30163.37475577433</v>
       </c>
       <c r="G36">
         <v>2777</v>
@@ -4239,28 +4239,28 @@
         <v>8297</v>
       </c>
       <c r="M36">
-        <v>1591.074927831731</v>
+        <v>1637.871249238546</v>
       </c>
       <c r="N36">
-        <v>6705.925072168269</v>
+        <v>6659.128750761453</v>
       </c>
       <c r="O36">
-        <v>979.0650605365672</v>
+        <v>972.2327976111721</v>
       </c>
       <c r="P36">
-        <v>5726.860011631702</v>
+        <v>5686.895953150281</v>
       </c>
       <c r="Q36">
-        <v>12249.8600116317</v>
+        <v>12209.89595315028</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.107165496950869</v>
+        <v>0.1080138578051533</v>
       </c>
       <c r="T36">
-        <v>1.417217019650555</v>
+        <v>1.436809649079753</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.21471355928341</v>
+        <v>5.065721743303884</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08643927757334963</v>
+        <v>0.08638277915912568</v>
       </c>
       <c r="C37">
-        <v>57101.02736389573</v>
+        <v>56356.83807977691</v>
       </c>
       <c r="D37">
-        <v>84487.40211967006</v>
+        <v>84605.02354285908</v>
       </c>
       <c r="E37">
-        <v>-2230.895975009462</v>
+        <v>-1369.085267701623</v>
       </c>
       <c r="F37">
-        <v>30163.37475577433</v>
+        <v>31025.18546308217</v>
       </c>
       <c r="G37">
         <v>2777</v>
@@ -4321,28 +4321,28 @@
         <v>8297</v>
       </c>
       <c r="M37">
-        <v>1637.871249238546</v>
+        <v>1684.667570645362</v>
       </c>
       <c r="N37">
-        <v>6659.128750761453</v>
+        <v>6612.332429354637</v>
       </c>
       <c r="O37">
-        <v>972.2327976111721</v>
+        <v>965.400534685777</v>
       </c>
       <c r="P37">
-        <v>5686.895953150281</v>
+        <v>5646.931894668861</v>
       </c>
       <c r="Q37">
-        <v>12209.89595315028</v>
+        <v>12169.93189466886</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1080138578051533</v>
+        <v>0.1088887299361339</v>
       </c>
       <c r="T37">
-        <v>1.436809649079753</v>
+        <v>1.457014548178612</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.065721743303884</v>
+        <v>4.925007250434332</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08638277915912569</v>
+        <v>0.08632628074490176</v>
       </c>
       <c r="C38">
-        <v>56356.8380797769</v>
+        <v>55612.97675192577</v>
       </c>
       <c r="D38">
-        <v>84605.02354285907</v>
+        <v>84722.97292231578</v>
       </c>
       <c r="E38">
-        <v>-1369.085267701626</v>
+        <v>-507.2745603937874</v>
       </c>
       <c r="F38">
-        <v>31025.18546308217</v>
+        <v>31886.99617039001</v>
       </c>
       <c r="G38">
         <v>2777</v>
@@ -4403,28 +4403,28 @@
         <v>8297</v>
       </c>
       <c r="M38">
-        <v>1684.667570645362</v>
+        <v>1731.463892052177</v>
       </c>
       <c r="N38">
-        <v>6612.332429354638</v>
+        <v>6565.536107947823</v>
       </c>
       <c r="O38">
-        <v>965.4005346857772</v>
+        <v>958.568271760382</v>
       </c>
       <c r="P38">
-        <v>5646.931894668861</v>
+        <v>5606.96783618744</v>
       </c>
       <c r="Q38">
-        <v>12169.93189466886</v>
+        <v>12129.96783618744</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1088887299361339</v>
+        <v>0.1097913757855583</v>
       </c>
       <c r="T38">
-        <v>1.457014548178612</v>
+        <v>1.47786087264569</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.925007250434333</v>
+        <v>4.79189894636854</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08632628074490176</v>
+        <v>0.08626978233067782</v>
       </c>
       <c r="C39">
-        <v>55612.97675192577</v>
+        <v>54869.4447538864</v>
       </c>
       <c r="D39">
-        <v>84722.97292231578</v>
+        <v>84841.25163158425</v>
       </c>
       <c r="E39">
-        <v>-507.2745603937874</v>
+        <v>354.536146914048</v>
       </c>
       <c r="F39">
-        <v>31886.99617039001</v>
+        <v>32748.80687769784</v>
       </c>
       <c r="G39">
         <v>2777</v>
@@ -4485,28 +4485,28 @@
         <v>8297</v>
       </c>
       <c r="M39">
-        <v>1731.463892052177</v>
+        <v>1778.260213458993</v>
       </c>
       <c r="N39">
-        <v>6565.536107947823</v>
+        <v>6518.739786541008</v>
       </c>
       <c r="O39">
-        <v>958.568271760382</v>
+        <v>951.736008834987</v>
       </c>
       <c r="P39">
-        <v>5606.96783618744</v>
+        <v>5567.003777706021</v>
       </c>
       <c r="Q39">
-        <v>12129.96783618744</v>
+        <v>12090.00377770602</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1097913757855583</v>
+        <v>0.1107231392430287</v>
       </c>
       <c r="T39">
-        <v>1.47786087264569</v>
+        <v>1.49937965919235</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.79189894636854</v>
+        <v>4.665796342516737</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08626978233067782</v>
+        <v>0.0862132839164539</v>
       </c>
       <c r="C40">
-        <v>54869.4447538864</v>
+        <v>54126.2434668837</v>
       </c>
       <c r="D40">
-        <v>84841.25163158425</v>
+        <v>84959.86105188938</v>
       </c>
       <c r="E40">
-        <v>354.536146914048</v>
+        <v>1216.346854221887</v>
       </c>
       <c r="F40">
-        <v>32748.80687769784</v>
+        <v>33610.61758500568</v>
       </c>
       <c r="G40">
         <v>2777</v>
@@ -4567,28 +4567,28 @@
         <v>8297</v>
       </c>
       <c r="M40">
-        <v>1778.260213458993</v>
+        <v>1825.056534865809</v>
       </c>
       <c r="N40">
-        <v>6518.739786541008</v>
+        <v>6471.943465134192</v>
       </c>
       <c r="O40">
-        <v>951.736008834987</v>
+        <v>944.903745909592</v>
       </c>
       <c r="P40">
-        <v>5567.003777706021</v>
+        <v>5527.0397192246</v>
       </c>
       <c r="Q40">
-        <v>12090.00377770602</v>
+        <v>12050.0397192246</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1107231392430287</v>
+        <v>0.1116854523220556</v>
       </c>
       <c r="T40">
-        <v>1.49937965919235</v>
+        <v>1.521603979724147</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.665796342516737</v>
+        <v>4.546160538862461</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.0862132839164539</v>
+        <v>0.08615678550222997</v>
       </c>
       <c r="C41">
-        <v>54126.2434668837</v>
+        <v>53383.37427987738</v>
       </c>
       <c r="D41">
-        <v>84959.86105188938</v>
+        <v>85078.80257219091</v>
       </c>
       <c r="E41">
-        <v>1216.346854221887</v>
+        <v>2078.15756152973</v>
       </c>
       <c r="F41">
-        <v>33610.61758500568</v>
+        <v>34472.42829231353</v>
       </c>
       <c r="G41">
         <v>2777</v>
@@ -4649,28 +4649,28 @@
         <v>8297</v>
       </c>
       <c r="M41">
-        <v>1825.056534865809</v>
+        <v>1871.852856272624</v>
       </c>
       <c r="N41">
-        <v>6471.943465134192</v>
+        <v>6425.147143727376</v>
       </c>
       <c r="O41">
-        <v>944.903745909592</v>
+        <v>938.0714829841968</v>
       </c>
       <c r="P41">
-        <v>5527.0397192246</v>
+        <v>5487.075660743179</v>
       </c>
       <c r="Q41">
-        <v>12050.0397192246</v>
+        <v>12010.07566074318</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1116854523220556</v>
+        <v>0.1126798425037166</v>
       </c>
       <c r="T41">
-        <v>1.521603979724147</v>
+        <v>1.544569110940337</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.546160538862461</v>
+        <v>4.432506525390899</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08615678550222997</v>
+        <v>0.08610028708800602</v>
       </c>
       <c r="C42">
-        <v>53383.37427987738</v>
+        <v>52640.83858961605</v>
       </c>
       <c r="D42">
-        <v>85078.80257219091</v>
+        <v>85198.07758923741</v>
       </c>
       <c r="E42">
-        <v>2078.15756152973</v>
+        <v>2939.968268837565</v>
       </c>
       <c r="F42">
-        <v>34472.42829231353</v>
+        <v>35334.23899962136</v>
       </c>
       <c r="G42">
         <v>2777</v>
@@ -4731,28 +4731,28 @@
         <v>8297</v>
       </c>
       <c r="M42">
-        <v>1871.852856272624</v>
+        <v>1918.64917767944</v>
       </c>
       <c r="N42">
-        <v>6425.147143727376</v>
+        <v>6378.35082232056</v>
       </c>
       <c r="O42">
-        <v>938.0714829841968</v>
+        <v>931.2392200588017</v>
       </c>
       <c r="P42">
-        <v>5487.075660743179</v>
+        <v>5447.111602261758</v>
       </c>
       <c r="Q42">
-        <v>12010.07566074318</v>
+        <v>11970.11160226176</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1126798425037166</v>
+        <v>0.1137079408271288</v>
       </c>
       <c r="T42">
-        <v>1.544569110940337</v>
+        <v>1.568312721180805</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.432506525390899</v>
+        <v>4.324396610137462</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08610028708800602</v>
+        <v>0.08640246867378208</v>
       </c>
       <c r="C43">
-        <v>52640.83858961605</v>
+        <v>51144.94598945984</v>
       </c>
       <c r="D43">
-        <v>85198.07758923741</v>
+        <v>84563.99569638904</v>
       </c>
       <c r="E43">
-        <v>2939.968268837565</v>
+        <v>3801.778976145408</v>
       </c>
       <c r="F43">
-        <v>35334.23899962136</v>
+        <v>36196.0497069292</v>
       </c>
       <c r="G43">
         <v>2777</v>
@@ -4813,45 +4813,45 @@
         <v>8297</v>
       </c>
       <c r="M43">
-        <v>1918.64917767944</v>
+        <v>2001.641548793185</v>
       </c>
       <c r="N43">
-        <v>6378.35082232056</v>
+        <v>6295.358451206816</v>
       </c>
       <c r="O43">
-        <v>931.2392200588017</v>
+        <v>919.1223338761951</v>
       </c>
       <c r="P43">
-        <v>5447.111602261758</v>
+        <v>5376.236117330621</v>
       </c>
       <c r="Q43">
-        <v>11970.11160226176</v>
+        <v>11899.23611733062</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1137079408271288</v>
+        <v>0.1147714908168657</v>
       </c>
       <c r="T43">
-        <v>1.568312721180805</v>
+        <v>1.592875076601979</v>
       </c>
       <c r="U43">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V43">
         <v>0.146</v>
       </c>
       <c r="W43">
-        <v>0.0463722</v>
+        <v>0.0472262</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y43">
-        <v>4.324396610137462</v>
+        <v>4.145097809846307</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.0864024686737821</v>
+        <v>0.08635451025955816</v>
       </c>
       <c r="C44">
-        <v>51144.94598945983</v>
+        <v>50383.13784926677</v>
       </c>
       <c r="D44">
-        <v>84563.99569638903</v>
+        <v>84663.9982635038</v>
       </c>
       <c r="E44">
-        <v>3801.778976145401</v>
+        <v>4663.589683453236</v>
       </c>
       <c r="F44">
-        <v>36196.0497069292</v>
+        <v>37057.86041423703</v>
       </c>
       <c r="G44">
         <v>2777</v>
@@ -4895,28 +4895,28 @@
         <v>8297</v>
       </c>
       <c r="M44">
-        <v>2001.641548793185</v>
+        <v>2049.299680907308</v>
       </c>
       <c r="N44">
-        <v>6295.358451206816</v>
+        <v>6247.700319092692</v>
       </c>
       <c r="O44">
-        <v>919.1223338761951</v>
+        <v>912.1642465875329</v>
       </c>
       <c r="P44">
-        <v>5376.236117330621</v>
+        <v>5335.536072505159</v>
       </c>
       <c r="Q44">
-        <v>11899.23611733062</v>
+        <v>11858.53607250516</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1147714908168657</v>
+        <v>0.115872358350102</v>
       </c>
       <c r="T44">
-        <v>1.592875076601979</v>
+        <v>1.618299269055474</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.145097809846307</v>
+        <v>4.04870018636151</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08635451025955816</v>
+        <v>0.08630655184533423</v>
       </c>
       <c r="C45">
-        <v>50383.13784926677</v>
+        <v>49621.56650852063</v>
       </c>
       <c r="D45">
-        <v>84663.9982635038</v>
+        <v>84764.2376300655</v>
       </c>
       <c r="E45">
-        <v>4663.589683453236</v>
+        <v>5525.400390761079</v>
       </c>
       <c r="F45">
-        <v>37057.86041423703</v>
+        <v>37919.67112154487</v>
       </c>
       <c r="G45">
         <v>2777</v>
@@ -4977,28 +4977,28 @@
         <v>8297</v>
       </c>
       <c r="M45">
-        <v>2049.299680907308</v>
+        <v>2096.957813021432</v>
       </c>
       <c r="N45">
-        <v>6247.700319092692</v>
+        <v>6200.042186978568</v>
       </c>
       <c r="O45">
-        <v>912.1642465875329</v>
+        <v>905.2061592988708</v>
       </c>
       <c r="P45">
-        <v>5335.536072505159</v>
+        <v>5294.836027679697</v>
       </c>
       <c r="Q45">
-        <v>11858.53607250516</v>
+        <v>11817.8360276797</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.115872358350102</v>
+        <v>0.1170125425809539</v>
       </c>
       <c r="T45">
-        <v>1.618299269055474</v>
+        <v>1.644631468382309</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.04870018636151</v>
+        <v>3.956684273035111</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08630655184533423</v>
+        <v>0.08625859343111029</v>
       </c>
       <c r="C46">
-        <v>49621.56650852063</v>
+        <v>48860.23280930652</v>
       </c>
       <c r="D46">
-        <v>84764.2376300655</v>
+        <v>84864.71463815923</v>
       </c>
       <c r="E46">
-        <v>5525.400390761079</v>
+        <v>6387.211098068914</v>
       </c>
       <c r="F46">
-        <v>37919.67112154487</v>
+        <v>38781.48182885271</v>
       </c>
       <c r="G46">
         <v>2777</v>
@@ -5059,28 +5059,28 @@
         <v>8297</v>
       </c>
       <c r="M46">
-        <v>2096.957813021432</v>
+        <v>2144.615945135555</v>
       </c>
       <c r="N46">
-        <v>6200.042186978568</v>
+        <v>6152.384054864446</v>
       </c>
       <c r="O46">
-        <v>905.2061592988708</v>
+        <v>898.2480720102091</v>
       </c>
       <c r="P46">
-        <v>5294.836027679697</v>
+        <v>5254.135982854236</v>
       </c>
       <c r="Q46">
-        <v>11817.8360276797</v>
+        <v>11777.13598285424</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1170125425809539</v>
+        <v>0.1181941880565641</v>
       </c>
       <c r="T46">
-        <v>1.644631468382309</v>
+        <v>1.67192120223012</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.956684273035111</v>
+        <v>3.868757955856554</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08625859343111029</v>
+        <v>0.08621063501688636</v>
       </c>
       <c r="C47">
-        <v>48860.23280930652</v>
+        <v>48099.13759770699</v>
       </c>
       <c r="D47">
-        <v>84864.71463815923</v>
+        <v>84965.43013386754</v>
       </c>
       <c r="E47">
-        <v>6387.211098068914</v>
+        <v>7249.021805376757</v>
       </c>
       <c r="F47">
-        <v>38781.48182885271</v>
+        <v>39643.29253616055</v>
       </c>
       <c r="G47">
         <v>2777</v>
@@ -5141,28 +5141,28 @@
         <v>8297</v>
       </c>
       <c r="M47">
-        <v>2144.615945135555</v>
+        <v>2192.274077249679</v>
       </c>
       <c r="N47">
-        <v>6152.384054864446</v>
+        <v>6104.725922750322</v>
       </c>
       <c r="O47">
-        <v>898.2480720102091</v>
+        <v>891.2899847215469</v>
       </c>
       <c r="P47">
-        <v>5254.135982854236</v>
+        <v>5213.435938028775</v>
       </c>
       <c r="Q47">
-        <v>11777.13598285424</v>
+        <v>11736.43593802878</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1181941880565641</v>
+        <v>0.1194195981794192</v>
       </c>
       <c r="T47">
-        <v>1.67192120223012</v>
+        <v>1.700221666961182</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.868757955856554</v>
+        <v>3.784654522033585</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08621063501688636</v>
+        <v>0.08616267660266241</v>
       </c>
       <c r="C48">
-        <v>48099.13759770699</v>
+        <v>47338.2817238258</v>
       </c>
       <c r="D48">
-        <v>84965.43013386754</v>
+        <v>85066.38496729419</v>
       </c>
       <c r="E48">
-        <v>7249.021805376757</v>
+        <v>8110.832512684592</v>
       </c>
       <c r="F48">
-        <v>39643.29253616055</v>
+        <v>40505.10324346839</v>
       </c>
       <c r="G48">
         <v>2777</v>
@@ -5223,28 +5223,28 @@
         <v>8297</v>
       </c>
       <c r="M48">
-        <v>2192.274077249679</v>
+        <v>2239.932209363802</v>
       </c>
       <c r="N48">
-        <v>6104.725922750322</v>
+        <v>6057.067790636198</v>
       </c>
       <c r="O48">
-        <v>891.2899847215469</v>
+        <v>884.3318974328848</v>
       </c>
       <c r="P48">
-        <v>5213.435938028775</v>
+        <v>5172.735893203313</v>
       </c>
       <c r="Q48">
-        <v>11736.43593802878</v>
+        <v>11695.73589320331</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1194195981794192</v>
+        <v>0.1206912501937027</v>
       </c>
       <c r="T48">
-        <v>1.700221666961182</v>
+        <v>1.729590073757568</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.784654522033585</v>
+        <v>3.704129957734998</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08616267660266241</v>
+        <v>0.08611471818843849</v>
       </c>
       <c r="C49">
-        <v>47338.2817238258</v>
+        <v>46577.66604181181</v>
       </c>
       <c r="D49">
-        <v>85066.38496729419</v>
+        <v>85167.57999258804</v>
       </c>
       <c r="E49">
-        <v>8110.832512684592</v>
+        <v>8972.643219992435</v>
       </c>
       <c r="F49">
-        <v>40505.10324346839</v>
+        <v>41366.91395077623</v>
       </c>
       <c r="G49">
         <v>2777</v>
@@ -5305,28 +5305,28 @@
         <v>8297</v>
       </c>
       <c r="M49">
-        <v>2239.932209363802</v>
+        <v>2287.590341477925</v>
       </c>
       <c r="N49">
-        <v>6057.067790636198</v>
+        <v>6009.409658522074</v>
       </c>
       <c r="O49">
-        <v>884.3318974328848</v>
+        <v>877.3738101442227</v>
       </c>
       <c r="P49">
-        <v>5172.735893203313</v>
+        <v>5132.035848377851</v>
       </c>
       <c r="Q49">
-        <v>11695.73589320331</v>
+        <v>11655.03584837785</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1206912501937027</v>
+        <v>0.1220118119008433</v>
       </c>
       <c r="T49">
-        <v>1.729590073757568</v>
+        <v>1.760088034661508</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.704129957734998</v>
+        <v>3.626960583615519</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08611471818843848</v>
+        <v>0.08606675977421455</v>
       </c>
       <c r="C50">
-        <v>46577.66604181183</v>
+        <v>45817.29140988323</v>
       </c>
       <c r="D50">
-        <v>85167.57999258806</v>
+        <v>85269.0160679673</v>
       </c>
       <c r="E50">
-        <v>8972.643219992427</v>
+        <v>9834.45392730027</v>
       </c>
       <c r="F50">
-        <v>41366.91395077622</v>
+        <v>42228.72465808407</v>
       </c>
       <c r="G50">
         <v>2777</v>
@@ -5387,28 +5387,28 @@
         <v>8297</v>
       </c>
       <c r="M50">
-        <v>2287.590341477925</v>
+        <v>2335.248473592049</v>
       </c>
       <c r="N50">
-        <v>6009.409658522075</v>
+        <v>5961.751526407951</v>
       </c>
       <c r="O50">
-        <v>877.3738101442229</v>
+        <v>870.4157228555608</v>
       </c>
       <c r="P50">
-        <v>5132.035848377852</v>
+        <v>5091.335803552391</v>
       </c>
       <c r="Q50">
-        <v>11655.03584837785</v>
+        <v>11614.33580355239</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1220118119008432</v>
+        <v>0.1233841603415972</v>
       </c>
       <c r="T50">
-        <v>1.760088034661507</v>
+        <v>1.791781994032268</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.626960583615519</v>
+        <v>3.552940979868263</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08606675977421455</v>
+        <v>0.08601880135999061</v>
       </c>
       <c r="C51">
-        <v>45817.29140988323</v>
+        <v>45057.1586903516</v>
       </c>
       <c r="D51">
-        <v>85269.0160679673</v>
+        <v>85370.6940557435</v>
       </c>
       <c r="E51">
-        <v>9834.45392730027</v>
+        <v>10696.26463460811</v>
       </c>
       <c r="F51">
-        <v>42228.72465808407</v>
+        <v>43090.5353653919</v>
       </c>
       <c r="G51">
         <v>2777</v>
@@ -5469,28 +5469,28 @@
         <v>8297</v>
       </c>
       <c r="M51">
-        <v>2335.248473592049</v>
+        <v>2382.906605706172</v>
       </c>
       <c r="N51">
-        <v>5961.751526407951</v>
+        <v>5914.093394293828</v>
       </c>
       <c r="O51">
-        <v>870.4157228555608</v>
+        <v>863.4576355668988</v>
       </c>
       <c r="P51">
-        <v>5091.335803552391</v>
+        <v>5050.635758726929</v>
       </c>
       <c r="Q51">
-        <v>11614.33580355239</v>
+        <v>11573.63575872693</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1233841603415972</v>
+        <v>0.1248114027199812</v>
       </c>
       <c r="T51">
-        <v>1.791781994032268</v>
+        <v>1.824743711777858</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.552940979868263</v>
+        <v>3.481882160270898</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08601880135999061</v>
+        <v>0.08597084294576669</v>
       </c>
       <c r="C52">
-        <v>45057.1586903516</v>
+        <v>44297.26874964646</v>
       </c>
       <c r="D52">
-        <v>85370.6940557435</v>
+        <v>85472.61482234619</v>
       </c>
       <c r="E52">
-        <v>10696.26463460811</v>
+        <v>11558.07534191594</v>
       </c>
       <c r="F52">
-        <v>43090.5353653919</v>
+        <v>43952.34607269974</v>
       </c>
       <c r="G52">
         <v>2777</v>
@@ -5551,28 +5551,28 @@
         <v>8297</v>
       </c>
       <c r="M52">
-        <v>2382.906605706172</v>
+        <v>2430.564737820296</v>
       </c>
       <c r="N52">
-        <v>5914.093394293828</v>
+        <v>5866.435262179704</v>
       </c>
       <c r="O52">
-        <v>863.4576355668988</v>
+        <v>856.4995482782368</v>
       </c>
       <c r="P52">
-        <v>5050.635758726929</v>
+        <v>5009.935713901467</v>
       </c>
       <c r="Q52">
-        <v>11573.63575872693</v>
+        <v>11532.93571390147</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1248114027199812</v>
+        <v>0.1262968998893198</v>
       </c>
       <c r="T52">
-        <v>1.824743711777858</v>
+        <v>1.859050805757963</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.481882160270898</v>
+        <v>3.4136099610499</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08597084294576669</v>
+        <v>0.08592288453154276</v>
       </c>
       <c r="C53">
-        <v>44297.26874964646</v>
+        <v>43537.62245833992</v>
       </c>
       <c r="D53">
-        <v>85472.61482234619</v>
+        <v>85574.7792383475</v>
       </c>
       <c r="E53">
-        <v>11558.07534191594</v>
+        <v>12419.88604922378</v>
       </c>
       <c r="F53">
-        <v>43952.34607269974</v>
+        <v>44814.15678000758</v>
       </c>
       <c r="G53">
         <v>2777</v>
@@ -5633,28 +5633,28 @@
         <v>8297</v>
       </c>
       <c r="M53">
-        <v>2430.564737820296</v>
+        <v>2478.222869934419</v>
       </c>
       <c r="N53">
-        <v>5866.435262179704</v>
+        <v>5818.77713006558</v>
       </c>
       <c r="O53">
-        <v>856.4995482782368</v>
+        <v>849.5414609895747</v>
       </c>
       <c r="P53">
-        <v>5009.935713901467</v>
+        <v>4969.235669076006</v>
       </c>
       <c r="Q53">
-        <v>11532.93571390147</v>
+        <v>11492.23566907601</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1262968998893198</v>
+        <v>0.1278442927740474</v>
       </c>
       <c r="T53">
-        <v>1.859050805757963</v>
+        <v>1.894787361987239</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.4136099610499</v>
+        <v>3.347963615645094</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08592288453154276</v>
+        <v>0.08587492611731883</v>
       </c>
       <c r="C54">
-        <v>43537.62245833992</v>
+        <v>42778.22069117134</v>
       </c>
       <c r="D54">
-        <v>85574.7792383475</v>
+        <v>85677.18817848676</v>
       </c>
       <c r="E54">
-        <v>12419.88604922378</v>
+        <v>13281.69675653162</v>
       </c>
       <c r="F54">
-        <v>44814.15678000758</v>
+        <v>45675.96748731541</v>
       </c>
       <c r="G54">
         <v>2777</v>
@@ -5715,28 +5715,28 @@
         <v>8297</v>
       </c>
       <c r="M54">
-        <v>2478.222869934419</v>
+        <v>2525.881002048543</v>
       </c>
       <c r="N54">
-        <v>5818.77713006558</v>
+        <v>5771.118997951457</v>
       </c>
       <c r="O54">
-        <v>849.5414609895747</v>
+        <v>842.5833737009127</v>
       </c>
       <c r="P54">
-        <v>4969.235669076006</v>
+        <v>4928.535624250545</v>
       </c>
       <c r="Q54">
-        <v>11492.23566907601</v>
+        <v>11451.53562425054</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1278442927740474</v>
+        <v>0.1294575321645081</v>
       </c>
       <c r="T54">
-        <v>1.894787361987239</v>
+        <v>1.932044622736909</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.347963615645094</v>
+        <v>3.284794490821602</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08587492611731883</v>
+        <v>0.08582696770309488</v>
       </c>
       <c r="C55">
-        <v>42778.22069117134</v>
+        <v>42019.06432707247</v>
       </c>
       <c r="D55">
-        <v>85677.18817848676</v>
+        <v>85779.84252169573</v>
       </c>
       <c r="E55">
-        <v>13281.69675653162</v>
+        <v>14143.50746383946</v>
       </c>
       <c r="F55">
-        <v>45675.96748731541</v>
+        <v>46537.77819462326</v>
       </c>
       <c r="G55">
         <v>2777</v>
@@ -5797,28 +5797,28 @@
         <v>8297</v>
       </c>
       <c r="M55">
-        <v>2525.881002048543</v>
+        <v>2573.539134162666</v>
       </c>
       <c r="N55">
-        <v>5771.118997951457</v>
+        <v>5723.460865837334</v>
       </c>
       <c r="O55">
-        <v>842.5833737009127</v>
+        <v>835.6252864122506</v>
       </c>
       <c r="P55">
-        <v>4928.535624250545</v>
+        <v>4887.835579425083</v>
       </c>
       <c r="Q55">
-        <v>11451.53562425054</v>
+        <v>11410.83557942508</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1294575321645081</v>
+        <v>0.1311409123980324</v>
       </c>
       <c r="T55">
-        <v>1.932044622736909</v>
+        <v>1.970921764388739</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.284794490821602</v>
+        <v>3.223964963213794</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08582696770309488</v>
+        <v>0.08577900928887097</v>
       </c>
       <c r="C56">
-        <v>42019.06432707247</v>
+        <v>41260.15424919222</v>
       </c>
       <c r="D56">
-        <v>85779.84252169573</v>
+        <v>85882.74315112332</v>
       </c>
       <c r="E56">
-        <v>14143.50746383946</v>
+        <v>15005.3181711473</v>
       </c>
       <c r="F56">
-        <v>46537.77819462326</v>
+        <v>47399.58890193109</v>
       </c>
       <c r="G56">
         <v>2777</v>
@@ -5879,28 +5879,28 @@
         <v>8297</v>
       </c>
       <c r="M56">
-        <v>2573.539134162666</v>
+        <v>2621.197266276789</v>
       </c>
       <c r="N56">
-        <v>5723.460865837334</v>
+        <v>5675.802733723211</v>
       </c>
       <c r="O56">
-        <v>835.6252864122506</v>
+        <v>828.6671991235887</v>
       </c>
       <c r="P56">
-        <v>4887.835579425083</v>
+        <v>4847.135534599622</v>
       </c>
       <c r="Q56">
-        <v>11410.83557942508</v>
+        <v>11370.13553459962</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1311409123980324</v>
+        <v>0.1328991095308244</v>
       </c>
       <c r="T56">
-        <v>1.970921764388739</v>
+        <v>2.011526779002873</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.223964963213794</v>
+        <v>3.165347418428089</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08577900928887097</v>
+        <v>0.08573105087464702</v>
       </c>
       <c r="C57">
-        <v>41260.15424919222</v>
+        <v>40501.49134492268</v>
       </c>
       <c r="D57">
-        <v>85882.74315112332</v>
+        <v>85985.89095416162</v>
       </c>
       <c r="E57">
-        <v>15005.3181711473</v>
+        <v>15867.12887845514</v>
       </c>
       <c r="F57">
-        <v>47399.58890193109</v>
+        <v>48261.39960923894</v>
       </c>
       <c r="G57">
         <v>2777</v>
@@ -5961,28 +5961,28 @@
         <v>8297</v>
       </c>
       <c r="M57">
-        <v>2621.197266276789</v>
+        <v>2668.855398390913</v>
       </c>
       <c r="N57">
-        <v>5675.802733723211</v>
+        <v>5628.144601609087</v>
       </c>
       <c r="O57">
-        <v>828.6671991235887</v>
+        <v>821.7091118349266</v>
       </c>
       <c r="P57">
-        <v>4847.135534599622</v>
+        <v>4806.43548977416</v>
       </c>
       <c r="Q57">
-        <v>11370.13553459962</v>
+        <v>11329.43548977416</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1328991095308244</v>
+        <v>0.1347372247151069</v>
       </c>
       <c r="T57">
-        <v>2.011526779002873</v>
+        <v>2.053977476099467</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.165347418428089</v>
+        <v>3.10882335738473</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08573105087464702</v>
+        <v>0.08568309246042308</v>
       </c>
       <c r="C58">
-        <v>40501.49134492268</v>
+        <v>39743.07650592388</v>
       </c>
       <c r="D58">
-        <v>85985.89095416162</v>
+        <v>86089.28682247065</v>
       </c>
       <c r="E58">
-        <v>15867.12887845514</v>
+        <v>16728.93958576298</v>
       </c>
       <c r="F58">
-        <v>48261.39960923894</v>
+        <v>49123.21031654677</v>
       </c>
       <c r="G58">
         <v>2777</v>
@@ -6043,28 +6043,28 @@
         <v>8297</v>
       </c>
       <c r="M58">
-        <v>2668.855398390913</v>
+        <v>2716.513530505037</v>
       </c>
       <c r="N58">
-        <v>5628.144601609087</v>
+        <v>5580.486469494963</v>
       </c>
       <c r="O58">
-        <v>821.7091118349266</v>
+        <v>814.7510245462645</v>
       </c>
       <c r="P58">
-        <v>4806.43548977416</v>
+        <v>4765.735444948698</v>
       </c>
       <c r="Q58">
-        <v>11329.43548977416</v>
+        <v>11288.7354449487</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1347372247151069</v>
+        <v>0.1366608336288909</v>
       </c>
       <c r="T58">
-        <v>2.053977476099467</v>
+        <v>2.098402624223809</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.10882335738473</v>
+        <v>3.054282596728858</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08568309246042308</v>
+        <v>0.08563513404619916</v>
       </c>
       <c r="C59">
-        <v>39743.07650592388</v>
+        <v>38984.91062814982</v>
       </c>
       <c r="D59">
-        <v>86089.28682247065</v>
+        <v>86192.93165200444</v>
       </c>
       <c r="E59">
-        <v>16728.93958576298</v>
+        <v>17590.75029307082</v>
       </c>
       <c r="F59">
-        <v>49123.21031654677</v>
+        <v>49985.02102385461</v>
       </c>
       <c r="G59">
         <v>2777</v>
@@ -6125,28 +6125,28 @@
         <v>8297</v>
       </c>
       <c r="M59">
-        <v>2716.513530505037</v>
+        <v>2764.17166261916</v>
       </c>
       <c r="N59">
-        <v>5580.486469494963</v>
+        <v>5532.82833738084</v>
       </c>
       <c r="O59">
-        <v>814.7510245462645</v>
+        <v>807.7929372576026</v>
       </c>
       <c r="P59">
-        <v>4765.735444948698</v>
+        <v>4725.035400123237</v>
       </c>
       <c r="Q59">
-        <v>11288.7354449487</v>
+        <v>11248.03540012324</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1366608336288909</v>
+        <v>0.1386760429671409</v>
       </c>
       <c r="T59">
-        <v>2.098402624223809</v>
+        <v>2.144943255592168</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.054282596728858</v>
+        <v>3.00162255195767</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08563513404619916</v>
+        <v>0.08684682563197521</v>
       </c>
       <c r="C60">
-        <v>38984.91062814984</v>
+        <v>35578.70706151339</v>
       </c>
       <c r="D60">
-        <v>86192.93165200444</v>
+        <v>83648.53879267583</v>
       </c>
       <c r="E60">
-        <v>17590.7502930708</v>
+        <v>18452.56100037865</v>
       </c>
       <c r="F60">
-        <v>49985.0210238546</v>
+        <v>50846.83173116244</v>
       </c>
       <c r="G60">
         <v>2777</v>
@@ -6207,45 +6207,45 @@
         <v>8297</v>
       </c>
       <c r="M60">
-        <v>2764.17166261916</v>
+        <v>2938.946874061189</v>
       </c>
       <c r="N60">
-        <v>5532.828337380841</v>
+        <v>5358.053125938811</v>
       </c>
       <c r="O60">
-        <v>807.7929372576027</v>
+        <v>782.2757563870663</v>
       </c>
       <c r="P60">
-        <v>4725.035400123238</v>
+        <v>4575.777369551744</v>
       </c>
       <c r="Q60">
-        <v>11248.03540012324</v>
+        <v>11098.77736955174</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1386760429671408</v>
+        <v>0.1407895551999395</v>
       </c>
       <c r="T60">
-        <v>2.144943255592168</v>
+        <v>2.193754161661422</v>
       </c>
       <c r="U60">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V60">
         <v>0.146</v>
       </c>
       <c r="W60">
-        <v>0.0472262</v>
+        <v>0.0493612</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y60">
-        <v>3.001622551957671</v>
+        <v>2.823120102383741</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08684682563197521</v>
+        <v>0.08682021721775128</v>
       </c>
       <c r="C61">
-        <v>35578.70706151339</v>
+        <v>34771.15630503924</v>
       </c>
       <c r="D61">
-        <v>83648.53879267583</v>
+        <v>83702.79874350951</v>
       </c>
       <c r="E61">
-        <v>18452.56100037865</v>
+        <v>19314.37170768648</v>
       </c>
       <c r="F61">
-        <v>50846.83173116244</v>
+        <v>51708.64243847028</v>
       </c>
       <c r="G61">
         <v>2777</v>
@@ -6289,28 +6289,28 @@
         <v>8297</v>
       </c>
       <c r="M61">
-        <v>2938.946874061189</v>
+        <v>2988.759532943582</v>
       </c>
       <c r="N61">
-        <v>5358.053125938811</v>
+        <v>5308.240467056417</v>
       </c>
       <c r="O61">
-        <v>782.2757563870663</v>
+        <v>775.0031081902368</v>
       </c>
       <c r="P61">
-        <v>4575.777369551744</v>
+        <v>4533.23735886618</v>
       </c>
       <c r="Q61">
-        <v>11098.77736955174</v>
+        <v>11056.23735886618</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1407895551999395</v>
+        <v>0.1430087430443782</v>
       </c>
       <c r="T61">
-        <v>2.193754161661422</v>
+        <v>2.245005613034139</v>
       </c>
       <c r="U61">
         <v>0.0578</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.823120102383741</v>
+        <v>2.776068100677345</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08682021721775128</v>
+        <v>0.08679360880352735</v>
       </c>
       <c r="C62">
-        <v>34771.15630503924</v>
+        <v>33963.67598741101</v>
       </c>
       <c r="D62">
-        <v>83702.79874350951</v>
+        <v>83757.12913318913</v>
       </c>
       <c r="E62">
-        <v>19314.37170768648</v>
+        <v>20176.18241499432</v>
       </c>
       <c r="F62">
-        <v>51708.64243847028</v>
+        <v>52570.45314577812</v>
       </c>
       <c r="G62">
         <v>2777</v>
@@ -6371,28 +6371,28 @@
         <v>8297</v>
       </c>
       <c r="M62">
-        <v>2988.759532943582</v>
+        <v>3038.572191825976</v>
       </c>
       <c r="N62">
-        <v>5308.240467056417</v>
+        <v>5258.427808174025</v>
       </c>
       <c r="O62">
-        <v>775.0031081902368</v>
+        <v>767.7304599934076</v>
       </c>
       <c r="P62">
-        <v>4533.23735886618</v>
+        <v>4490.697348180617</v>
       </c>
       <c r="Q62">
-        <v>11056.23735886618</v>
+        <v>11013.69734818062</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1430087430443782</v>
+        <v>0.1453417353936599</v>
       </c>
       <c r="T62">
-        <v>2.245005613034139</v>
+        <v>2.298885343964432</v>
       </c>
       <c r="U62">
         <v>0.0578</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.776068100677345</v>
+        <v>2.730558787551487</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08679360880352735</v>
+        <v>0.08676700038930342</v>
       </c>
       <c r="C63">
-        <v>33963.67598741101</v>
+        <v>33156.26624588062</v>
       </c>
       <c r="D63">
-        <v>83757.12913318913</v>
+        <v>83811.53009896657</v>
       </c>
       <c r="E63">
-        <v>20176.18241499432</v>
+        <v>21037.99312230216</v>
       </c>
       <c r="F63">
-        <v>52570.45314577812</v>
+        <v>53432.26385308595</v>
       </c>
       <c r="G63">
         <v>2777</v>
@@ -6453,28 +6453,28 @@
         <v>8297</v>
       </c>
       <c r="M63">
-        <v>3038.572191825976</v>
+        <v>3088.384850708369</v>
       </c>
       <c r="N63">
-        <v>5258.427808174025</v>
+        <v>5208.615149291631</v>
       </c>
       <c r="O63">
-        <v>767.7304599934076</v>
+        <v>760.4578117965782</v>
       </c>
       <c r="P63">
-        <v>4490.697348180617</v>
+        <v>4448.157337495053</v>
       </c>
       <c r="Q63">
-        <v>11013.69734818062</v>
+        <v>10971.15733749505</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1453417353936599</v>
+        <v>0.1477975168139564</v>
       </c>
       <c r="T63">
-        <v>2.298885343964432</v>
+        <v>2.355600850206845</v>
       </c>
       <c r="U63">
         <v>0.0578</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.730558787551487</v>
+        <v>2.686517516784527</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08676700038930342</v>
+        <v>0.08674039197507949</v>
       </c>
       <c r="C64">
-        <v>33156.26624588062</v>
+        <v>32348.92721805675</v>
       </c>
       <c r="D64">
-        <v>83811.53009896657</v>
+        <v>83866.00177845055</v>
       </c>
       <c r="E64">
-        <v>21037.99312230216</v>
+        <v>21899.80382961</v>
       </c>
       <c r="F64">
-        <v>53432.26385308595</v>
+        <v>54294.0745603938</v>
       </c>
       <c r="G64">
         <v>2777</v>
@@ -6535,28 +6535,28 @@
         <v>8297</v>
       </c>
       <c r="M64">
-        <v>3088.384850708369</v>
+        <v>3138.197509590762</v>
       </c>
       <c r="N64">
-        <v>5208.615149291631</v>
+        <v>5158.802490409238</v>
       </c>
       <c r="O64">
-        <v>760.4578117965782</v>
+        <v>753.1851635997488</v>
       </c>
       <c r="P64">
-        <v>4448.157337495053</v>
+        <v>4405.617326809489</v>
       </c>
       <c r="Q64">
-        <v>10971.15733749505</v>
+        <v>10928.61732680949</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1477975168139564</v>
+        <v>0.1503860431758905</v>
       </c>
       <c r="T64">
-        <v>2.355600850206845</v>
+        <v>2.415382059489389</v>
       </c>
       <c r="U64">
         <v>0.0578</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.686517516784527</v>
+        <v>2.643874381597471</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08674039197507949</v>
+        <v>0.08671378356085555</v>
       </c>
       <c r="C65">
-        <v>32348.92721805675</v>
+        <v>31541.65904190612</v>
       </c>
       <c r="D65">
-        <v>83866.00177845055</v>
+        <v>83920.54430960775</v>
       </c>
       <c r="E65">
-        <v>21899.80382961</v>
+        <v>22761.61453691784</v>
       </c>
       <c r="F65">
-        <v>54294.0745603938</v>
+        <v>55155.88526770163</v>
       </c>
       <c r="G65">
         <v>2777</v>
@@ -6617,28 +6617,28 @@
         <v>8297</v>
       </c>
       <c r="M65">
-        <v>3138.197509590762</v>
+        <v>3188.010168473154</v>
       </c>
       <c r="N65">
-        <v>5158.802490409238</v>
+        <v>5108.989831526846</v>
       </c>
       <c r="O65">
-        <v>753.1851635997488</v>
+        <v>745.9125154029194</v>
       </c>
       <c r="P65">
-        <v>4405.617326809489</v>
+        <v>4363.077316123926</v>
       </c>
       <c r="Q65">
-        <v>10928.61732680949</v>
+        <v>10886.07731612393</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1503860431758905</v>
+        <v>0.1531183765579321</v>
       </c>
       <c r="T65">
-        <v>2.415382059489389</v>
+        <v>2.478484447065407</v>
       </c>
       <c r="U65">
         <v>0.0578</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.643874381597471</v>
+        <v>2.602563844385011</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08671378356085555</v>
+        <v>0.08668717514663163</v>
       </c>
       <c r="C66">
-        <v>31541.65904190612</v>
+        <v>30734.46185575444</v>
       </c>
       <c r="D66">
-        <v>83920.54430960775</v>
+        <v>83975.15783076391</v>
       </c>
       <c r="E66">
-        <v>22761.61453691784</v>
+        <v>23623.42524422568</v>
       </c>
       <c r="F66">
-        <v>55155.88526770163</v>
+        <v>56017.69597500948</v>
       </c>
       <c r="G66">
         <v>2777</v>
@@ -6699,28 +6699,28 @@
         <v>8297</v>
       </c>
       <c r="M66">
-        <v>3188.010168473154</v>
+        <v>3237.822827355548</v>
       </c>
       <c r="N66">
-        <v>5108.989831526846</v>
+        <v>5059.177172644452</v>
       </c>
       <c r="O66">
-        <v>745.9125154029194</v>
+        <v>738.63986720609</v>
       </c>
       <c r="P66">
-        <v>4363.077316123926</v>
+        <v>4320.537305438362</v>
       </c>
       <c r="Q66">
-        <v>10886.07731612393</v>
+        <v>10843.53730543836</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1531183765579321</v>
+        <v>0.1560068432760904</v>
       </c>
       <c r="T66">
-        <v>2.478484447065407</v>
+        <v>2.545192685360055</v>
       </c>
       <c r="U66">
         <v>0.0578</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.602563844385011</v>
+        <v>2.562524400625241</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08668717514663163</v>
+        <v>0.08666056673240768</v>
       </c>
       <c r="C67">
-        <v>30734.46185575444</v>
+        <v>29927.335798288</v>
       </c>
       <c r="D67">
-        <v>83975.15783076391</v>
+        <v>84029.84248060531</v>
       </c>
       <c r="E67">
-        <v>23623.42524422568</v>
+        <v>24485.23595153352</v>
       </c>
       <c r="F67">
-        <v>56017.69597500948</v>
+        <v>56879.50668231731</v>
       </c>
       <c r="G67">
         <v>2777</v>
@@ -6781,28 +6781,28 @@
         <v>8297</v>
       </c>
       <c r="M67">
-        <v>3237.822827355548</v>
+        <v>3287.635486237941</v>
       </c>
       <c r="N67">
-        <v>5059.177172644452</v>
+        <v>5009.364513762059</v>
       </c>
       <c r="O67">
-        <v>738.63986720609</v>
+        <v>731.3672190092606</v>
       </c>
       <c r="P67">
-        <v>4320.537305438362</v>
+        <v>4277.997294752799</v>
       </c>
       <c r="Q67">
-        <v>10843.53730543836</v>
+        <v>10800.9972947528</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1560068432760904</v>
+        <v>0.1590652198011991</v>
       </c>
       <c r="T67">
-        <v>2.545192685360055</v>
+        <v>2.615824937672035</v>
       </c>
       <c r="U67">
         <v>0.0578</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.562524400625241</v>
+        <v>2.523698273343041</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08666056673240768</v>
+        <v>0.08863658831818376</v>
       </c>
       <c r="C68">
-        <v>29927.335798288</v>
+        <v>25189.28776419577</v>
       </c>
       <c r="D68">
-        <v>84029.84248060531</v>
+        <v>80153.60515382093</v>
       </c>
       <c r="E68">
-        <v>24485.23595153352</v>
+        <v>25347.04665884136</v>
       </c>
       <c r="F68">
-        <v>56879.50668231731</v>
+        <v>57741.31738962515</v>
       </c>
       <c r="G68">
         <v>2777</v>
@@ -6863,45 +6863,45 @@
         <v>8297</v>
       </c>
       <c r="M68">
-        <v>3287.635486237941</v>
+        <v>3539.542755984022</v>
       </c>
       <c r="N68">
-        <v>5009.364513762059</v>
+        <v>4757.457244015978</v>
       </c>
       <c r="O68">
-        <v>731.3672190092606</v>
+        <v>694.5887576263327</v>
       </c>
       <c r="P68">
-        <v>4277.997294752799</v>
+        <v>4062.868486389646</v>
       </c>
       <c r="Q68">
-        <v>10800.9972947528</v>
+        <v>10585.86848638965</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1590652198011991</v>
+        <v>0.1623089524793447</v>
       </c>
       <c r="T68">
-        <v>2.615824937672035</v>
+        <v>2.690737932548378</v>
       </c>
       <c r="U68">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V68">
         <v>0.146</v>
       </c>
       <c r="W68">
-        <v>0.0493612</v>
+        <v>0.0523502</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y68">
-        <v>2.523698273343041</v>
+        <v>2.344088084816302</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08863658831818376</v>
+        <v>0.08863986990395981</v>
       </c>
       <c r="C69">
-        <v>25189.28776419577</v>
+        <v>24321.33719392474</v>
       </c>
       <c r="D69">
-        <v>80153.60515382093</v>
+        <v>80147.46529085773</v>
       </c>
       <c r="E69">
-        <v>25347.04665884136</v>
+        <v>26208.85736614919</v>
       </c>
       <c r="F69">
-        <v>57741.31738962515</v>
+        <v>58603.12809693299</v>
       </c>
       <c r="G69">
         <v>2777</v>
@@ -6945,28 +6945,28 @@
         <v>8297</v>
       </c>
       <c r="M69">
-        <v>3539.542755984022</v>
+        <v>3592.371752341992</v>
       </c>
       <c r="N69">
-        <v>4757.457244015978</v>
+        <v>4704.628247658007</v>
       </c>
       <c r="O69">
-        <v>694.5887576263327</v>
+        <v>686.875724158069</v>
       </c>
       <c r="P69">
-        <v>4062.868486389646</v>
+        <v>4017.752523499938</v>
       </c>
       <c r="Q69">
-        <v>10585.86848638965</v>
+        <v>10540.75252349994</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1623089524793447</v>
+        <v>0.1657554184498744</v>
       </c>
       <c r="T69">
-        <v>2.690737932548378</v>
+        <v>2.770332989604491</v>
       </c>
       <c r="U69">
         <v>0.0613</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.344088084816302</v>
+        <v>2.309616201216062</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08863986990395981</v>
+        <v>0.08864315148973589</v>
       </c>
       <c r="C70">
-        <v>24321.33719392474</v>
+        <v>23453.38756422341</v>
       </c>
       <c r="D70">
-        <v>80147.46529085773</v>
+        <v>80141.32636846424</v>
       </c>
       <c r="E70">
-        <v>26208.85736614919</v>
+        <v>27070.66807345704</v>
       </c>
       <c r="F70">
-        <v>58603.12809693299</v>
+        <v>59464.93880424083</v>
       </c>
       <c r="G70">
         <v>2777</v>
@@ -7027,28 +7027,28 @@
         <v>8297</v>
       </c>
       <c r="M70">
-        <v>3592.371752341992</v>
+        <v>3645.200748699963</v>
       </c>
       <c r="N70">
-        <v>4704.628247658007</v>
+        <v>4651.799251300037</v>
       </c>
       <c r="O70">
-        <v>686.875724158069</v>
+        <v>679.1626906898053</v>
       </c>
       <c r="P70">
-        <v>4017.752523499938</v>
+        <v>3972.636560610232</v>
       </c>
       <c r="Q70">
-        <v>10540.75252349994</v>
+        <v>10495.63656061023</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1657554184498744</v>
+        <v>0.1694242370636642</v>
       </c>
       <c r="T70">
-        <v>2.770332989604491</v>
+        <v>2.855063211631968</v>
       </c>
       <c r="U70">
         <v>0.0613</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.309616201216062</v>
+        <v>2.276143502647713</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08864315148973589</v>
+        <v>0.09032027307551195</v>
       </c>
       <c r="C71">
-        <v>23453.38756422341</v>
+        <v>19572.57586971801</v>
       </c>
       <c r="D71">
-        <v>80141.32636846424</v>
+        <v>77122.32538126668</v>
       </c>
       <c r="E71">
-        <v>27070.66807345704</v>
+        <v>27932.47878076487</v>
       </c>
       <c r="F71">
-        <v>59464.93880424083</v>
+        <v>60326.74951154867</v>
       </c>
       <c r="G71">
         <v>2777</v>
@@ -7109,45 +7109,45 @@
         <v>8297</v>
       </c>
       <c r="M71">
-        <v>3645.200748699963</v>
+        <v>3866.94464369027</v>
       </c>
       <c r="N71">
-        <v>4651.799251300037</v>
+        <v>4430.05535630973</v>
       </c>
       <c r="O71">
-        <v>679.1626906898053</v>
+        <v>646.7880820212206</v>
       </c>
       <c r="P71">
-        <v>3972.636560610232</v>
+        <v>3783.26727428851</v>
       </c>
       <c r="Q71">
-        <v>10495.63656061023</v>
+        <v>10306.26727428851</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1694242370636642</v>
+        <v>0.1733376435850399</v>
       </c>
       <c r="T71">
-        <v>2.855063211631968</v>
+        <v>2.945442115127942</v>
       </c>
       <c r="U71">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V71">
         <v>0.146</v>
       </c>
       <c r="W71">
-        <v>0.0523502</v>
+        <v>0.0547414</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y71">
-        <v>2.276143502647713</v>
+        <v>2.145621612023408</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09032027307551195</v>
+        <v>0.09034746666128803</v>
       </c>
       <c r="C72">
-        <v>19572.57586971801</v>
+        <v>18663.68655777365</v>
       </c>
       <c r="D72">
-        <v>77122.32538126668</v>
+        <v>77075.24677663016</v>
       </c>
       <c r="E72">
-        <v>27932.47878076487</v>
+        <v>28794.28948807271</v>
       </c>
       <c r="F72">
-        <v>60326.74951154867</v>
+        <v>61188.5602188565</v>
       </c>
       <c r="G72">
         <v>2777</v>
@@ -7191,28 +7191,28 @@
         <v>8297</v>
       </c>
       <c r="M72">
-        <v>3866.94464369027</v>
+        <v>3922.186710028702</v>
       </c>
       <c r="N72">
-        <v>4430.05535630973</v>
+        <v>4374.813289971298</v>
       </c>
       <c r="O72">
-        <v>646.7880820212206</v>
+        <v>638.7227403358095</v>
       </c>
       <c r="P72">
-        <v>3783.26727428851</v>
+        <v>3736.090549635489</v>
       </c>
       <c r="Q72">
-        <v>10306.26727428851</v>
+        <v>10259.09054963549</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1733376435850399</v>
+        <v>0.177520940211338</v>
       </c>
       <c r="T72">
-        <v>2.945442115127942</v>
+        <v>3.042054046451226</v>
       </c>
       <c r="U72">
         <v>0.0641</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.145621612023408</v>
+        <v>2.115401589318853</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09034746666128803</v>
+        <v>0.09037466024706409</v>
       </c>
       <c r="C73">
-        <v>18663.68655777366</v>
+        <v>17754.8546881549</v>
       </c>
       <c r="D73">
-        <v>77075.24677663016</v>
+        <v>77028.22561431924</v>
       </c>
       <c r="E73">
-        <v>28794.2894880727</v>
+        <v>29656.10019538054</v>
       </c>
       <c r="F73">
-        <v>61188.5602188565</v>
+        <v>62050.37092616434</v>
       </c>
       <c r="G73">
         <v>2777</v>
@@ -7273,28 +7273,28 @@
         <v>8297</v>
       </c>
       <c r="M73">
-        <v>3922.186710028702</v>
+        <v>3977.428776367134</v>
       </c>
       <c r="N73">
-        <v>4374.813289971298</v>
+        <v>4319.571223632865</v>
       </c>
       <c r="O73">
-        <v>638.7227403358095</v>
+        <v>630.6573986503984</v>
       </c>
       <c r="P73">
-        <v>3736.090549635489</v>
+        <v>3688.913824982467</v>
       </c>
       <c r="Q73">
-        <v>10259.09054963549</v>
+        <v>10211.91382498247</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.177520940211338</v>
+        <v>0.1820030437395146</v>
       </c>
       <c r="T73">
-        <v>3.042054046451225</v>
+        <v>3.145566830011885</v>
       </c>
       <c r="U73">
         <v>0.0641</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.115401589318854</v>
+        <v>2.086021011689425</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09037466024706409</v>
+        <v>0.09040185383284015</v>
       </c>
       <c r="C74">
-        <v>17754.8546881549</v>
+        <v>16846.0801557946</v>
       </c>
       <c r="D74">
-        <v>77028.22561431924</v>
+        <v>76981.26178926678</v>
       </c>
       <c r="E74">
-        <v>29656.10019538054</v>
+        <v>30517.91090268838</v>
       </c>
       <c r="F74">
-        <v>62050.37092616434</v>
+        <v>62912.18163347217</v>
       </c>
       <c r="G74">
         <v>2777</v>
@@ -7355,28 +7355,28 @@
         <v>8297</v>
       </c>
       <c r="M74">
-        <v>3977.428776367134</v>
+        <v>4032.670842705566</v>
       </c>
       <c r="N74">
-        <v>4319.571223632865</v>
+        <v>4264.329157294434</v>
       </c>
       <c r="O74">
-        <v>630.6573986503984</v>
+        <v>622.5920569649873</v>
       </c>
       <c r="P74">
-        <v>3688.913824982467</v>
+        <v>3641.737100329447</v>
       </c>
       <c r="Q74">
-        <v>10211.91382498247</v>
+        <v>10164.73710032945</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1820030437395146</v>
+        <v>0.186817154936445</v>
       </c>
       <c r="T74">
-        <v>3.145566830011885</v>
+        <v>3.256747227169631</v>
       </c>
       <c r="U74">
         <v>0.0641</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.086021011689425</v>
+        <v>2.057445381392309</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09040185383284015</v>
+        <v>0.09042904741861622</v>
       </c>
       <c r="C75">
-        <v>16846.0801557946</v>
+        <v>15937.36285588169</v>
       </c>
       <c r="D75">
-        <v>76981.26178926678</v>
+        <v>76934.35519666171</v>
       </c>
       <c r="E75">
-        <v>30517.91090268838</v>
+        <v>31379.72160999622</v>
       </c>
       <c r="F75">
-        <v>62912.18163347217</v>
+        <v>63773.99234078002</v>
       </c>
       <c r="G75">
         <v>2777</v>
@@ -7437,28 +7437,28 @@
         <v>8297</v>
       </c>
       <c r="M75">
-        <v>4032.670842705566</v>
+        <v>4087.912909043999</v>
       </c>
       <c r="N75">
-        <v>4264.329157294434</v>
+        <v>4209.087090956001</v>
       </c>
       <c r="O75">
-        <v>622.5920569649873</v>
+        <v>614.526715279576</v>
       </c>
       <c r="P75">
-        <v>3641.737100329447</v>
+        <v>3594.560375676425</v>
       </c>
       <c r="Q75">
-        <v>10164.73710032945</v>
+        <v>10117.56037567642</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.186817154936445</v>
+        <v>0.1920015823792932</v>
       </c>
       <c r="T75">
-        <v>3.256747227169631</v>
+        <v>3.376479962570281</v>
       </c>
       <c r="U75">
         <v>0.0641</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.057445381392309</v>
+        <v>2.029642065427548</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09042904741861622</v>
+        <v>0.09045624100439228</v>
       </c>
       <c r="C76">
-        <v>15937.36285588169</v>
+        <v>15028.70268386051</v>
       </c>
       <c r="D76">
-        <v>76934.35519666171</v>
+        <v>76887.50573194836</v>
       </c>
       <c r="E76">
-        <v>31379.72160999622</v>
+        <v>32241.53231730406</v>
       </c>
       <c r="F76">
-        <v>63773.99234078002</v>
+        <v>64635.80304808785</v>
       </c>
       <c r="G76">
         <v>2777</v>
@@ -7519,28 +7519,28 @@
         <v>8297</v>
       </c>
       <c r="M76">
-        <v>4087.912909043999</v>
+        <v>4143.154975382432</v>
       </c>
       <c r="N76">
-        <v>4209.087090956001</v>
+        <v>4153.845024617568</v>
       </c>
       <c r="O76">
-        <v>614.526715279576</v>
+        <v>606.4613735941649</v>
       </c>
       <c r="P76">
-        <v>3594.560375676425</v>
+        <v>3547.383651023403</v>
       </c>
       <c r="Q76">
-        <v>10117.56037567642</v>
+        <v>10070.3836510234</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1920015823792932</v>
+        <v>0.1976007640175691</v>
       </c>
       <c r="T76">
-        <v>3.376479962570281</v>
+        <v>3.505791316802983</v>
       </c>
       <c r="U76">
         <v>0.0641</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.029642065427548</v>
+        <v>2.002580171221847</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09045624100439228</v>
+        <v>0.09554594659016835</v>
       </c>
       <c r="C77">
-        <v>15028.70268386051</v>
+        <v>6300.225560004277</v>
       </c>
       <c r="D77">
-        <v>76887.50573194836</v>
+        <v>69020.83931539996</v>
       </c>
       <c r="E77">
-        <v>32241.53231730406</v>
+        <v>33103.3430246119</v>
       </c>
       <c r="F77">
-        <v>64635.80304808785</v>
+        <v>65497.61375539569</v>
       </c>
       <c r="G77">
         <v>2777</v>
@@ -7601,45 +7601,45 @@
         <v>8297</v>
       </c>
       <c r="M77">
-        <v>4143.154975382432</v>
+        <v>4709.27842901295</v>
       </c>
       <c r="N77">
-        <v>4153.845024617568</v>
+        <v>3587.72157098705</v>
       </c>
       <c r="O77">
-        <v>606.4613735941649</v>
+        <v>523.8073493641092</v>
       </c>
       <c r="P77">
-        <v>3547.383651023403</v>
+        <v>3063.914221622941</v>
       </c>
       <c r="Q77">
-        <v>10070.3836510234</v>
+        <v>9586.914221622941</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1976007640175691</v>
+        <v>0.2036665441257015</v>
       </c>
       <c r="T77">
-        <v>3.505791316802983</v>
+        <v>3.645878617221744</v>
       </c>
       <c r="U77">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V77">
         <v>0.146</v>
       </c>
       <c r="W77">
-        <v>0.0547414</v>
+        <v>0.0614026</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y77">
-        <v>2.002580171221847</v>
+        <v>1.761841038933649</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09554594659016835</v>
+        <v>0.09820431417594441</v>
       </c>
       <c r="C78">
-        <v>6300.225560004277</v>
+        <v>1937.123692524328</v>
       </c>
       <c r="D78">
-        <v>69020.83931539996</v>
+        <v>65519.54815522784</v>
       </c>
       <c r="E78">
-        <v>33103.3430246119</v>
+        <v>33965.15373191972</v>
       </c>
       <c r="F78">
-        <v>65497.61375539569</v>
+        <v>66359.42446270352</v>
       </c>
       <c r="G78">
         <v>2777</v>
@@ -7683,45 +7683,45 @@
         <v>8297</v>
       </c>
       <c r="M78">
-        <v>4709.27842901295</v>
+        <v>5030.044374272928</v>
       </c>
       <c r="N78">
-        <v>3587.72157098705</v>
+        <v>3266.955625727072</v>
       </c>
       <c r="O78">
-        <v>523.8073493641092</v>
+        <v>476.9755213561526</v>
       </c>
       <c r="P78">
-        <v>3063.914221622941</v>
+        <v>2789.98010437092</v>
       </c>
       <c r="Q78">
-        <v>9586.914221622941</v>
+        <v>9312.980104370919</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2036665441257015</v>
+        <v>0.2102597833736714</v>
       </c>
       <c r="T78">
-        <v>3.645878617221744</v>
+        <v>3.798147422024745</v>
       </c>
       <c r="U78">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V78">
         <v>0.146</v>
       </c>
       <c r="W78">
-        <v>0.0614026</v>
+        <v>0.0647332</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y78">
-        <v>1.761841038933649</v>
+        <v>1.649488430447355</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09820431417594441</v>
+        <v>0.09833142576172049</v>
       </c>
       <c r="C79">
-        <v>1937.123692524328</v>
+        <v>916.7737195373047</v>
       </c>
       <c r="D79">
-        <v>65519.54815522784</v>
+        <v>65361.00888954867</v>
       </c>
       <c r="E79">
-        <v>33965.15373191972</v>
+        <v>34826.96443922757</v>
       </c>
       <c r="F79">
-        <v>66359.42446270352</v>
+        <v>67221.23517001136</v>
       </c>
       <c r="G79">
         <v>2777</v>
@@ -7765,28 +7765,28 @@
         <v>8297</v>
       </c>
       <c r="M79">
-        <v>5030.044374272928</v>
+        <v>5095.369625886862</v>
       </c>
       <c r="N79">
-        <v>3266.955625727072</v>
+        <v>3201.630374113138</v>
       </c>
       <c r="O79">
-        <v>476.9755213561526</v>
+        <v>467.4380346205181</v>
       </c>
       <c r="P79">
-        <v>2789.98010437092</v>
+        <v>2734.19233949262</v>
       </c>
       <c r="Q79">
-        <v>9312.980104370919</v>
+        <v>9257.19233949262</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2102597833736714</v>
+        <v>0.2174524080078204</v>
       </c>
       <c r="T79">
-        <v>3.798147422024745</v>
+        <v>3.964258845446199</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.649488430447355</v>
+        <v>1.628341142877517</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09833142576172049</v>
+        <v>0.09845853734749656</v>
       </c>
       <c r="C80">
-        <v>916.7737195373047</v>
+        <v>-102.8108627463807</v>
       </c>
       <c r="D80">
-        <v>65361.00888954867</v>
+        <v>65203.23501457283</v>
       </c>
       <c r="E80">
-        <v>34826.96443922757</v>
+        <v>35688.77514653541</v>
       </c>
       <c r="F80">
-        <v>67221.23517001136</v>
+        <v>68083.04587731921</v>
       </c>
       <c r="G80">
         <v>2777</v>
@@ -7847,28 +7847,28 @@
         <v>8297</v>
       </c>
       <c r="M80">
-        <v>5095.369625886862</v>
+        <v>5160.694877500797</v>
       </c>
       <c r="N80">
-        <v>3201.630374113138</v>
+        <v>3136.305122499203</v>
       </c>
       <c r="O80">
-        <v>467.4380346205181</v>
+        <v>457.9005478848836</v>
       </c>
       <c r="P80">
-        <v>2734.19233949262</v>
+        <v>2678.40457461432</v>
       </c>
       <c r="Q80">
-        <v>9257.19233949262</v>
+        <v>9201.40457461432</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2174524080078204</v>
+        <v>0.2253300445118884</v>
       </c>
       <c r="T80">
-        <v>3.964258845446199</v>
+        <v>4.146190404431604</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.628341142877517</v>
+        <v>1.607729229676536</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09845853734749656</v>
+        <v>0.09858564893327262</v>
       </c>
       <c r="C81">
-        <v>-102.8108627463807</v>
+        <v>-1121.635583671989</v>
       </c>
       <c r="D81">
-        <v>65203.23501457283</v>
+        <v>65046.22100095507</v>
       </c>
       <c r="E81">
-        <v>35688.77514653541</v>
+        <v>36550.58585384325</v>
       </c>
       <c r="F81">
-        <v>68083.04587731921</v>
+        <v>68944.85658462705</v>
       </c>
       <c r="G81">
         <v>2777</v>
@@ -7929,28 +7929,28 @@
         <v>8297</v>
       </c>
       <c r="M81">
-        <v>5160.694877500797</v>
+        <v>5226.02012911473</v>
       </c>
       <c r="N81">
-        <v>3136.305122499203</v>
+        <v>3070.97987088527</v>
       </c>
       <c r="O81">
-        <v>457.9005478848836</v>
+        <v>448.3630611492493</v>
       </c>
       <c r="P81">
-        <v>2678.40457461432</v>
+        <v>2622.61680973602</v>
       </c>
       <c r="Q81">
-        <v>9201.40457461432</v>
+        <v>9145.616809736021</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2253300445118884</v>
+        <v>0.2339954446663631</v>
       </c>
       <c r="T81">
-        <v>4.146190404431604</v>
+        <v>4.346315119315546</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.607729229676536</v>
+        <v>1.587632614305579</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09858564893327262</v>
+        <v>0.09871276051904869</v>
       </c>
       <c r="C82">
-        <v>-1121.635583671989</v>
+        <v>-2139.705919452521</v>
       </c>
       <c r="D82">
-        <v>65046.22100095507</v>
+        <v>64889.96137248236</v>
       </c>
       <c r="E82">
-        <v>36550.58585384325</v>
+        <v>37412.39656115108</v>
       </c>
       <c r="F82">
-        <v>68944.85658462705</v>
+        <v>69806.66729193488</v>
       </c>
       <c r="G82">
         <v>2777</v>
@@ -8011,28 +8011,28 @@
         <v>8297</v>
       </c>
       <c r="M82">
-        <v>5226.02012911473</v>
+        <v>5291.345380728664</v>
       </c>
       <c r="N82">
-        <v>3070.97987088527</v>
+        <v>3005.654619271336</v>
       </c>
       <c r="O82">
-        <v>448.3630611492493</v>
+        <v>438.825574413615</v>
       </c>
       <c r="P82">
-        <v>2622.61680973602</v>
+        <v>2566.829044857721</v>
       </c>
       <c r="Q82">
-        <v>9145.616809736021</v>
+        <v>9089.829044857721</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2339954446663631</v>
+        <v>0.2435729922055194</v>
       </c>
       <c r="T82">
-        <v>4.346315119315546</v>
+        <v>4.567505593660958</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.587632614305579</v>
+        <v>1.568032211659832</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09871276051904869</v>
+        <v>0.09883987210482476</v>
       </c>
       <c r="C83">
-        <v>-2139.705919452521</v>
+        <v>-3157.027293805382</v>
       </c>
       <c r="D83">
-        <v>64889.96137248236</v>
+        <v>64734.45070543734</v>
       </c>
       <c r="E83">
-        <v>37412.39656115108</v>
+        <v>38274.20726845892</v>
       </c>
       <c r="F83">
-        <v>69806.66729193488</v>
+        <v>70668.47799924272</v>
       </c>
       <c r="G83">
         <v>2777</v>
@@ -8093,28 +8093,28 @@
         <v>8297</v>
       </c>
       <c r="M83">
-        <v>5291.345380728664</v>
+        <v>5356.670632342599</v>
       </c>
       <c r="N83">
-        <v>3005.654619271336</v>
+        <v>2940.329367657401</v>
       </c>
       <c r="O83">
-        <v>438.825574413615</v>
+        <v>429.2880876779806</v>
       </c>
       <c r="P83">
-        <v>2566.829044857721</v>
+        <v>2511.041279979421</v>
       </c>
       <c r="Q83">
-        <v>9089.829044857721</v>
+        <v>9034.041279979421</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2435729922055194</v>
+        <v>0.2542147116934709</v>
       </c>
       <c r="T83">
-        <v>4.567505593660958</v>
+        <v>4.813272787378082</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.568032211659832</v>
+        <v>1.548909867615199</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09883987210482476</v>
+        <v>0.09896698369060082</v>
       </c>
       <c r="C84">
-        <v>-3157.027293805382</v>
+        <v>-4173.605078579872</v>
       </c>
       <c r="D84">
-        <v>64734.45070543734</v>
+        <v>64579.6836279707</v>
       </c>
       <c r="E84">
-        <v>38274.20726845892</v>
+        <v>39136.01797576676</v>
       </c>
       <c r="F84">
-        <v>70668.47799924272</v>
+        <v>71530.28870655056</v>
       </c>
       <c r="G84">
         <v>2777</v>
@@ -8175,28 +8175,28 @@
         <v>8297</v>
       </c>
       <c r="M84">
-        <v>5356.670632342599</v>
+        <v>5421.995883956533</v>
       </c>
       <c r="N84">
-        <v>2940.329367657401</v>
+        <v>2875.004116043467</v>
       </c>
       <c r="O84">
-        <v>429.2880876779806</v>
+        <v>419.7506009423461</v>
       </c>
       <c r="P84">
-        <v>2511.041279979421</v>
+        <v>2455.253515101121</v>
       </c>
       <c r="Q84">
-        <v>9034.041279979421</v>
+        <v>8978.253515101122</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2542147116934709</v>
+        <v>0.2661083981800049</v>
       </c>
       <c r="T84">
-        <v>4.813272787378082</v>
+        <v>5.087953768591339</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.548909867615199</v>
+        <v>1.530248302945136</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09896698369060082</v>
+        <v>0.09909409527637689</v>
       </c>
       <c r="C85">
-        <v>-4173.605078579872</v>
+        <v>-5189.444594375731</v>
       </c>
       <c r="D85">
-        <v>64579.6836279707</v>
+        <v>64425.65481948267</v>
       </c>
       <c r="E85">
-        <v>39136.01797576676</v>
+        <v>39997.82868307461</v>
       </c>
       <c r="F85">
-        <v>71530.28870655056</v>
+        <v>72392.09941385841</v>
       </c>
       <c r="G85">
         <v>2777</v>
@@ -8257,28 +8257,28 @@
         <v>8297</v>
       </c>
       <c r="M85">
-        <v>5421.995883956533</v>
+        <v>5487.321135570468</v>
       </c>
       <c r="N85">
-        <v>2875.004116043467</v>
+        <v>2809.678864429532</v>
       </c>
       <c r="O85">
-        <v>419.7506009423461</v>
+        <v>410.2131142067117</v>
       </c>
       <c r="P85">
-        <v>2455.253515101121</v>
+        <v>2399.46575022282</v>
       </c>
       <c r="Q85">
-        <v>8978.253515101122</v>
+        <v>8922.46575022282</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2661083981800049</v>
+        <v>0.2794887954773557</v>
       </c>
       <c r="T85">
-        <v>5.087953768591339</v>
+        <v>5.396969872456252</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.530248302945136</v>
+        <v>1.512031061243408</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09909409527637689</v>
+        <v>0.109528986862153</v>
       </c>
       <c r="C86">
-        <v>-5189.444594375716</v>
+        <v>-16600.21828516982</v>
       </c>
       <c r="D86">
-        <v>64425.65481948267</v>
+        <v>53876.69183599641</v>
       </c>
       <c r="E86">
-        <v>39997.82868307459</v>
+        <v>40859.63939038244</v>
       </c>
       <c r="F86">
-        <v>72392.09941385839</v>
+        <v>73253.91012116623</v>
       </c>
       <c r="G86">
         <v>2777</v>
@@ -8339,45 +8339,45 @@
         <v>8297</v>
       </c>
       <c r="M86">
-        <v>5487.321135570466</v>
+        <v>6592.851910904961</v>
       </c>
       <c r="N86">
-        <v>2809.678864429534</v>
+        <v>1704.148089095039</v>
       </c>
       <c r="O86">
-        <v>410.2131142067119</v>
+        <v>248.8056210078757</v>
       </c>
       <c r="P86">
-        <v>2399.465750222822</v>
+        <v>1455.342468087163</v>
       </c>
       <c r="Q86">
-        <v>8922.465750222822</v>
+        <v>7978.342468087163</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2794887954773555</v>
+        <v>0.2946532457476863</v>
       </c>
       <c r="T86">
-        <v>5.396969872456249</v>
+        <v>5.747188123503149</v>
       </c>
       <c r="U86">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V86">
         <v>0.146</v>
       </c>
       <c r="W86">
-        <v>0.0647332</v>
+        <v>0.07686</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y86">
-        <v>1.512031061243409</v>
+        <v>1.258484205640396</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.109528986862153</v>
+        <v>0.1319179440563445</v>
       </c>
       <c r="C87">
-        <v>-16600.21828516982</v>
+        <v>-31468.90015618732</v>
       </c>
       <c r="D87">
-        <v>53876.69183599641</v>
+        <v>39869.82067228674</v>
       </c>
       <c r="E87">
-        <v>40859.63939038244</v>
+        <v>41721.45009769026</v>
       </c>
       <c r="F87">
-        <v>73253.91012116623</v>
+        <v>74115.72082847406</v>
       </c>
       <c r="G87">
         <v>2777</v>
@@ -8421,45 +8421,45 @@
         <v>8297</v>
       </c>
       <c r="M87">
-        <v>6592.851910904961</v>
+        <v>8790.124490257025</v>
       </c>
       <c r="N87">
-        <v>1704.148089095039</v>
+        <v>-493.1244902570252</v>
       </c>
       <c r="O87">
-        <v>248.8056210078757</v>
+        <v>-71.99617557752568</v>
       </c>
       <c r="P87">
-        <v>1455.342468087163</v>
+        <v>-421.1283146794995</v>
       </c>
       <c r="Q87">
-        <v>7978.342468087163</v>
+        <v>6101.871685320501</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2946532457476863</v>
+        <v>0.3141282439224437</v>
       </c>
       <c r="T87">
-        <v>5.747188123503149</v>
+        <v>6.196957134467523</v>
       </c>
       <c r="U87">
-        <v>0.09</v>
+        <v>0.1186</v>
       </c>
       <c r="V87">
-        <v>0.146</v>
+        <v>0.1378094248087924</v>
       </c>
       <c r="W87">
-        <v>0.07686</v>
+        <v>0.1022558022176772</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y87">
-        <v>1.258484205640396</v>
+        <v>0.9439001699232356</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1319179440563445</v>
+        <v>0.1326459440563445</v>
       </c>
       <c r="C88">
-        <v>-31468.90015618732</v>
+        <v>-32664.92600462591</v>
       </c>
       <c r="D88">
-        <v>39869.82067228674</v>
+        <v>39535.605531156</v>
       </c>
       <c r="E88">
-        <v>41721.45009769026</v>
+        <v>42583.26080499811</v>
       </c>
       <c r="F88">
-        <v>74115.72082847406</v>
+        <v>74977.53153578191</v>
       </c>
       <c r="G88">
         <v>2777</v>
@@ -8503,37 +8503,37 @@
         <v>8297</v>
       </c>
       <c r="M88">
-        <v>8790.124490257025</v>
+        <v>8892.335240143735</v>
       </c>
       <c r="N88">
-        <v>-493.1244902570252</v>
+        <v>-595.3352401437351</v>
       </c>
       <c r="O88">
-        <v>-71.99617557752568</v>
+        <v>-86.91894506098531</v>
       </c>
       <c r="P88">
-        <v>-421.1283146794995</v>
+        <v>-508.4162950827497</v>
       </c>
       <c r="Q88">
-        <v>6101.871685320501</v>
+        <v>6014.583704917251</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3141282439224437</v>
+        <v>0.3347688780703239</v>
       </c>
       <c r="T88">
-        <v>6.196957134467523</v>
+        <v>6.673646144811178</v>
       </c>
       <c r="U88">
         <v>0.1186</v>
       </c>
       <c r="V88">
-        <v>0.1378094248087924</v>
+        <v>0.1362254084316798</v>
       </c>
       <c r="W88">
-        <v>0.1022558022176772</v>
+        <v>0.1024436665600028</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.9439001699232356</v>
+        <v>0.9330507426827386</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1326459440563445</v>
+        <v>0.1333739440563445</v>
       </c>
       <c r="C89">
-        <v>-32664.92600462591</v>
+        <v>-33855.39520889678</v>
       </c>
       <c r="D89">
-        <v>39535.605531156</v>
+        <v>39206.94703419297</v>
       </c>
       <c r="E89">
-        <v>42583.26080499811</v>
+        <v>43445.07151230595</v>
       </c>
       <c r="F89">
-        <v>74977.53153578191</v>
+        <v>75839.34224308975</v>
       </c>
       <c r="G89">
         <v>2777</v>
@@ -8585,37 +8585,37 @@
         <v>8297</v>
       </c>
       <c r="M89">
-        <v>8892.335240143735</v>
+        <v>8994.545990030445</v>
       </c>
       <c r="N89">
-        <v>-595.3352401437351</v>
+        <v>-697.545990030445</v>
       </c>
       <c r="O89">
-        <v>-86.91894506098531</v>
+        <v>-101.841714544445</v>
       </c>
       <c r="P89">
-        <v>-508.4162950827497</v>
+        <v>-595.704275486</v>
       </c>
       <c r="Q89">
-        <v>6014.583704917251</v>
+        <v>5927.295724514</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3347688780703239</v>
+        <v>0.3588496179095176</v>
       </c>
       <c r="T89">
-        <v>6.673646144811178</v>
+        <v>7.229783323545444</v>
       </c>
       <c r="U89">
         <v>0.1186</v>
       </c>
       <c r="V89">
-        <v>0.1362254084316798</v>
+        <v>0.1346773924267743</v>
       </c>
       <c r="W89">
-        <v>0.1024436665600028</v>
+        <v>0.1026272612581846</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.9330507426827386</v>
+        <v>0.922447893334071</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1333739440563445</v>
+        <v>0.1341019440563445</v>
       </c>
       <c r="C90">
-        <v>-33855.39520889678</v>
+        <v>-35040.44520324319</v>
       </c>
       <c r="D90">
-        <v>39206.94703419297</v>
+        <v>38883.7077471544</v>
       </c>
       <c r="E90">
-        <v>43445.07151230595</v>
+        <v>44306.88221961379</v>
       </c>
       <c r="F90">
-        <v>75839.34224308975</v>
+        <v>76701.15295039759</v>
       </c>
       <c r="G90">
         <v>2777</v>
@@ -8667,37 +8667,37 @@
         <v>8297</v>
       </c>
       <c r="M90">
-        <v>8994.545990030445</v>
+        <v>9096.756739917155</v>
       </c>
       <c r="N90">
-        <v>-697.545990030445</v>
+        <v>-799.7567399171548</v>
       </c>
       <c r="O90">
-        <v>-101.841714544445</v>
+        <v>-116.7644840279046</v>
       </c>
       <c r="P90">
-        <v>-595.704275486</v>
+        <v>-682.9922558892503</v>
       </c>
       <c r="Q90">
-        <v>5927.295724514</v>
+        <v>5840.00774411075</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3588496179095176</v>
+        <v>0.3873086740831101</v>
       </c>
       <c r="T90">
-        <v>7.229783323545444</v>
+        <v>7.887036352958667</v>
       </c>
       <c r="U90">
         <v>0.1186</v>
       </c>
       <c r="V90">
-        <v>0.1346773924267743</v>
+        <v>0.1331641632983836</v>
       </c>
       <c r="W90">
-        <v>0.1026272612581846</v>
+        <v>0.1028067302328117</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.922447893334071</v>
+        <v>0.9120833102629017</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1341019440563445</v>
+        <v>0.1348299440563445</v>
       </c>
       <c r="C91">
-        <v>-35040.44520324319</v>
+        <v>-36220.20892669594</v>
       </c>
       <c r="D91">
-        <v>38883.7077471544</v>
+        <v>38565.75473100948</v>
       </c>
       <c r="E91">
-        <v>44306.88221961379</v>
+        <v>45168.69292692162</v>
       </c>
       <c r="F91">
-        <v>76701.15295039759</v>
+        <v>77562.96365770542</v>
       </c>
       <c r="G91">
         <v>2777</v>
@@ -8749,37 +8749,37 @@
         <v>8297</v>
       </c>
       <c r="M91">
-        <v>9096.756739917155</v>
+        <v>9198.967489803863</v>
       </c>
       <c r="N91">
-        <v>-799.7567399171548</v>
+        <v>-901.9674898038629</v>
       </c>
       <c r="O91">
-        <v>-116.7644840279046</v>
+        <v>-131.687253511364</v>
       </c>
       <c r="P91">
-        <v>-682.9922558892503</v>
+        <v>-770.2802362924989</v>
       </c>
       <c r="Q91">
-        <v>5840.00774411075</v>
+        <v>5752.719763707501</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3873086740831101</v>
+        <v>0.4214595414914211</v>
       </c>
       <c r="T91">
-        <v>7.887036352958667</v>
+        <v>8.675739988254533</v>
       </c>
       <c r="U91">
         <v>0.1186</v>
       </c>
       <c r="V91">
-        <v>0.1331641632983836</v>
+        <v>0.1316845614839572</v>
       </c>
       <c r="W91">
-        <v>0.1028067302328117</v>
+        <v>0.1029822110080027</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.9120833102629017</v>
+        <v>0.9019490512599807</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1348299440563445</v>
+        <v>0.1355579440563445</v>
       </c>
       <c r="C92">
-        <v>-36220.20892669594</v>
+        <v>-37394.81500537002</v>
       </c>
       <c r="D92">
-        <v>38565.75473100948</v>
+        <v>38252.95935964325</v>
       </c>
       <c r="E92">
-        <v>45168.69292692162</v>
+        <v>46030.50363422946</v>
       </c>
       <c r="F92">
-        <v>77562.96365770542</v>
+        <v>78424.77436501326</v>
       </c>
       <c r="G92">
         <v>2777</v>
@@ -8831,37 +8831,37 @@
         <v>8297</v>
       </c>
       <c r="M92">
-        <v>9198.967489803863</v>
+        <v>9301.178239690573</v>
       </c>
       <c r="N92">
-        <v>-901.9674898038629</v>
+        <v>-1004.178239690573</v>
       </c>
       <c r="O92">
-        <v>-131.687253511364</v>
+        <v>-146.6100229948236</v>
       </c>
       <c r="P92">
-        <v>-770.2802362924989</v>
+        <v>-857.5682166957492</v>
       </c>
       <c r="Q92">
-        <v>5752.719763707501</v>
+        <v>5665.431783304251</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4214595414914211</v>
+        <v>0.4631994905460236</v>
       </c>
       <c r="T92">
-        <v>8.675739988254533</v>
+        <v>9.639711098060594</v>
       </c>
       <c r="U92">
         <v>0.1186</v>
       </c>
       <c r="V92">
-        <v>0.1316845614839572</v>
+        <v>0.1302374783907269</v>
       </c>
       <c r="W92">
-        <v>0.1029822110080027</v>
+        <v>0.1031538350628598</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.9019490512599807</v>
+        <v>0.8920375232241566</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1355579440563445</v>
+        <v>0.1362859440563445</v>
       </c>
       <c r="C93">
-        <v>-37394.81500537002</v>
+        <v>-38564.38792596129</v>
       </c>
       <c r="D93">
-        <v>38252.95935964325</v>
+        <v>37945.19714635982</v>
       </c>
       <c r="E93">
-        <v>46030.50363422946</v>
+        <v>46892.31434153731</v>
       </c>
       <c r="F93">
-        <v>78424.77436501326</v>
+        <v>79286.5850723211</v>
       </c>
       <c r="G93">
         <v>2777</v>
@@ -8913,37 +8913,37 @@
         <v>8297</v>
       </c>
       <c r="M93">
-        <v>9301.178239690573</v>
+        <v>9403.388989577285</v>
       </c>
       <c r="N93">
-        <v>-1004.178239690573</v>
+        <v>-1106.388989577285</v>
       </c>
       <c r="O93">
-        <v>-146.6100229948236</v>
+        <v>-161.5327924782835</v>
       </c>
       <c r="P93">
-        <v>-857.5682166957492</v>
+        <v>-944.856197099001</v>
       </c>
       <c r="Q93">
-        <v>5665.431783304251</v>
+        <v>5578.143802900999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4631994905460236</v>
+        <v>0.5153744268642766</v>
       </c>
       <c r="T93">
-        <v>9.639711098060594</v>
+        <v>10.84467498531817</v>
       </c>
       <c r="U93">
         <v>0.1186</v>
       </c>
       <c r="V93">
-        <v>0.1302374783907269</v>
+        <v>0.1288218536256102</v>
       </c>
       <c r="W93">
-        <v>0.1031538350628598</v>
+        <v>0.1033217281600026</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8920375232241566</v>
+        <v>0.8823414631891113</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1362859440563445</v>
+        <v>0.1370139440563445</v>
       </c>
       <c r="C94">
-        <v>-38564.38792596129</v>
+        <v>-39729.04820093486</v>
       </c>
       <c r="D94">
-        <v>37945.19714635982</v>
+        <v>37642.34757869409</v>
       </c>
       <c r="E94">
-        <v>46892.31434153731</v>
+        <v>47754.12504884515</v>
       </c>
       <c r="F94">
-        <v>79286.5850723211</v>
+        <v>80148.39577962895</v>
       </c>
       <c r="G94">
         <v>2777</v>
@@ -8995,37 +8995,37 @@
         <v>8297</v>
       </c>
       <c r="M94">
-        <v>9403.388989577285</v>
+        <v>9505.599739463994</v>
       </c>
       <c r="N94">
-        <v>-1106.388989577285</v>
+        <v>-1208.599739463994</v>
       </c>
       <c r="O94">
-        <v>-161.5327924782835</v>
+        <v>-176.4555619617432</v>
       </c>
       <c r="P94">
-        <v>-944.856197099001</v>
+        <v>-1032.144177502251</v>
       </c>
       <c r="Q94">
-        <v>5578.143802900999</v>
+        <v>5490.855822497749</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5153744268642766</v>
+        <v>0.5824564878448877</v>
       </c>
       <c r="T94">
-        <v>10.84467498531817</v>
+        <v>12.39391426893506</v>
       </c>
       <c r="U94">
         <v>0.1186</v>
       </c>
       <c r="V94">
-        <v>0.1288218536256102</v>
+        <v>0.1274366724038295</v>
       </c>
       <c r="W94">
-        <v>0.1033217281600026</v>
+        <v>0.1034860106529058</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8823414631891113</v>
+        <v>0.8728539205741745</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1370139440563445</v>
+        <v>0.1377419440563445</v>
       </c>
       <c r="C95">
-        <v>-39729.04820093486</v>
+        <v>-40888.91252586574</v>
       </c>
       <c r="D95">
-        <v>37642.34757869409</v>
+        <v>37344.29396107104</v>
       </c>
       <c r="E95">
-        <v>47754.12504884515</v>
+        <v>48615.93575615298</v>
       </c>
       <c r="F95">
-        <v>80148.39577962895</v>
+        <v>81010.20648693678</v>
       </c>
       <c r="G95">
         <v>2777</v>
@@ -9077,37 +9077,37 @@
         <v>8297</v>
       </c>
       <c r="M95">
-        <v>9505.599739463994</v>
+        <v>9607.810489350702</v>
       </c>
       <c r="N95">
-        <v>-1208.599739463994</v>
+        <v>-1310.810489350702</v>
       </c>
       <c r="O95">
-        <v>-176.4555619617432</v>
+        <v>-191.3783314452025</v>
       </c>
       <c r="P95">
-        <v>-1032.144177502251</v>
+        <v>-1119.4321579055</v>
       </c>
       <c r="Q95">
-        <v>5490.855822497749</v>
+        <v>5403.567842094501</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5824564878448877</v>
+        <v>0.6718992358190358</v>
       </c>
       <c r="T95">
-        <v>12.39391426893506</v>
+        <v>14.4595666470909</v>
       </c>
       <c r="U95">
         <v>0.1186</v>
       </c>
       <c r="V95">
-        <v>0.1274366724038295</v>
+        <v>0.1260809631229377</v>
       </c>
       <c r="W95">
-        <v>0.1034860106529058</v>
+        <v>0.1036467977736196</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8728539205741745</v>
+        <v>0.8635682405680665</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1377419440563445</v>
+        <v>0.1384699440563446</v>
       </c>
       <c r="C96">
-        <v>-40888.91252586574</v>
+        <v>-42044.09392936317</v>
       </c>
       <c r="D96">
-        <v>37344.29396107104</v>
+        <v>37050.92326488145</v>
       </c>
       <c r="E96">
-        <v>48615.93575615298</v>
+        <v>49477.74646346082</v>
       </c>
       <c r="F96">
-        <v>81010.20648693678</v>
+        <v>81872.01719424462</v>
       </c>
       <c r="G96">
         <v>2777</v>
@@ -9159,37 +9159,37 @@
         <v>8297</v>
       </c>
       <c r="M96">
-        <v>9607.810489350702</v>
+        <v>9710.021239237412</v>
       </c>
       <c r="N96">
-        <v>-1310.810489350702</v>
+        <v>-1413.021239237412</v>
       </c>
       <c r="O96">
-        <v>-191.3783314452025</v>
+        <v>-206.3011009286622</v>
       </c>
       <c r="P96">
-        <v>-1119.4321579055</v>
+        <v>-1206.72013830875</v>
       </c>
       <c r="Q96">
-        <v>5403.567842094501</v>
+        <v>5316.27986169125</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6718992358190358</v>
+        <v>0.7971190829828433</v>
       </c>
       <c r="T96">
-        <v>14.4595666470909</v>
+        <v>17.35147997650909</v>
       </c>
       <c r="U96">
         <v>0.1186</v>
       </c>
       <c r="V96">
-        <v>0.1260809631229377</v>
+        <v>0.1247537950900647</v>
       </c>
       <c r="W96">
-        <v>0.1036467977736196</v>
+        <v>0.1038041999023183</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8635682405680665</v>
+        <v>0.8544780485620869</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1384699440563446</v>
+        <v>0.1391979440563445</v>
       </c>
       <c r="C97">
-        <v>-42044.09392936317</v>
+        <v>-43194.70191598329</v>
       </c>
       <c r="D97">
-        <v>37050.92326488145</v>
+        <v>36762.12598556917</v>
       </c>
       <c r="E97">
-        <v>49477.74646346082</v>
+        <v>50339.55717076866</v>
       </c>
       <c r="F97">
-        <v>81872.01719424462</v>
+        <v>82733.82790155246</v>
       </c>
       <c r="G97">
         <v>2777</v>
@@ -9241,37 +9241,37 @@
         <v>8297</v>
       </c>
       <c r="M97">
-        <v>9710.021239237412</v>
+        <v>9812.231989124122</v>
       </c>
       <c r="N97">
-        <v>-1413.021239237412</v>
+        <v>-1515.231989124122</v>
       </c>
       <c r="O97">
-        <v>-206.3011009286622</v>
+        <v>-221.2238704121218</v>
       </c>
       <c r="P97">
-        <v>-1206.72013830875</v>
+        <v>-1294.008118712</v>
       </c>
       <c r="Q97">
-        <v>5316.27986169125</v>
+        <v>5228.991881288</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7971190829828433</v>
+        <v>0.9849488537285545</v>
       </c>
       <c r="T97">
-        <v>17.35147997650909</v>
+        <v>21.68934997063637</v>
       </c>
       <c r="U97">
         <v>0.1186</v>
       </c>
       <c r="V97">
-        <v>0.1247537950900647</v>
+        <v>0.1234542763912098</v>
       </c>
       <c r="W97">
-        <v>0.1038041999023183</v>
+        <v>0.1039583228200025</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8544780485620869</v>
+        <v>0.8455772355562317</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1391979440563445</v>
+        <v>0.1399259440563445</v>
       </c>
       <c r="C98">
-        <v>-43194.70191598328</v>
+        <v>-44340.84260250996</v>
       </c>
       <c r="D98">
-        <v>36762.12598556917</v>
+        <v>36477.79600635033</v>
       </c>
       <c r="E98">
-        <v>50339.55717076865</v>
+        <v>51201.36787807649</v>
       </c>
       <c r="F98">
-        <v>82733.82790155245</v>
+        <v>83595.63860886029</v>
       </c>
       <c r="G98">
         <v>2777</v>
@@ -9323,37 +9323,37 @@
         <v>8297</v>
       </c>
       <c r="M98">
-        <v>9812.23198912412</v>
+        <v>9914.44273901083</v>
       </c>
       <c r="N98">
-        <v>-1515.23198912412</v>
+        <v>-1617.44273901083</v>
       </c>
       <c r="O98">
-        <v>-221.2238704121216</v>
+        <v>-236.1466398955812</v>
       </c>
       <c r="P98">
-        <v>-1294.008118711999</v>
+        <v>-1381.296099115249</v>
       </c>
       <c r="Q98">
-        <v>5228.991881288001</v>
+        <v>5141.703900884751</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9849488537285519</v>
+        <v>1.297998471638069</v>
       </c>
       <c r="T98">
-        <v>21.68934997063631</v>
+        <v>28.91913329418175</v>
       </c>
       <c r="U98">
         <v>0.1186</v>
       </c>
       <c r="V98">
-        <v>0.1234542763912098</v>
+        <v>0.1221815518923314</v>
       </c>
       <c r="W98">
-        <v>0.1039583228200025</v>
+        <v>0.1041092679455695</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8455772355562319</v>
+        <v>0.8368599444680233</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1399259440563445</v>
+        <v>0.1406539440563445</v>
       </c>
       <c r="C99">
-        <v>-44340.84260250996</v>
+        <v>-45482.61884795978</v>
       </c>
       <c r="D99">
-        <v>36477.79600635033</v>
+        <v>36197.83046820835</v>
       </c>
       <c r="E99">
-        <v>51201.36787807649</v>
+        <v>52063.17858538433</v>
       </c>
       <c r="F99">
-        <v>83595.63860886029</v>
+        <v>84457.44931616813</v>
       </c>
       <c r="G99">
         <v>2777</v>
@@ -9405,37 +9405,37 @@
         <v>8297</v>
       </c>
       <c r="M99">
-        <v>9914.44273901083</v>
+        <v>10016.65348889754</v>
       </c>
       <c r="N99">
-        <v>-1617.44273901083</v>
+        <v>-1719.653488897542</v>
       </c>
       <c r="O99">
-        <v>-236.1466398955812</v>
+        <v>-251.0694093790411</v>
       </c>
       <c r="P99">
-        <v>-1381.296099115249</v>
+        <v>-1468.584079518501</v>
       </c>
       <c r="Q99">
-        <v>5141.703900884751</v>
+        <v>5054.415920481499</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.297998471638069</v>
+        <v>1.924097707457104</v>
       </c>
       <c r="T99">
-        <v>28.91913329418175</v>
+        <v>43.37869994127263</v>
       </c>
       <c r="U99">
         <v>0.1186</v>
       </c>
       <c r="V99">
-        <v>0.1221815518923314</v>
+        <v>0.1209348013628178</v>
       </c>
       <c r="W99">
-        <v>0.1041092679455695</v>
+        <v>0.1042571325583698</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8368599444680233</v>
+        <v>0.8283205572795739</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1406539440563445</v>
+        <v>0.1413819440563445</v>
       </c>
       <c r="C100">
-        <v>-45482.61884795978</v>
+        <v>-46620.13037764595</v>
       </c>
       <c r="D100">
-        <v>36197.83046820835</v>
+        <v>35922.12964583001</v>
       </c>
       <c r="E100">
-        <v>52063.17858538433</v>
+        <v>52924.98929269216</v>
       </c>
       <c r="F100">
-        <v>84457.44931616813</v>
+        <v>85319.26002347596</v>
       </c>
       <c r="G100">
         <v>2777</v>
@@ -9487,37 +9487,37 @@
         <v>8297</v>
       </c>
       <c r="M100">
-        <v>10016.65348889754</v>
+        <v>10118.86423878425</v>
       </c>
       <c r="N100">
-        <v>-1719.653488897542</v>
+        <v>-1821.86423878425</v>
       </c>
       <c r="O100">
-        <v>-251.0694093790411</v>
+        <v>-265.9921788625005</v>
       </c>
       <c r="P100">
-        <v>-1468.584079518501</v>
+        <v>-1555.872059921749</v>
       </c>
       <c r="Q100">
-        <v>5054.415920481499</v>
+        <v>4967.127940078251</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.924097707457104</v>
+        <v>3.802395414914208</v>
       </c>
       <c r="T100">
-        <v>43.37869994127263</v>
+        <v>86.75739988254524</v>
       </c>
       <c r="U100">
         <v>0.1186</v>
       </c>
       <c r="V100">
-        <v>0.1209348013628178</v>
+        <v>0.1197132377126883</v>
       </c>
       <c r="W100">
-        <v>0.1042571325583698</v>
+        <v>0.1044020100072752</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8283205572795739</v>
+        <v>0.8199536829636187</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1413819440563445</v>
-      </c>
-      <c r="C101">
-        <v>-46620.13037764595</v>
-      </c>
-      <c r="D101">
-        <v>35922.12964583001</v>
-      </c>
-      <c r="E101">
-        <v>52924.98929269216</v>
-      </c>
-      <c r="F101">
-        <v>85319.26002347596</v>
-      </c>
-      <c r="G101">
-        <v>2777</v>
-      </c>
-      <c r="H101">
-        <v>53786.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>14820</v>
-      </c>
-      <c r="K101">
-        <v>6523</v>
-      </c>
-      <c r="L101">
-        <v>8297</v>
-      </c>
-      <c r="M101">
-        <v>10118.86423878425</v>
-      </c>
-      <c r="N101">
-        <v>-1821.86423878425</v>
-      </c>
-      <c r="O101">
-        <v>-265.9921788625005</v>
-      </c>
-      <c r="P101">
-        <v>-1555.872059921749</v>
-      </c>
-      <c r="Q101">
-        <v>4967.127940078251</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.802395414914208</v>
-      </c>
-      <c r="T101">
-        <v>86.75739988254524</v>
-      </c>
-      <c r="U101">
-        <v>0.1186</v>
-      </c>
-      <c r="V101">
-        <v>0.1197132377126883</v>
-      </c>
-      <c r="W101">
-        <v>0.1044020100072752</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Caa/CCC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8199536829636187</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
